--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>45847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>46029</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44874</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44482</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45418</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44949</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45800</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44571</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>45436</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45190</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45586</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>43969</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44858</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45684</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44949</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44544</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45540</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45068</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44650</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45400</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>46107</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>45960</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45847</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>44706</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45933</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>45847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44489</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44711</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45485</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>44956</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45664</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>46204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>46247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45783</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45581</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>45810</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45071</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>44749</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45082</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>44545</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45898</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45831</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44872</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44778</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45616</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45821</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44679</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44530</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44843</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>44771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45754</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44985</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45169</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44866</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>46163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45741</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>46027</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>44695</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45609</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>46183</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>46183</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>44743</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44629</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45642</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44880</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44474</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44956</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44863</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45118</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>45943</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>46150</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>46150</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45092</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45219</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44868</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45226</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45548</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46198</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>46247</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45383</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45803</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45559</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44896</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>44678</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44869</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45457</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45177</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45007</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44963</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45219</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45687</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45293</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>44649</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44617</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44867</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44483</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45623</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45730</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45468</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45280</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>46010</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44637</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45081</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45897</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44903</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>44747</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45764</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45987</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45904</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45992</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45418</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>44778</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44797</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44955</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>44592</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44813</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46178</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44705</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46093</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>44760</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>44813</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44461</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46133</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>46062</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>46204</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45223</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45450</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45474</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45473</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45205</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45960</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>45112</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45687</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44704</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45113</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44489</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44620</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45460</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45794</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45549</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>44965</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45826</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45855</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45708</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44639</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44518</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45572</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45994</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44642</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44540</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>44650</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44833</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44728</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>44777</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44810</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44560</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44634</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>44581</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44771</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44477</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44524</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>44574</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44516</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>44834</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44496</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44626</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44690</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>44682</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44642</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44708</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44776</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44746</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44845</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>44543</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44543</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44495</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44749</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>44882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44545</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>44722</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44742</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44756</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44806</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44511</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44510</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>44867</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>44511</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44683</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>44539</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>44496</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44516</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44712</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44769</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>44543</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44543</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>44545</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44545</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>44621</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>44637</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44735</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>44763</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44735</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>44524</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44575</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44572</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>44650</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44725</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>44580</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44777</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44665</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44637</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44655</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44595</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44744</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>44826</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44526</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>44642</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44637</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44698</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>44609</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>44760</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>44817</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>44477</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44584</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44678</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>44623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>44682</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>44682</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>44665</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44665</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>44533</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44543</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>44704</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44682</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44725</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>44523</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44595</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>44815</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>44495</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45022</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44743</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>44670</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45237</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>45518</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45443</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>45089</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>44743</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>44510</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45208</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44637</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45054</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45019</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45435</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44510</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44938</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44956</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45721</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>44841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45621</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45600</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>44643</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45376</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45636</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44832</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45245</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>44995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44783</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>45310</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44904</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45587</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>44895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45219</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>44817</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44769</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45700</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>45561</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45450</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45450</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45223</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44708</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>44708</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45145</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45642</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45208</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45208</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>44900</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45455</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>44834</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45433</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>44867</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45482</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45536</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>44953</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45531</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44816</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44901</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44931</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>44771</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>44687</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45362</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>44760</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44581</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>44732</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45640</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45394</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>44611</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>45547</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45576</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>44945</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44803</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44803</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45469</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45701</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>44778</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45670</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>44767</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>44687</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45033</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45104</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45121</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44809</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>44858</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45236</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45063</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45707</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45453</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>44949</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45243</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45177</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45757</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45708</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>44584</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45203</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45531</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45086</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45271</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45203</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>44714</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>45530</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45208</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>44845</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44472</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>44937</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45084</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>45218</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41395,7 +41395,7 @@
         <v>45208</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45356</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>44785</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45341</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45554</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45075</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44580</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45202</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45254</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>45254</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45730</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44962</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>44624</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45442</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>45670</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42500,7 +42500,7 @@
         <v>45723</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45953</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>45391</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45435</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45953</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42870,7 +42870,7 @@
         <v>45639</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45145</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45903</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>44840</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45835</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45706</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44908</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45712</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45168</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45259</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45813</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45888</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45051</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44525</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>44673</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45890</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45245</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45859</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45797</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45817</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45859</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44670</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>44516</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45621</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>45893</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45893</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45215</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45894</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45089</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>45695</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>45376</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45735</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45894</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45159</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45894</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45894</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45700</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45897</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45897</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45896</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45897</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45667</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45685</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45427</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45898</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45898</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45721</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45082</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45089</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45155</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45880</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45344</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45835</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>44459</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45490</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45469</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45831</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45638</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45772</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45908</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45092</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>44749</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45813</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45245</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>45056</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45831</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45910</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45800</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45376</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>44974</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45460</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45918</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45609</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45786</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>45257</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45923</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45022</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45022</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>44854</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>44922</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48790,7 +48790,7 @@
         <v>45853</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>44700</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48936,7 +48936,7 @@
         <v>44635</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>44743</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>45930</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45930</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45930</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45933</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45933</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45936</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45935</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45257</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45330</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45937</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45757</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45937</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45621</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>44769</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>44763</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>44833</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45944</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>45947</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45947</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45947</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45947</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>45951</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>45737</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45401</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>46150</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45111</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45952</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51108,7 +51108,7 @@
         <v>45749</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>46150</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>45952</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45952</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44704</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45957</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>44778</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45450</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45085</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>45625</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45956</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45954</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>46150</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>46150</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45960</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>46150</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52369,7 +52369,7 @@
         <v>45817</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>44993</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>44925</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45721</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>44777</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45640</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45533</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>44621</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         <v>45273</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>45967</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>45631</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45490</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>44470</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>44953</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45175</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>45971</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45973</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>44992</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45469</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>44777</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>44704</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>45456</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45104</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>44824</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>45644</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>46155</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45985</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>45982</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>45128</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>45322</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54652,7 +54652,7 @@
         <v>45993</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45992</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45993</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45075</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45075</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45075</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45075</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45993</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45092</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>44546</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45947</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45610</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45411</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45886</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45239</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
         <v>45916</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>45817</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45994</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46111</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>45414</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45994</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>45994</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>45996</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45999</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>46167</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>46000</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>44643</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46001</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>45456</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>45020</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46000</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57003,7 +57003,7 @@
         <v>46002</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>46002</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>44882</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45075</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         <v>45075</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45075</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>45075</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45771</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>44596</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>44596</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>45208</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57811,7 +57811,7 @@
         <v>45552</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>45847</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>46008</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>46009</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>46008</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45183</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>45293</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58337,7 +58337,7 @@
         <v>45957</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>45755</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>44952</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>44790</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>44879</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45293</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>45293</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58853,7 +58853,7 @@
         <v>44775</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58926,7 +58926,7 @@
         <v>45956</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>44490</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>45586</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>44648</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45740</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>45740</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>45085</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>46029</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>44953</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45617</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>46029</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>46029</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>46030</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         <v>45065</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>45068</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60026,7 +60026,7 @@
         <v>44644</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60099,7 +60099,7 @@
         <v>46034</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>46034</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60250,7 +60250,7 @@
         <v>44746</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45139</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60396,7 +60396,7 @@
         <v>45218</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60469,7 +60469,7 @@
         <v>46036</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>46036</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60615,7 +60615,7 @@
         <v>45414</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>44599</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60761,7 +60761,7 @@
         <v>45412</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>46174</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60907,7 +60907,7 @@
         <v>45205</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60980,7 +60980,7 @@
         <v>45147</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>45191</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46042</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>45084</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>45442</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>46043</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>44525</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61501,7 +61501,7 @@
         <v>44540</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>44556</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45845</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>46047</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45468</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61866,7 +61866,7 @@
         <v>45468</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>46049</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>45139</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>46049</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>46049</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>46049</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>45890</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62377,7 +62377,7 @@
         <v>46178</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62450,7 +62450,7 @@
         <v>46052</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>44525</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>45463</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>45636</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62747,7 +62747,7 @@
         <v>46056</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>45146</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46057</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62981,7 +62981,7 @@
         <v>46057</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>44698</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>45468</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         <v>46057</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>46178</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>46058</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>46059</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>46177</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>46177</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63658,7 +63658,7 @@
         <v>44691</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63731,7 +63731,7 @@
         <v>46063</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63804,7 +63804,7 @@
         <v>46062</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63882,7 +63882,7 @@
         <v>46063</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63955,7 +63955,7 @@
         <v>46061</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         <v>46178</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64101,7 +64101,7 @@
         <v>45356</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64174,7 +64174,7 @@
         <v>44816</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>46065</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>46065</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>46065</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64466,7 +64466,7 @@
         <v>45107</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45075</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         <v>45075</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64685,7 +64685,7 @@
         <v>46069</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64763,7 +64763,7 @@
         <v>46069</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         <v>46069</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64919,7 +64919,7 @@
         <v>46181</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>46182</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65065,7 +65065,7 @@
         <v>46072</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65138,7 +65138,7 @@
         <v>46181</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65216,7 +65216,7 @@
         <v>46077</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>46183</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65367,7 +65367,7 @@
         <v>46183</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>46077</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65518,7 +65518,7 @@
         <v>46077</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65596,7 +65596,7 @@
         <v>44764</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65669,7 +65669,7 @@
         <v>46183</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65747,7 +65747,7 @@
         <v>46077</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65825,7 +65825,7 @@
         <v>45238</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65898,7 +65898,7 @@
         <v>45261</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65971,7 +65971,7 @@
         <v>45524</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66044,7 +66044,7 @@
         <v>45245</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66117,7 +66117,7 @@
         <v>45454</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66190,7 +66190,7 @@
         <v>46084</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>46188</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66336,7 +66336,7 @@
         <v>44470</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46188</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66482,7 +66482,7 @@
         <v>46188</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66555,7 +66555,7 @@
         <v>45231</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>44866</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66701,7 +66701,7 @@
         <v>45082</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66774,7 +66774,7 @@
         <v>45082</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66847,7 +66847,7 @@
         <v>46189</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66920,7 +66920,7 @@
         <v>45260</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66993,7 +66993,7 @@
         <v>45260</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67066,7 +67066,7 @@
         <v>45617</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67139,7 +67139,7 @@
         <v>46094</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67217,7 +67217,7 @@
         <v>45063</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67290,7 +67290,7 @@
         <v>45721</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67363,7 +67363,7 @@
         <v>46093</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67436,7 +67436,7 @@
         <v>46094</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67514,7 +67514,7 @@
         <v>46094</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67592,7 +67592,7 @@
         <v>45055</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67665,7 +67665,7 @@
         <v>45614</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67738,7 +67738,7 @@
         <v>46077</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67811,7 +67811,7 @@
         <v>44714</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67884,7 +67884,7 @@
         <v>45687</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67962,7 +67962,7 @@
         <v>46191</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68035,7 +68035,7 @@
         <v>46191</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68108,7 +68108,7 @@
         <v>46191</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68181,7 +68181,7 @@
         <v>45225</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68254,7 +68254,7 @@
         <v>46100</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68327,7 +68327,7 @@
         <v>46100</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68400,7 +68400,7 @@
         <v>46195</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68473,7 +68473,7 @@
         <v>45253</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68546,7 +68546,7 @@
         <v>44851</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>45042</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68692,7 +68692,7 @@
         <v>44585</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>45469</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68843,7 +68843,7 @@
         <v>45385</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68916,7 +68916,7 @@
         <v>45202</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68989,7 +68989,7 @@
         <v>45075</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69062,7 +69062,7 @@
         <v>44743</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>46197</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69213,7 +69213,7 @@
         <v>46197</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69286,7 +69286,7 @@
         <v>45054</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69359,7 +69359,7 @@
         <v>45054</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69432,7 +69432,7 @@
         <v>44925</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69505,7 +69505,7 @@
         <v>44760</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69578,7 +69578,7 @@
         <v>46197</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69651,7 +69651,7 @@
         <v>45644</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69724,7 +69724,7 @@
         <v>44621</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>46113</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>45183</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69943,7 +69943,7 @@
         <v>45089</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70016,7 +70016,7 @@
         <v>44719</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70089,7 +70089,7 @@
         <v>44698</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70162,7 +70162,7 @@
         <v>46119</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>45957</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70313,7 +70313,7 @@
         <v>46119</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70391,7 +70391,7 @@
         <v>45519</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70464,7 +70464,7 @@
         <v>46119</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70537,7 +70537,7 @@
         <v>45170</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70610,7 +70610,7 @@
         <v>46119</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70688,7 +70688,7 @@
         <v>44549</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70761,7 +70761,7 @@
         <v>45601</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70834,7 +70834,7 @@
         <v>44516</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70912,7 +70912,7 @@
         <v>44516</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70990,7 +70990,7 @@
         <v>45448</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71063,7 +71063,7 @@
         <v>44782</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71136,7 +71136,7 @@
         <v>44753</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71209,7 +71209,7 @@
         <v>46107</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71282,7 +71282,7 @@
         <v>44902</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71355,7 +71355,7 @@
         <v>44795</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71428,7 +71428,7 @@
         <v>45518</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71501,7 +71501,7 @@
         <v>46202</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71574,7 +71574,7 @@
         <v>46133</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71647,7 +71647,7 @@
         <v>46132</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71720,7 +71720,7 @@
         <v>46134</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71793,7 +71793,7 @@
         <v>45686</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71866,7 +71866,7 @@
         <v>45522</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71939,7 +71939,7 @@
         <v>45357</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72012,7 +72012,7 @@
         <v>45147</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72085,7 +72085,7 @@
         <v>44923</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72158,7 +72158,7 @@
         <v>46135</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72231,7 +72231,7 @@
         <v>45212</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72304,7 +72304,7 @@
         <v>46119</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72382,7 +72382,7 @@
         <v>45119</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72455,7 +72455,7 @@
         <v>45668</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72528,7 +72528,7 @@
         <v>44682</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72601,7 +72601,7 @@
         <v>46247</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72674,7 +72674,7 @@
         <v>46247</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72747,7 +72747,7 @@
         <v>46247</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72820,7 +72820,7 @@
         <v>44815</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72893,7 +72893,7 @@
         <v>44986</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72966,7 +72966,7 @@
         <v>46247</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73039,7 +73039,7 @@
         <v>46203</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73112,7 +73112,7 @@
         <v>45089</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73185,7 +73185,7 @@
         <v>45898</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73258,7 +73258,7 @@
         <v>45971</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73331,7 +73331,7 @@
         <v>45587</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73404,7 +73404,7 @@
         <v>45310</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73477,7 +73477,7 @@
         <v>44866</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73550,7 +73550,7 @@
         <v>44868</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73623,7 +73623,7 @@
         <v>45853</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73696,7 +73696,7 @@
         <v>44495</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>44963</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73842,7 +73842,7 @@
         <v>46203</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73915,7 +73915,7 @@
         <v>46204</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73988,7 +73988,7 @@
         <v>46246</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74061,7 +74061,7 @@
         <v>44816</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74134,7 +74134,7 @@
         <v>46204</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74207,7 +74207,7 @@
         <v>45693</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74280,7 +74280,7 @@
         <v>46206</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74353,7 +74353,7 @@
         <v>45558</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>44956</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74499,7 +74499,7 @@
         <v>44956</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74572,7 +74572,7 @@
         <v>46207</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74645,7 +74645,7 @@
         <v>44684</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74718,7 +74718,7 @@
         <v>45253</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74791,7 +74791,7 @@
         <v>44980</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74864,7 +74864,7 @@
         <v>46207</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74937,7 +74937,7 @@
         <v>45174</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75015,7 +75015,7 @@
         <v>45232</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75088,7 +75088,7 @@
         <v>46209</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75161,7 +75161,7 @@
         <v>45075</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75234,7 +75234,7 @@
         <v>45468</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75307,7 +75307,7 @@
         <v>46255</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75380,7 +75380,7 @@
         <v>44938</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75453,7 +75453,7 @@
         <v>46254</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75526,7 +75526,7 @@
         <v>46254</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75604,7 +75604,7 @@
         <v>46254</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75682,7 +75682,7 @@
         <v>44806</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75755,7 +75755,7 @@
         <v>44934</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75828,7 +75828,7 @@
         <v>46216</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75901,7 +75901,7 @@
         <v>46258</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75974,7 +75974,7 @@
         <v>46259</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76047,7 +76047,7 @@
         <v>44799</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76120,7 +76120,7 @@
         <v>46258</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76193,7 +76193,7 @@
         <v>45063</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76266,7 +76266,7 @@
         <v>45075</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76339,7 +76339,7 @@
         <v>46259</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76412,7 +76412,7 @@
         <v>45245</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76485,7 +76485,7 @@
         <v>45245</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76558,7 +76558,7 @@
         <v>46258</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76631,7 +76631,7 @@
         <v>46260</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76709,7 +76709,7 @@
         <v>46260</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76787,7 +76787,7 @@
         <v>46261</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76860,7 +76860,7 @@
         <v>46218</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76933,7 +76933,7 @@
         <v>44750</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77006,7 +77006,7 @@
         <v>44750</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77079,7 +77079,7 @@
         <v>46261</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77152,7 +77152,7 @@
         <v>45075</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77225,7 +77225,7 @@
         <v>46260</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77303,7 +77303,7 @@
         <v>46261</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77376,7 +77376,7 @@
         <v>45338</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77449,7 +77449,7 @@
         <v>45254</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77522,7 +77522,7 @@
         <v>46220</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77595,7 +77595,7 @@
         <v>45775</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77668,7 +77668,7 @@
         <v>44693</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77741,7 +77741,7 @@
         <v>44769</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77814,7 +77814,7 @@
         <v>46266</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77887,7 +77887,7 @@
         <v>46266</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77960,7 +77960,7 @@
         <v>46265</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -78033,7 +78033,7 @@
         <v>45113</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -78106,7 +78106,7 @@
         <v>46266</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78179,7 +78179,7 @@
         <v>45328</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78252,7 +78252,7 @@
         <v>46266</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78325,7 +78325,7 @@
         <v>45348</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78403,7 +78403,7 @@
         <v>45728</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78476,7 +78476,7 @@
         <v>46268</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78549,7 +78549,7 @@
         <v>46268</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78622,7 +78622,7 @@
         <v>44490</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78695,7 +78695,7 @@
         <v>46225</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78768,7 +78768,7 @@
         <v>46272</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78841,7 +78841,7 @@
         <v>45316</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78914,7 +78914,7 @@
         <v>45253</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78987,7 +78987,7 @@
         <v>45190</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -79060,7 +79060,7 @@
         <v>45783</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -79133,7 +79133,7 @@
         <v>46261</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79206,7 +79206,7 @@
         <v>46261</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79279,7 +79279,7 @@
         <v>45783</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79352,7 +79352,7 @@
         <v>46274</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79430,7 +79430,7 @@
         <v>45799</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79503,7 +79503,7 @@
         <v>45408</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79576,7 +79576,7 @@
         <v>45635</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79649,7 +79649,7 @@
         <v>44578</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79722,7 +79722,7 @@
         <v>45735</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79795,7 +79795,7 @@
         <v>45709</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79873,7 +79873,7 @@
         <v>45537</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79946,7 +79946,7 @@
         <v>45187</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -80019,7 +80019,7 @@
         <v>45385</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -80092,7 +80092,7 @@
         <v>45572</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -80165,7 +80165,7 @@
         <v>45549</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80238,7 +80238,7 @@
         <v>45579</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80311,7 +80311,7 @@
         <v>45352</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80384,7 +80384,7 @@
         <v>46237</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80457,7 +80457,7 @@
         <v>46238</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80530,7 +80530,7 @@
         <v>45414</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80603,7 +80603,7 @@
         <v>46254</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80676,7 +80676,7 @@
         <v>45272</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80749,7 +80749,7 @@
         <v>45272</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80822,7 +80822,7 @@
         <v>46239</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80895,7 +80895,7 @@
         <v>45475</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80968,7 +80968,7 @@
         <v>45518</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -81041,7 +81041,7 @@
         <v>46241</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -81114,7 +81114,7 @@
         <v>44708</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81187,7 +81187,7 @@
         <v>45436</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81260,7 +81260,7 @@
         <v>45385</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81333,7 +81333,7 @@
         <v>45713</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81411,7 +81411,7 @@
         <v>45729</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81484,7 +81484,7 @@
         <v>46239</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81557,7 +81557,7 @@
         <v>45798</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81630,7 +81630,7 @@
         <v>45798</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81703,7 +81703,7 @@
         <v>46283</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81776,7 +81776,7 @@
         <v>45798</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81849,7 +81849,7 @@
         <v>45586</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81922,7 +81922,7 @@
         <v>45803</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81995,7 +81995,7 @@
         <v>45800</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -82068,7 +82068,7 @@
         <v>44813</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -82141,7 +82141,7 @@
         <v>45224</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82214,7 +82214,7 @@
         <v>45810</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82287,7 +82287,7 @@
         <v>45810</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82360,7 +82360,7 @@
         <v>45790</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82433,7 +82433,7 @@
         <v>45810</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82506,7 +82506,7 @@
         <v>45813</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82579,7 +82579,7 @@
         <v>45817</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82657,7 +82657,7 @@
         <v>45747</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82730,7 +82730,7 @@
         <v>45376</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82808,7 +82808,7 @@
         <v>45824</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82886,7 +82886,7 @@
         <v>45831</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82959,7 +82959,7 @@
         <v>45834</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -83032,7 +83032,7 @@
         <v>45834</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -83105,7 +83105,7 @@
         <v>45835</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83178,7 +83178,7 @@
         <v>45834</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83251,7 +83251,7 @@
         <v>45839</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83324,7 +83324,7 @@
         <v>45840</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83397,7 +83397,7 @@
         <v>45841</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83470,7 +83470,7 @@
         <v>45152</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83543,7 +83543,7 @@
         <v>45581</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83616,7 +83616,7 @@
         <v>45852</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83689,7 +83689,7 @@
         <v>45855</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83767,7 +83767,7 @@
         <v>45855</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83845,7 +83845,7 @@
         <v>45525</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83918,7 +83918,7 @@
         <v>45776</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83991,7 +83991,7 @@
         <v>45446</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -84064,7 +84064,7 @@
         <v>45880</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -84142,7 +84142,7 @@
         <v>45776</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84215,7 +84215,7 @@
         <v>45386</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84288,7 +84288,7 @@
         <v>45882</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84361,7 +84361,7 @@
         <v>43943</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84434,7 +84434,7 @@
         <v>43969</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84507,7 +84507,7 @@
         <v>44959</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84580,7 +84580,7 @@
         <v>44099</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84653,7 +84653,7 @@
         <v>44854</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84726,7 +84726,7 @@
         <v>44599</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84799,7 +84799,7 @@
         <v>45260</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84872,7 +84872,7 @@
         <v>44638</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84950,7 +84950,7 @@
         <v>45366</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -85023,7 +85023,7 @@
         <v>44652</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -85096,7 +85096,7 @@
         <v>45537</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -85169,7 +85169,7 @@
         <v>44627</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85242,7 +85242,7 @@
         <v>44497</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85315,7 +85315,7 @@
         <v>44558</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85388,7 +85388,7 @@
         <v>44497</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85461,7 +85461,7 @@
         <v>44971</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85534,7 +85534,7 @@
         <v>44574</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85607,7 +85607,7 @@
         <v>44690</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85680,7 +85680,7 @@
         <v>45569</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -85753,7 +85753,7 @@
         <v>45188</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -85826,7 +85826,7 @@
         <v>44973</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -85899,7 +85899,7 @@
         <v>45183</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -85972,7 +85972,7 @@
         <v>44973</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -86045,7 +86045,7 @@
         <v>45817</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -86118,7 +86118,7 @@
         <v>45807</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -86191,7 +86191,7 @@
         <v>46062</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -86264,7 +86264,7 @@
         <v>46062</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -86337,7 +86337,7 @@
         <v>46188</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -86410,7 +86410,7 @@
         <v>44614</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>12</v>
@@ -1146,13 +1146,13 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1177,6 +1177,7 @@
 Fällmossa
 Guldlockmossa
 Hasselticka
+Igelkottsröksvamp
 Liten baronmossa
 Lönnlav
 Mörk husmossa
@@ -1250,7 +1251,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1400,7 +1401,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1544,7 +1545,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1688,7 +1689,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1831,7 +1832,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1973,7 +1974,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2110,7 +2111,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2245,7 +2246,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2385,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2515,7 +2516,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2649,7 +2650,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2782,7 +2783,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2915,7 +2916,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2961,10 +2962,10 @@
         <v>25</v>
       </c>
       <c r="T18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3053,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3187,7 +3188,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3318,7 +3319,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3448,7 +3449,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3574,7 +3575,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3703,7 +3704,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3836,7 +3837,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3963,7 +3964,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4095,7 +4096,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4225,7 +4226,7 @@
         <v>46103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4347,7 +4348,7 @@
         <v>45847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4470,7 +4471,7 @@
         <v>46029</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4592,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4714,7 +4715,7 @@
         <v>44482</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4832,7 +4833,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4948,7 +4949,7 @@
         <v>45418</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5067,7 +5068,7 @@
         <v>45800</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5190,7 +5191,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5309,7 +5310,7 @@
         <v>44949</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5424,7 +5425,7 @@
         <v>44880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5544,7 +5545,7 @@
         <v>44571</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5658,7 +5659,7 @@
         <v>45436</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5780,7 +5781,7 @@
         <v>45190</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5902,7 +5903,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6024,7 +6025,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6147,7 +6148,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6268,7 +6269,7 @@
         <v>44467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6381,7 +6382,7 @@
         <v>45586</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6498,7 +6499,7 @@
         <v>43969</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6615,7 +6616,7 @@
         <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6727,7 +6728,7 @@
         <v>44858</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6839,7 +6840,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6951,7 +6952,7 @@
         <v>45684</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7063,7 +7064,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7174,7 +7175,7 @@
         <v>45446</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7289,7 +7290,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7409,7 +7410,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7520,7 +7521,7 @@
         <v>44949</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7631,7 +7632,7 @@
         <v>45847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7742,7 +7743,7 @@
         <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7857,7 +7858,7 @@
         <v>46107</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7976,7 +7977,7 @@
         <v>45960</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8096,7 +8097,7 @@
         <v>44544</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8207,7 +8208,7 @@
         <v>44650</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8318,7 +8319,7 @@
         <v>44706</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8429,7 +8430,7 @@
         <v>45933</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8539,7 +8540,7 @@
         <v>45847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8653,7 +8654,7 @@
         <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8763,7 +8764,7 @@
         <v>44489</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8872,7 +8873,7 @@
         <v>44711</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8985,7 +8986,7 @@
         <v>45104</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9103,7 +9104,7 @@
         <v>45485</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9212,7 +9213,7 @@
         <v>45581</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9325,7 +9326,7 @@
         <v>45810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9434,7 +9435,7 @@
         <v>46204</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9547,7 +9548,7 @@
         <v>45664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9656,7 +9657,7 @@
         <v>46247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9765,7 +9766,7 @@
         <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9883,7 +9884,7 @@
         <v>44956</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9996,7 +9997,7 @@
         <v>45783</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10105,7 +10106,7 @@
         <v>44972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10223,7 +10224,7 @@
         <v>45071</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10332,7 +10333,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10441,7 +10442,7 @@
         <v>44749</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10549,7 +10550,7 @@
         <v>44855</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10657,7 +10658,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10765,7 +10766,7 @@
         <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10873,7 +10874,7 @@
         <v>45616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10981,7 +10982,7 @@
         <v>44778</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11093,7 +11094,7 @@
         <v>44683</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11205,7 +11206,7 @@
         <v>45821</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11322,7 +11323,7 @@
         <v>45082</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11439,7 +11440,7 @@
         <v>44545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11547,7 +11548,7 @@
         <v>44839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11659,7 +11660,7 @@
         <v>44743</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11772,7 +11773,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11880,7 +11881,7 @@
         <v>44679</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11988,7 +11989,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12101,7 +12102,7 @@
         <v>44530</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12209,7 +12210,7 @@
         <v>44843</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12316,7 +12317,7 @@
         <v>44763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12432,7 +12433,7 @@
         <v>46027</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12544,7 +12545,7 @@
         <v>45169</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12660,7 +12661,7 @@
         <v>44985</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12767,7 +12768,7 @@
         <v>44698</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12878,7 +12879,7 @@
         <v>45957</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12994,7 +12995,7 @@
         <v>45754</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13101,7 +13102,7 @@
         <v>44695</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13208,7 +13209,7 @@
         <v>46163</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13315,7 +13316,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13422,7 +13423,7 @@
         <v>46183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13529,7 +13530,7 @@
         <v>46183</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13636,7 +13637,7 @@
         <v>44866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13743,7 +13744,7 @@
         <v>45741</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13850,7 +13851,7 @@
         <v>44771</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13966,7 +13967,7 @@
         <v>44743</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14078,7 +14079,7 @@
         <v>44629</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14190,7 +14191,7 @@
         <v>45642</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14297,7 +14298,7 @@
         <v>44594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14403,7 +14404,7 @@
         <v>44880</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14509,7 +14510,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14619,7 +14620,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14725,7 +14726,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14831,7 +14832,7 @@
         <v>45383</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14941,7 +14942,7 @@
         <v>44956</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15047,7 +15048,7 @@
         <v>44474</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15153,7 +15154,7 @@
         <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15259,7 +15260,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15369,7 +15370,7 @@
         <v>45803</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15484,7 +15485,7 @@
         <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15595,7 +15596,7 @@
         <v>45945</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15701,7 +15702,7 @@
         <v>45070</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15807,7 +15808,7 @@
         <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15913,7 +15914,7 @@
         <v>46150</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16019,7 +16020,7 @@
         <v>46150</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16125,7 +16126,7 @@
         <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16231,7 +16232,7 @@
         <v>46198</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16341,7 +16342,7 @@
         <v>45069</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16451,7 +16452,7 @@
         <v>45226</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16557,7 +16558,7 @@
         <v>44863</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16667,7 +16668,7 @@
         <v>46288</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16773,7 +16774,7 @@
         <v>46247</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16879,7 +16880,7 @@
         <v>44868</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16985,7 +16986,7 @@
         <v>45118</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17096,7 +17097,7 @@
         <v>44678</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17202,7 +17203,7 @@
         <v>44896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17312,7 +17313,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17418,7 +17419,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17524,7 +17525,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17639,7 +17640,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17744,7 +17745,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17853,7 +17854,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17958,7 +17959,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18067,7 +18068,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18172,7 +18173,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18281,7 +18282,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18390,7 +18391,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18495,7 +18496,7 @@
         <v>45730</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18600,7 +18601,7 @@
         <v>44778</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18705,7 +18706,7 @@
         <v>45223</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18810,7 +18811,7 @@
         <v>45794</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18915,7 +18916,7 @@
         <v>45457</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19025,7 +19026,7 @@
         <v>44869</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19130,7 +19131,7 @@
         <v>45897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19235,7 +19236,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19340,7 +19341,7 @@
         <v>45532</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19449,7 +19450,7 @@
         <v>45549</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19554,7 +19555,7 @@
         <v>44617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19663,7 +19664,7 @@
         <v>44867</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19768,7 +19769,7 @@
         <v>46093</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19873,7 +19874,7 @@
         <v>44963</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19978,7 +19979,7 @@
         <v>45112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20083,7 +20084,7 @@
         <v>44489</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20193,7 +20194,7 @@
         <v>45623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20303,7 +20304,7 @@
         <v>45957</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20413,7 +20414,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20523,7 +20524,7 @@
         <v>44797</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20628,7 +20629,7 @@
         <v>44903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20733,7 +20734,7 @@
         <v>46133</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20838,7 +20839,7 @@
         <v>45987</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20943,7 +20944,7 @@
         <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21048,7 +21049,7 @@
         <v>44965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21153,7 +21154,7 @@
         <v>45450</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21263,7 +21264,7 @@
         <v>45840</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21368,7 +21369,7 @@
         <v>46010</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21473,7 +21474,7 @@
         <v>45474</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21578,7 +21579,7 @@
         <v>45826</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21688,7 +21689,7 @@
         <v>46062</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21793,7 +21794,7 @@
         <v>44955</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21898,7 +21899,7 @@
         <v>45764</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22003,7 +22004,7 @@
         <v>45081</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22112,7 +22113,7 @@
         <v>44760</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22217,7 +22218,7 @@
         <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22322,7 +22323,7 @@
         <v>44483</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22427,7 +22428,7 @@
         <v>45147</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22532,7 +22533,7 @@
         <v>45147</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22637,7 +22638,7 @@
         <v>45855</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22747,7 +22748,7 @@
         <v>44705</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22852,7 +22853,7 @@
         <v>45418</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22957,7 +22958,7 @@
         <v>45260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23062,7 +23063,7 @@
         <v>45177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23167,7 +23168,7 @@
         <v>45708</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23281,7 +23282,7 @@
         <v>45113</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23386,7 +23387,7 @@
         <v>46204</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23500,7 +23501,7 @@
         <v>44649</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23605,7 +23606,7 @@
         <v>45687</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23715,7 +23716,7 @@
         <v>45608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23820,7 +23821,7 @@
         <v>45687</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23930,7 +23931,7 @@
         <v>45960</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24039,7 +24040,7 @@
         <v>45219</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24144,7 +24145,7 @@
         <v>44813</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24249,7 +24250,7 @@
         <v>44704</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24354,7 +24355,7 @@
         <v>45293</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24468,7 +24469,7 @@
         <v>45468</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24573,7 +24574,7 @@
         <v>44747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24678,7 +24679,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24783,7 +24784,7 @@
         <v>44813</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24888,7 +24889,7 @@
         <v>45007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24993,7 +24994,7 @@
         <v>45183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25098,7 +25099,7 @@
         <v>45205</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25203,7 +25204,7 @@
         <v>44637</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25308,7 +25309,7 @@
         <v>45473</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25417,7 +25418,7 @@
         <v>44620</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25522,7 +25523,7 @@
         <v>45460</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25627,7 +25628,7 @@
         <v>44639</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25732,7 +25733,7 @@
         <v>44917</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25837,7 +25838,7 @@
         <v>44518</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25942,7 +25943,7 @@
         <v>45572</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26047,7 +26048,7 @@
         <v>45994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26157,7 +26158,7 @@
         <v>44642</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26230,7 +26231,7 @@
         <v>44540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26303,7 +26304,7 @@
         <v>44650</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26376,7 +26377,7 @@
         <v>44833</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26454,7 +26455,7 @@
         <v>44777</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26527,7 +26528,7 @@
         <v>44728</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26605,7 +26606,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26678,7 +26679,7 @@
         <v>44552</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26756,7 +26757,7 @@
         <v>44634</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26829,7 +26830,7 @@
         <v>44581</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26902,7 +26903,7 @@
         <v>44560</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26975,7 +26976,7 @@
         <v>44771</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27048,7 +27049,7 @@
         <v>44477</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27121,7 +27122,7 @@
         <v>44524</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27194,7 +27195,7 @@
         <v>44574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27267,7 +27268,7 @@
         <v>44516</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27340,7 +27341,7 @@
         <v>44834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27413,7 +27414,7 @@
         <v>44496</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27486,7 +27487,7 @@
         <v>44690</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27559,7 +27560,7 @@
         <v>44682</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27632,7 +27633,7 @@
         <v>44626</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27705,7 +27706,7 @@
         <v>44708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27778,7 +27779,7 @@
         <v>44642</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27851,7 +27852,7 @@
         <v>44776</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27924,7 +27925,7 @@
         <v>44746</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27997,7 +27998,7 @@
         <v>44845</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28070,7 +28071,7 @@
         <v>44543</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28143,7 +28144,7 @@
         <v>44543</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28216,7 +28217,7 @@
         <v>44495</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28289,7 +28290,7 @@
         <v>44749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28362,7 +28363,7 @@
         <v>44882</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28435,7 +28436,7 @@
         <v>44545</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28508,7 +28509,7 @@
         <v>44722</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28581,7 +28582,7 @@
         <v>44742</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28654,7 +28655,7 @@
         <v>44756</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28727,7 +28728,7 @@
         <v>44806</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28800,7 +28801,7 @@
         <v>44511</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28873,7 +28874,7 @@
         <v>44510</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28946,7 +28947,7 @@
         <v>44867</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29019,7 +29020,7 @@
         <v>44511</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29092,7 +29093,7 @@
         <v>44683</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29165,7 +29166,7 @@
         <v>44539</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29238,7 +29239,7 @@
         <v>44496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29311,7 +29312,7 @@
         <v>44516</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29384,7 +29385,7 @@
         <v>44712</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29457,7 +29458,7 @@
         <v>44769</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29530,7 +29531,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29603,7 +29604,7 @@
         <v>44543</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29676,7 +29677,7 @@
         <v>44545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29749,7 +29750,7 @@
         <v>44545</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29822,7 +29823,7 @@
         <v>44621</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29895,7 +29896,7 @@
         <v>44496</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29968,7 +29969,7 @@
         <v>44637</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30041,7 +30042,7 @@
         <v>44735</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30114,7 +30115,7 @@
         <v>44763</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30187,7 +30188,7 @@
         <v>44735</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30260,7 +30261,7 @@
         <v>44524</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30333,7 +30334,7 @@
         <v>44575</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30406,7 +30407,7 @@
         <v>44572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30479,7 +30480,7 @@
         <v>44650</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30552,7 +30553,7 @@
         <v>44725</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30625,7 +30626,7 @@
         <v>44580</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30698,7 +30699,7 @@
         <v>44777</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30771,7 +30772,7 @@
         <v>44637</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30844,7 +30845,7 @@
         <v>44655</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30917,7 +30918,7 @@
         <v>44665</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30990,7 +30991,7 @@
         <v>44595</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31063,7 +31064,7 @@
         <v>44744</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31136,7 +31137,7 @@
         <v>44826</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31209,7 +31210,7 @@
         <v>44845</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31282,7 +31283,7 @@
         <v>44526</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31355,7 +31356,7 @@
         <v>44642</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31428,7 +31429,7 @@
         <v>44637</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31501,7 +31502,7 @@
         <v>44607</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31574,7 +31575,7 @@
         <v>44698</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31647,7 +31648,7 @@
         <v>44609</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31720,7 +31721,7 @@
         <v>44760</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31793,7 +31794,7 @@
         <v>44817</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31866,7 +31867,7 @@
         <v>44477</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31944,7 +31945,7 @@
         <v>44584</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32017,7 +32018,7 @@
         <v>44678</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32090,7 +32091,7 @@
         <v>44682</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32163,7 +32164,7 @@
         <v>44682</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32236,7 +32237,7 @@
         <v>44623</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32309,7 +32310,7 @@
         <v>44665</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32382,7 +32383,7 @@
         <v>44665</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32455,7 +32456,7 @@
         <v>44533</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32528,7 +32529,7 @@
         <v>44543</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32601,7 +32602,7 @@
         <v>44704</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32674,7 +32675,7 @@
         <v>44682</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32747,7 +32748,7 @@
         <v>44725</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32820,7 +32821,7 @@
         <v>44523</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32893,7 +32894,7 @@
         <v>44815</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32966,7 +32967,7 @@
         <v>44595</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33039,7 +33040,7 @@
         <v>44495</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33112,7 +33113,7 @@
         <v>45621</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33190,7 +33191,7 @@
         <v>45075</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33263,7 +33264,7 @@
         <v>45075</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33336,7 +33337,7 @@
         <v>44764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33409,7 +33410,7 @@
         <v>45051</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33482,7 +33483,7 @@
         <v>45273</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33555,7 +33556,7 @@
         <v>45749</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33633,7 +33634,7 @@
         <v>45362</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33706,7 +33707,7 @@
         <v>44743</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33779,7 +33780,7 @@
         <v>45203</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33852,7 +33853,7 @@
         <v>44824</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33925,7 +33926,7 @@
         <v>45625</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33998,7 +33999,7 @@
         <v>45208</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34071,7 +34072,7 @@
         <v>44879</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34144,7 +34145,7 @@
         <v>44833</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34217,7 +34218,7 @@
         <v>45218</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34290,7 +34291,7 @@
         <v>45330</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34363,7 +34364,7 @@
         <v>44840</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34436,7 +34437,7 @@
         <v>45433</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34509,7 +34510,7 @@
         <v>45435</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34582,7 +34583,7 @@
         <v>45239</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34655,7 +34656,7 @@
         <v>44895</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34728,7 +34729,7 @@
         <v>45450</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34806,7 +34807,7 @@
         <v>45450</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34884,7 +34885,7 @@
         <v>44845</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34957,7 +34958,7 @@
         <v>45755</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35030,7 +35031,7 @@
         <v>45558</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35103,7 +35104,7 @@
         <v>45454</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35176,7 +35177,7 @@
         <v>45202</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35254,7 +35255,7 @@
         <v>45075</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35332,7 +35333,7 @@
         <v>45075</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35405,7 +35406,7 @@
         <v>45075</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35478,7 +35479,7 @@
         <v>44866</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35551,7 +35552,7 @@
         <v>45075</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35624,7 +35625,7 @@
         <v>44809</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35697,7 +35698,7 @@
         <v>44962</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35770,7 +35771,7 @@
         <v>45257</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35843,7 +35844,7 @@
         <v>45089</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35916,7 +35917,7 @@
         <v>45356</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35989,7 +35990,7 @@
         <v>45448</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36062,7 +36063,7 @@
         <v>45119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36135,7 +36136,7 @@
         <v>45463</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36208,7 +36209,7 @@
         <v>45063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36281,7 +36282,7 @@
         <v>44956</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36354,7 +36355,7 @@
         <v>45272</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36427,7 +36428,7 @@
         <v>45272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36500,7 +36501,7 @@
         <v>44472</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36573,7 +36574,7 @@
         <v>45468</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36646,7 +36647,7 @@
         <v>45385</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36719,7 +36720,7 @@
         <v>45729</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36792,7 +36793,7 @@
         <v>44470</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36865,7 +36866,7 @@
         <v>44834</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36938,7 +36939,7 @@
         <v>45713</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37016,7 +37017,7 @@
         <v>45436</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37089,7 +37090,7 @@
         <v>45518</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37162,7 +37163,7 @@
         <v>44516</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37240,7 +37241,7 @@
         <v>45475</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37313,7 +37314,7 @@
         <v>46029</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37386,7 +37387,7 @@
         <v>45524</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37459,7 +37460,7 @@
         <v>45341</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37532,7 +37533,7 @@
         <v>44708</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37605,7 +37606,7 @@
         <v>45798</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37678,7 +37679,7 @@
         <v>44952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37756,7 +37757,7 @@
         <v>45798</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37829,7 +37830,7 @@
         <v>45798</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37902,7 +37903,7 @@
         <v>45469</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37975,7 +37976,7 @@
         <v>45469</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38048,7 +38049,7 @@
         <v>46030</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38121,7 +38122,7 @@
         <v>46029</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38194,7 +38195,7 @@
         <v>46029</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38267,7 +38268,7 @@
         <v>46034</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38340,7 +38341,7 @@
         <v>46034</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38418,7 +38419,7 @@
         <v>45888</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38491,7 +38492,7 @@
         <v>46036</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38564,7 +38565,7 @@
         <v>46036</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38637,7 +38638,7 @@
         <v>45890</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38710,7 +38711,7 @@
         <v>45813</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38783,7 +38784,7 @@
         <v>45586</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38856,7 +38857,7 @@
         <v>44540</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38929,7 +38930,7 @@
         <v>45894</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39002,7 +39003,7 @@
         <v>45894</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39075,7 +39076,7 @@
         <v>45859</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39148,7 +39149,7 @@
         <v>45414</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39221,7 +39222,7 @@
         <v>45893</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39294,7 +39295,7 @@
         <v>45894</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39367,7 +39368,7 @@
         <v>45859</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39440,7 +39441,7 @@
         <v>45089</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39513,7 +39514,7 @@
         <v>45893</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39586,7 +39587,7 @@
         <v>45894</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39659,7 +39660,7 @@
         <v>46042</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39732,7 +39733,7 @@
         <v>45896</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39805,7 +39806,7 @@
         <v>44904</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39878,7 +39879,7 @@
         <v>45800</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39951,7 +39952,7 @@
         <v>45897</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40024,7 +40025,7 @@
         <v>44901</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40097,7 +40098,7 @@
         <v>45898</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40170,7 +40171,7 @@
         <v>45898</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40248,7 +40249,7 @@
         <v>45897</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40321,7 +40322,7 @@
         <v>45897</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40394,7 +40395,7 @@
         <v>46043</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40467,7 +40468,7 @@
         <v>45075</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40540,7 +40541,7 @@
         <v>45427</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40613,7 +40614,7 @@
         <v>46047</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40686,7 +40687,7 @@
         <v>45075</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40759,7 +40760,7 @@
         <v>45721</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40832,7 +40833,7 @@
         <v>46049</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40905,7 +40906,7 @@
         <v>45610</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40978,7 +40979,7 @@
         <v>46049</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41051,7 +41052,7 @@
         <v>46049</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41124,7 +41125,7 @@
         <v>46049</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41197,7 +41198,7 @@
         <v>45831</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41270,7 +41271,7 @@
         <v>44993</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41348,7 +41349,7 @@
         <v>45531</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41421,7 +41422,7 @@
         <v>45908</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41494,7 +41495,7 @@
         <v>45772</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41567,7 +41568,7 @@
         <v>46052</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41645,7 +41646,7 @@
         <v>44525</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41723,7 +41724,7 @@
         <v>45890</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41796,7 +41797,7 @@
         <v>45803</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41869,7 +41870,7 @@
         <v>45910</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41942,7 +41943,7 @@
         <v>46056</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42020,7 +42021,7 @@
         <v>45442</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42093,7 +42094,7 @@
         <v>45155</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42166,7 +42167,7 @@
         <v>46058</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42244,7 +42245,7 @@
         <v>45831</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42317,7 +42318,7 @@
         <v>46057</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42395,7 +42396,7 @@
         <v>46057</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42473,7 +42474,7 @@
         <v>46057</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42551,7 +42552,7 @@
         <v>44938</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42624,7 +42625,7 @@
         <v>46059</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42697,7 +42698,7 @@
         <v>45224</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42770,7 +42771,7 @@
         <v>46061</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42843,7 +42844,7 @@
         <v>46062</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42921,7 +42922,7 @@
         <v>45918</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42994,7 +42995,7 @@
         <v>46063</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43067,7 +43068,7 @@
         <v>46063</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43140,7 +43141,7 @@
         <v>45786</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43213,7 +43214,7 @@
         <v>46065</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43286,7 +43287,7 @@
         <v>46065</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43359,7 +43360,7 @@
         <v>44902</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43432,7 +43433,7 @@
         <v>46065</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43505,7 +43506,7 @@
         <v>46069</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43583,7 +43584,7 @@
         <v>44813</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43656,7 +43657,7 @@
         <v>46069</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43734,7 +43735,7 @@
         <v>46069</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43812,7 +43813,7 @@
         <v>45923</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43885,7 +43886,7 @@
         <v>45586</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43958,7 +43959,7 @@
         <v>45853</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44031,7 +44032,7 @@
         <v>45687</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44109,7 +44110,7 @@
         <v>46072</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44182,7 +44183,7 @@
         <v>46077</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44260,7 +44261,7 @@
         <v>44923</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44333,7 +44334,7 @@
         <v>46077</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44411,7 +44412,7 @@
         <v>45412</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44484,7 +44485,7 @@
         <v>46077</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44562,7 +44563,7 @@
         <v>46077</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44640,7 +44641,7 @@
         <v>44585</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44718,7 +44719,7 @@
         <v>45552</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44791,7 +44792,7 @@
         <v>44945</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44864,7 +44865,7 @@
         <v>44937</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44937,7 +44938,7 @@
         <v>45145</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45010,7 +45011,7 @@
         <v>45215</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45083,7 +45084,7 @@
         <v>45930</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45161,7 +45162,7 @@
         <v>45930</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45239,7 +45240,7 @@
         <v>45930</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45317,7 +45318,7 @@
         <v>45155</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45390,7 +45391,7 @@
         <v>45254</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45463,7 +45464,7 @@
         <v>45260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45536,7 +45537,7 @@
         <v>45260</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45609,7 +45610,7 @@
         <v>45790</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45682,7 +45683,7 @@
         <v>45810</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45755,7 +45756,7 @@
         <v>44714</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45828,7 +45829,7 @@
         <v>45810</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45901,7 +45902,7 @@
         <v>46084</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45974,7 +45975,7 @@
         <v>45936</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46047,7 +46048,7 @@
         <v>45935</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46120,7 +46121,7 @@
         <v>45933</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46193,7 +46194,7 @@
         <v>45933</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46266,7 +46267,7 @@
         <v>45205</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46339,7 +46340,7 @@
         <v>45937</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46412,7 +46413,7 @@
         <v>45937</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46485,7 +46486,7 @@
         <v>45701</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46558,7 +46559,7 @@
         <v>46093</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46631,7 +46632,7 @@
         <v>46094</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46709,7 +46710,7 @@
         <v>46094</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46787,7 +46788,7 @@
         <v>44611</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46860,7 +46861,7 @@
         <v>44986</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46933,7 +46934,7 @@
         <v>46094</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47011,7 +47012,7 @@
         <v>45810</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47084,7 +47085,7 @@
         <v>45944</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47157,7 +47158,7 @@
         <v>44775</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47230,7 +47231,7 @@
         <v>46100</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47303,7 +47304,7 @@
         <v>45223</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47376,7 +47377,7 @@
         <v>46100</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47449,7 +47450,7 @@
         <v>45947</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47527,7 +47528,7 @@
         <v>44693</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47600,7 +47601,7 @@
         <v>45947</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47678,7 +47679,7 @@
         <v>45947</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47756,7 +47757,7 @@
         <v>45947</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47834,7 +47835,7 @@
         <v>45952</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47907,7 +47908,7 @@
         <v>45952</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47980,7 +47981,7 @@
         <v>45952</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48053,7 +48054,7 @@
         <v>45951</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48131,7 +48132,7 @@
         <v>44867</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48204,7 +48205,7 @@
         <v>45075</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48277,7 +48278,7 @@
         <v>45348</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48355,7 +48356,7 @@
         <v>45957</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48433,7 +48434,7 @@
         <v>45954</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48506,7 +48507,7 @@
         <v>46113</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48579,7 +48580,7 @@
         <v>44803</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48652,7 +48653,7 @@
         <v>45956</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48725,7 +48726,7 @@
         <v>45957</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48798,7 +48799,7 @@
         <v>45693</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48871,7 +48872,7 @@
         <v>45092</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48944,7 +48945,7 @@
         <v>45092</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49017,7 +49018,7 @@
         <v>46119</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49090,7 +49091,7 @@
         <v>45075</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49163,7 +49164,7 @@
         <v>46119</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49241,7 +49242,7 @@
         <v>46119</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49319,7 +49320,7 @@
         <v>45960</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49392,7 +49393,7 @@
         <v>46119</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49465,7 +49466,7 @@
         <v>45636</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49538,7 +49539,7 @@
         <v>45020</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49611,7 +49612,7 @@
         <v>45139</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49684,7 +49685,7 @@
         <v>45614</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49757,7 +49758,7 @@
         <v>44704</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49830,7 +49831,7 @@
         <v>45967</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49903,7 +49904,7 @@
         <v>45022</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49976,7 +49977,7 @@
         <v>45168</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50054,7 +50055,7 @@
         <v>44790</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50127,7 +50128,7 @@
         <v>45813</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50200,7 +50201,7 @@
         <v>45971</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50278,7 +50279,7 @@
         <v>45411</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50356,7 +50357,7 @@
         <v>44953</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50429,7 +50430,7 @@
         <v>45376</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50507,7 +50508,7 @@
         <v>45973</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50580,7 +50581,7 @@
         <v>45519</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50653,7 +50654,7 @@
         <v>45107</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50726,7 +50727,7 @@
         <v>46107</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50799,7 +50800,7 @@
         <v>45111</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50872,7 +50873,7 @@
         <v>46132</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50945,7 +50946,7 @@
         <v>44974</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51018,7 +51019,7 @@
         <v>44771</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51091,7 +51092,7 @@
         <v>46134</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51164,7 +51165,7 @@
         <v>46133</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51237,7 +51238,7 @@
         <v>45982</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51315,7 +51316,7 @@
         <v>45609</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51388,7 +51389,7 @@
         <v>44743</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51466,7 +51467,7 @@
         <v>45817</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51544,7 +51545,7 @@
         <v>45638</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51622,7 +51623,7 @@
         <v>45985</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51700,7 +51701,7 @@
         <v>45712</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51778,7 +51779,7 @@
         <v>45898</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51851,7 +51852,7 @@
         <v>45601</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51924,7 +51925,7 @@
         <v>45177</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51997,7 +51998,7 @@
         <v>44763</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52070,7 +52071,7 @@
         <v>45700</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52148,7 +52149,7 @@
         <v>46119</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52226,7 +52227,7 @@
         <v>45735</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52299,7 +52300,7 @@
         <v>46135</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52372,7 +52373,7 @@
         <v>44495</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52445,7 +52446,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52523,7 +52524,7 @@
         <v>45992</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52596,7 +52597,7 @@
         <v>45435</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52669,7 +52670,7 @@
         <v>44749</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52742,7 +52743,7 @@
         <v>44782</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52815,7 +52816,7 @@
         <v>45994</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52888,7 +52889,7 @@
         <v>45993</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52961,7 +52962,7 @@
         <v>45994</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53034,7 +53035,7 @@
         <v>45994</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53112,7 +53113,7 @@
         <v>45993</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53185,7 +53186,7 @@
         <v>44719</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53258,7 +53259,7 @@
         <v>45903</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53336,7 +53337,7 @@
         <v>45996</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53409,7 +53410,7 @@
         <v>44980</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53482,7 +53483,7 @@
         <v>45700</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53555,7 +53556,7 @@
         <v>45747</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53628,7 +53629,7 @@
         <v>45490</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53706,7 +53707,7 @@
         <v>45999</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53779,7 +53780,7 @@
         <v>45707</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53852,7 +53853,7 @@
         <v>45667</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53925,7 +53926,7 @@
         <v>45853</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53998,7 +53999,7 @@
         <v>44777</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54071,7 +54072,7 @@
         <v>45085</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54144,7 +54145,7 @@
         <v>46000</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54217,7 +54218,7 @@
         <v>45243</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54295,7 +54296,7 @@
         <v>45953</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54368,7 +54369,7 @@
         <v>45817</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54441,7 +54442,7 @@
         <v>44760</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54514,7 +54515,7 @@
         <v>45042</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54587,7 +54588,7 @@
         <v>46002</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54660,7 +54661,7 @@
         <v>45219</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54733,7 +54734,7 @@
         <v>45442</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54806,7 +54807,7 @@
         <v>46002</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54879,7 +54880,7 @@
         <v>46000</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54952,7 +54953,7 @@
         <v>46001</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55025,7 +55026,7 @@
         <v>45068</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55098,7 +55099,7 @@
         <v>45797</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55171,7 +55172,7 @@
         <v>45953</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55244,7 +55245,7 @@
         <v>45835</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55322,7 +55323,7 @@
         <v>45063</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55395,7 +55396,7 @@
         <v>46008</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55473,7 +55474,7 @@
         <v>46008</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55546,7 +55547,7 @@
         <v>45880</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55624,7 +55625,7 @@
         <v>45847</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55702,7 +55703,7 @@
         <v>45391</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55775,7 +55776,7 @@
         <v>45670</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55848,7 +55849,7 @@
         <v>45191</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55926,7 +55927,7 @@
         <v>46009</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55999,7 +56000,7 @@
         <v>44510</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56077,7 +56078,7 @@
         <v>44815</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56150,7 +56151,7 @@
         <v>45587</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56223,7 +56224,7 @@
         <v>45771</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56296,7 +56297,7 @@
         <v>45824</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56374,7 +56375,7 @@
         <v>45706</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56452,7 +56453,7 @@
         <v>45730</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56525,7 +56526,7 @@
         <v>45723</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56603,7 +56604,7 @@
         <v>45554</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56676,7 +56677,7 @@
         <v>44670</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56749,7 +56750,7 @@
         <v>44851</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56822,7 +56823,7 @@
         <v>45971</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56895,7 +56896,7 @@
         <v>45054</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56968,7 +56969,7 @@
         <v>45800</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57041,7 +57042,7 @@
         <v>45813</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57119,7 +57120,7 @@
         <v>45236</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57192,7 +57193,7 @@
         <v>45055</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57265,7 +57266,7 @@
         <v>45831</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57338,7 +57339,7 @@
         <v>45075</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57411,7 +57412,7 @@
         <v>44596</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57489,7 +57490,7 @@
         <v>44549</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57562,7 +57563,7 @@
         <v>45063</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57635,7 +57636,7 @@
         <v>45065</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57713,7 +57714,7 @@
         <v>46150</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57786,7 +57787,7 @@
         <v>45469</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57859,7 +57860,7 @@
         <v>46150</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57932,7 +57933,7 @@
         <v>46150</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58005,7 +58006,7 @@
         <v>46150</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58078,7 +58079,7 @@
         <v>46150</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58151,7 +58152,7 @@
         <v>44760</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58224,7 +58225,7 @@
         <v>44816</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58297,7 +58298,7 @@
         <v>45834</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58370,7 +58371,7 @@
         <v>45834</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58443,7 +58444,7 @@
         <v>45089</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58516,7 +58517,7 @@
         <v>45834</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58589,7 +58590,7 @@
         <v>46155</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58662,7 +58663,7 @@
         <v>45835</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58735,7 +58736,7 @@
         <v>45817</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58808,7 +58809,7 @@
         <v>45740</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58881,7 +58882,7 @@
         <v>45740</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58954,7 +58955,7 @@
         <v>45344</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59027,7 +59028,7 @@
         <v>45947</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59100,7 +59101,7 @@
         <v>45231</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59173,7 +59174,7 @@
         <v>46111</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59246,7 +59247,7 @@
         <v>44992</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59319,7 +59320,7 @@
         <v>45054</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59392,7 +59393,7 @@
         <v>45054</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59465,7 +59466,7 @@
         <v>45840</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59538,7 +59539,7 @@
         <v>45104</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59611,7 +59612,7 @@
         <v>45839</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59684,7 +59685,7 @@
         <v>45022</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59757,7 +59758,7 @@
         <v>45841</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59830,7 +59831,7 @@
         <v>45886</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59903,7 +59904,7 @@
         <v>45916</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59976,7 +59977,7 @@
         <v>44643</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60049,7 +60050,7 @@
         <v>45817</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60122,7 +60123,7 @@
         <v>45581</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60195,7 +60196,7 @@
         <v>45152</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60268,7 +60269,7 @@
         <v>44949</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60341,7 +60342,7 @@
         <v>44953</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60414,7 +60415,7 @@
         <v>44963</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60487,7 +60488,7 @@
         <v>45084</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60560,7 +60561,7 @@
         <v>44882</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60633,7 +60634,7 @@
         <v>45852</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60706,7 +60707,7 @@
         <v>45455</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60779,7 +60780,7 @@
         <v>45147</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60852,7 +60853,7 @@
         <v>46167</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60925,7 +60926,7 @@
         <v>45855</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61003,7 +61004,7 @@
         <v>44556</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61076,7 +61077,7 @@
         <v>45855</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61154,7 +61155,7 @@
         <v>44470</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61227,7 +61228,7 @@
         <v>45957</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61300,7 +61301,7 @@
         <v>45956</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61373,7 +61374,7 @@
         <v>44621</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61446,7 +61447,7 @@
         <v>44868</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61519,7 +61520,7 @@
         <v>45104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61592,7 +61593,7 @@
         <v>45104</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61665,7 +61666,7 @@
         <v>45376</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61738,7 +61739,7 @@
         <v>45776</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61811,7 +61812,7 @@
         <v>44510</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61889,7 +61890,7 @@
         <v>45576</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61962,7 +61963,7 @@
         <v>46174</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62035,7 +62036,7 @@
         <v>45845</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62108,7 +62109,7 @@
         <v>46177</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62181,7 +62182,7 @@
         <v>45446</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62254,7 +62255,7 @@
         <v>45525</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62327,7 +62328,7 @@
         <v>45385</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62400,7 +62401,7 @@
         <v>45536</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62473,7 +62474,7 @@
         <v>46177</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62546,7 +62547,7 @@
         <v>45170</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62619,7 +62620,7 @@
         <v>44525</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62692,7 +62693,7 @@
         <v>44546</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62765,7 +62766,7 @@
         <v>44516</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62843,7 +62844,7 @@
         <v>44516</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62921,7 +62922,7 @@
         <v>46178</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62994,7 +62995,7 @@
         <v>45468</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63067,7 +63068,7 @@
         <v>46181</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63145,7 +63146,7 @@
         <v>46181</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63218,7 +63219,7 @@
         <v>44769</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63291,7 +63292,7 @@
         <v>46178</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63364,7 +63365,7 @@
         <v>46178</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63437,7 +63438,7 @@
         <v>46183</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63515,7 +63516,7 @@
         <v>45271</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63588,7 +63589,7 @@
         <v>45642</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63661,7 +63662,7 @@
         <v>44637</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63739,7 +63740,7 @@
         <v>45443</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63812,7 +63813,7 @@
         <v>45245</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63885,7 +63886,7 @@
         <v>46183</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63958,7 +63959,7 @@
         <v>46183</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64031,7 +64032,7 @@
         <v>44953</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64104,7 +64105,7 @@
         <v>46189</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64177,7 +64178,7 @@
         <v>45533</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64250,7 +64251,7 @@
         <v>46188</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64323,7 +64324,7 @@
         <v>46188</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64396,7 +64397,7 @@
         <v>45547</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64469,7 +64470,7 @@
         <v>46188</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64542,7 +64543,7 @@
         <v>46191</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64615,7 +64616,7 @@
         <v>44584</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64688,7 +64689,7 @@
         <v>45721</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64761,7 +64762,7 @@
         <v>46191</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64834,7 +64835,7 @@
         <v>46191</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64907,7 +64908,7 @@
         <v>46077</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64980,7 +64981,7 @@
         <v>46195</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65053,7 +65054,7 @@
         <v>44795</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65126,7 +65127,7 @@
         <v>45075</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65199,7 +65200,7 @@
         <v>45075</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65272,7 +65273,7 @@
         <v>45075</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65345,7 +65346,7 @@
         <v>45089</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65418,7 +65419,7 @@
         <v>45776</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65491,7 +65492,7 @@
         <v>45203</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65564,7 +65565,7 @@
         <v>46197</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65637,7 +65638,7 @@
         <v>44596</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65710,7 +65711,7 @@
         <v>46197</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65783,7 +65784,7 @@
         <v>46197</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65856,7 +65857,7 @@
         <v>45636</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65929,7 +65930,7 @@
         <v>45880</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66007,7 +66008,7 @@
         <v>45639</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66080,7 +66081,7 @@
         <v>45644</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66153,7 +66154,7 @@
         <v>45450</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66231,7 +66232,7 @@
         <v>45957</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66309,7 +66310,7 @@
         <v>44580</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66382,7 +66383,7 @@
         <v>45113</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66455,7 +66456,7 @@
         <v>44673</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66528,7 +66529,7 @@
         <v>44648</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66601,7 +66602,7 @@
         <v>44643</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66674,7 +66675,7 @@
         <v>45386</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66747,7 +66748,7 @@
         <v>46202</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66820,7 +66821,7 @@
         <v>46203</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66893,7 +66894,7 @@
         <v>45882</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66966,7 +66967,7 @@
         <v>46203</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67039,7 +67040,7 @@
         <v>46204</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67112,7 +67113,7 @@
         <v>44816</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67185,7 +67186,7 @@
         <v>45456</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67258,7 +67259,7 @@
         <v>44525</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67331,7 +67332,7 @@
         <v>45617</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67404,7 +67405,7 @@
         <v>46204</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67477,7 +67478,7 @@
         <v>45121</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67550,7 +67551,7 @@
         <v>45232</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67623,7 +67624,7 @@
         <v>45376</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67696,7 +67697,7 @@
         <v>46207</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67769,7 +67770,7 @@
         <v>46207</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67842,7 +67843,7 @@
         <v>45183</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67915,7 +67916,7 @@
         <v>46206</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67988,7 +67989,7 @@
         <v>44644</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68061,7 +68062,7 @@
         <v>46209</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68134,7 +68135,7 @@
         <v>44635</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68207,7 +68208,7 @@
         <v>44670</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68280,7 +68281,7 @@
         <v>45695</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68358,7 +68359,7 @@
         <v>46254</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68431,7 +68432,7 @@
         <v>45208</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68504,7 +68505,7 @@
         <v>45202</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68577,7 +68578,7 @@
         <v>44624</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68650,7 +68651,7 @@
         <v>45147</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68723,7 +68724,7 @@
         <v>44687</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68801,7 +68802,7 @@
         <v>45775</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68874,7 +68875,7 @@
         <v>46255</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68947,7 +68948,7 @@
         <v>45146</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69025,7 +69026,7 @@
         <v>46258</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69098,7 +69099,7 @@
         <v>46254</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69176,7 +69177,7 @@
         <v>45522</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69249,7 +69250,7 @@
         <v>46258</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69322,7 +69323,7 @@
         <v>45685</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69395,7 +69396,7 @@
         <v>46258</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69468,7 +69469,7 @@
         <v>45757</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69541,7 +69542,7 @@
         <v>46254</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69619,7 +69620,7 @@
         <v>45174</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69697,7 +69698,7 @@
         <v>45686</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69770,7 +69771,7 @@
         <v>44704</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69843,7 +69844,7 @@
         <v>46216</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69916,7 +69917,7 @@
         <v>45208</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69989,7 +69990,7 @@
         <v>45208</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70062,7 +70063,7 @@
         <v>46259</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70135,7 +70136,7 @@
         <v>45237</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70208,7 +70209,7 @@
         <v>45145</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70281,7 +70282,7 @@
         <v>46260</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70359,7 +70360,7 @@
         <v>46259</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70432,7 +70433,7 @@
         <v>46260</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70510,7 +70511,7 @@
         <v>46218</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70583,7 +70584,7 @@
         <v>46260</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70661,7 +70662,7 @@
         <v>45245</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70734,7 +70735,7 @@
         <v>46261</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70807,7 +70808,7 @@
         <v>44708</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70880,7 +70881,7 @@
         <v>44708</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70958,7 +70959,7 @@
         <v>44746</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71031,7 +71032,7 @@
         <v>46261</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71104,7 +71105,7 @@
         <v>46261</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71177,7 +71178,7 @@
         <v>44684</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71250,7 +71251,7 @@
         <v>45127</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71328,7 +71329,7 @@
         <v>45245</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71401,7 +71402,7 @@
         <v>44743</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71479,7 +71480,7 @@
         <v>44732</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71552,7 +71553,7 @@
         <v>45208</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71625,7 +71626,7 @@
         <v>45128</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71698,7 +71699,7 @@
         <v>46220</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71771,7 +71772,7 @@
         <v>44799</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71844,7 +71845,7 @@
         <v>46265</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71917,7 +71918,7 @@
         <v>45293</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71995,7 +71996,7 @@
         <v>45728</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72068,7 +72069,7 @@
         <v>46225</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72141,7 +72142,7 @@
         <v>46268</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72214,7 +72215,7 @@
         <v>46268</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72287,7 +72288,7 @@
         <v>46266</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72360,7 +72361,7 @@
         <v>46266</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72433,7 +72434,7 @@
         <v>46266</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72506,7 +72507,7 @@
         <v>45254</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72579,7 +72580,7 @@
         <v>46266</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72652,7 +72653,7 @@
         <v>46261</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72725,7 +72726,7 @@
         <v>46261</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72798,7 +72799,7 @@
         <v>44925</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72871,7 +72872,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72949,7 +72950,7 @@
         <v>44806</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73022,7 +73023,7 @@
         <v>44783</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73095,7 +73096,7 @@
         <v>46272</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73168,7 +73169,7 @@
         <v>44785</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73246,7 +73247,7 @@
         <v>45394</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73319,7 +73320,7 @@
         <v>45019</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73392,7 +73393,7 @@
         <v>45631</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73465,7 +73466,7 @@
         <v>44769</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73538,7 +73539,7 @@
         <v>46237</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73611,7 +73612,7 @@
         <v>45401</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73684,7 +73685,7 @@
         <v>46238</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73757,7 +73758,7 @@
         <v>45208</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73830,7 +73831,7 @@
         <v>45238</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73903,7 +73904,7 @@
         <v>44698</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73976,7 +73977,7 @@
         <v>45469</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74049,7 +74050,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74122,7 +74123,7 @@
         <v>44621</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74195,7 +74196,7 @@
         <v>45212</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74268,7 +74269,7 @@
         <v>46239</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74341,7 +74342,7 @@
         <v>46239</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74414,7 +74415,7 @@
         <v>45640</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74487,7 +74488,7 @@
         <v>45328</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74560,7 +74561,7 @@
         <v>46241</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74633,7 +74634,7 @@
         <v>45721</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74706,7 +74707,7 @@
         <v>45456</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74779,7 +74780,7 @@
         <v>45531</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74852,7 +74853,7 @@
         <v>44691</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74925,7 +74926,7 @@
         <v>44908</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74998,7 +74999,7 @@
         <v>46283</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75071,7 +75072,7 @@
         <v>45518</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75144,7 +75145,7 @@
         <v>45414</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75217,7 +75218,7 @@
         <v>45033</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75290,7 +75291,7 @@
         <v>44769</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75363,7 +75364,7 @@
         <v>45183</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75436,7 +75437,7 @@
         <v>46288</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75509,7 +75510,7 @@
         <v>44854</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75582,7 +75583,7 @@
         <v>46288</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75655,7 +75656,7 @@
         <v>44778</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75728,7 +75729,7 @@
         <v>44832</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75801,7 +75802,7 @@
         <v>44682</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75874,7 +75875,7 @@
         <v>45587</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75947,7 +75948,7 @@
         <v>45085</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76025,7 +76026,7 @@
         <v>46289</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76098,7 +76099,7 @@
         <v>44925</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76171,7 +76172,7 @@
         <v>46289</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76244,7 +76245,7 @@
         <v>46289</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76317,7 +76318,7 @@
         <v>46182</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76390,7 +76391,7 @@
         <v>46284</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76463,7 +76464,7 @@
         <v>46284</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76536,7 +76537,7 @@
         <v>44866</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76609,7 +76610,7 @@
         <v>45799</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76682,7 +76683,7 @@
         <v>45561</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76755,7 +76756,7 @@
         <v>46247</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76828,7 +76829,7 @@
         <v>46247</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76901,7 +76902,7 @@
         <v>46247</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76974,7 +76975,7 @@
         <v>46289</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77047,7 +77048,7 @@
         <v>44922</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77120,7 +77121,7 @@
         <v>44767</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77193,7 +77194,7 @@
         <v>44490</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77266,7 +77267,7 @@
         <v>44490</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77339,7 +77340,7 @@
         <v>44995</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77412,7 +77413,7 @@
         <v>44750</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77485,7 +77486,7 @@
         <v>44750</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77558,7 +77559,7 @@
         <v>46247</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77631,7 +77632,7 @@
         <v>46246</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77704,7 +77705,7 @@
         <v>45338</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77777,7 +77778,7 @@
         <v>45082</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77850,7 +77851,7 @@
         <v>45082</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77923,7 +77924,7 @@
         <v>45468</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77996,7 +77997,7 @@
         <v>45261</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78069,7 +78070,7 @@
         <v>45253</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78142,7 +78143,7 @@
         <v>45621</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78220,7 +78221,7 @@
         <v>44938</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78293,7 +78294,7 @@
         <v>44753</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78366,7 +78367,7 @@
         <v>44698</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78444,7 +78445,7 @@
         <v>44777</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78517,7 +78518,7 @@
         <v>45668</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78590,7 +78591,7 @@
         <v>45670</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78663,7 +78664,7 @@
         <v>44599</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78736,7 +78737,7 @@
         <v>44743</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78814,7 +78815,7 @@
         <v>45640</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78887,7 +78888,7 @@
         <v>44858</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78960,7 +78961,7 @@
         <v>45453</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -79033,7 +79034,7 @@
         <v>45310</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79106,7 +79107,7 @@
         <v>45310</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79179,7 +79180,7 @@
         <v>44700</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79252,7 +79253,7 @@
         <v>45254</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79325,7 +79326,7 @@
         <v>45089</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79398,7 +79399,7 @@
         <v>45159</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79471,7 +79472,7 @@
         <v>45322</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79544,7 +79545,7 @@
         <v>45414</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79617,7 +79618,7 @@
         <v>45225</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79690,7 +79691,7 @@
         <v>45139</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79763,7 +79764,7 @@
         <v>45082</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79836,7 +79837,7 @@
         <v>45482</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79909,7 +79910,7 @@
         <v>44956</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79982,7 +79983,7 @@
         <v>45084</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -80060,7 +80061,7 @@
         <v>45257</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80133,7 +80134,7 @@
         <v>44803</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80206,7 +80207,7 @@
         <v>44687</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80279,7 +80280,7 @@
         <v>45056</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80352,7 +80353,7 @@
         <v>45530</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80425,7 +80426,7 @@
         <v>45218</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80498,7 +80499,7 @@
         <v>44817</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80571,7 +80572,7 @@
         <v>45022</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80644,7 +80645,7 @@
         <v>44841</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80722,7 +80723,7 @@
         <v>45518</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80795,7 +80796,7 @@
         <v>45757</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80868,7 +80869,7 @@
         <v>45721</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80941,7 +80942,7 @@
         <v>45708</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -81019,7 +81020,7 @@
         <v>44934</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81092,7 +81093,7 @@
         <v>44778</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81165,7 +81166,7 @@
         <v>44581</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81238,7 +81239,7 @@
         <v>45376</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81311,7 +81312,7 @@
         <v>45293</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81384,7 +81385,7 @@
         <v>45245</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81457,7 +81458,7 @@
         <v>45245</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81530,7 +81531,7 @@
         <v>44956</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81603,7 +81604,7 @@
         <v>44931</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81676,7 +81677,7 @@
         <v>45460</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81749,7 +81750,7 @@
         <v>45293</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81822,7 +81823,7 @@
         <v>45617</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81895,7 +81896,7 @@
         <v>44900</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81968,7 +81969,7 @@
         <v>44714</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -82041,7 +82042,7 @@
         <v>45245</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82114,7 +82115,7 @@
         <v>45356</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82187,7 +82188,7 @@
         <v>45092</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82260,7 +82261,7 @@
         <v>44816</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82333,7 +82334,7 @@
         <v>45075</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82406,7 +82407,7 @@
         <v>45490</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82479,7 +82480,7 @@
         <v>45357</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82552,7 +82553,7 @@
         <v>45600</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82630,7 +82631,7 @@
         <v>45644</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82703,7 +82704,7 @@
         <v>45086</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82776,7 +82777,7 @@
         <v>45253</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82849,7 +82850,7 @@
         <v>45737</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82927,7 +82928,7 @@
         <v>45175</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -83000,7 +83001,7 @@
         <v>45259</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83073,7 +83074,7 @@
         <v>45253</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83146,7 +83147,7 @@
         <v>45316</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83219,7 +83220,7 @@
         <v>45190</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83292,7 +83293,7 @@
         <v>45783</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83365,7 +83366,7 @@
         <v>45783</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83438,7 +83439,7 @@
         <v>45385</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83511,7 +83512,7 @@
         <v>45549</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83584,7 +83585,7 @@
         <v>45187</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83657,7 +83658,7 @@
         <v>45735</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83730,7 +83731,7 @@
         <v>45709</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83808,7 +83809,7 @@
         <v>45572</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83881,7 +83882,7 @@
         <v>45537</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83954,7 +83955,7 @@
         <v>45579</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -84027,7 +84028,7 @@
         <v>45352</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84100,7 +84101,7 @@
         <v>44578</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84173,7 +84174,7 @@
         <v>45408</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84246,7 +84247,7 @@
         <v>45635</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84319,7 +84320,7 @@
         <v>44099</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84392,7 +84393,7 @@
         <v>43969</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84465,7 +84466,7 @@
         <v>44959</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84538,7 +84539,7 @@
         <v>43943</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84611,7 +84612,7 @@
         <v>44599</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84684,7 +84685,7 @@
         <v>44638</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84762,7 +84763,7 @@
         <v>44652</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84835,7 +84836,7 @@
         <v>44627</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84908,7 +84909,7 @@
         <v>44558</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84981,7 +84982,7 @@
         <v>44574</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -85054,7 +85055,7 @@
         <v>44690</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85127,7 +85128,7 @@
         <v>44854</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85200,7 +85201,7 @@
         <v>45260</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85273,7 +85274,7 @@
         <v>45366</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85346,7 +85347,7 @@
         <v>45537</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85419,7 +85420,7 @@
         <v>44497</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85492,7 +85493,7 @@
         <v>44497</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85565,7 +85566,7 @@
         <v>44971</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -85638,7 +85639,7 @@
         <v>45569</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -85711,7 +85712,7 @@
         <v>45188</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -85784,7 +85785,7 @@
         <v>44973</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -85857,7 +85858,7 @@
         <v>45183</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -85930,7 +85931,7 @@
         <v>44973</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -86003,7 +86004,7 @@
         <v>45817</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -86076,7 +86077,7 @@
         <v>45807</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -86149,7 +86150,7 @@
         <v>46062</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -86222,7 +86223,7 @@
         <v>46062</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -86295,7 +86296,7 @@
         <v>46188</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -86368,7 +86369,7 @@
         <v>44614</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45847</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>46029</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44482</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>45418</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>45800</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44949</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44571</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>45436</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45190</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>44467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45586</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>43969</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44858</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45684</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45446</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44949</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46107</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45960</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>44544</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44650</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44706</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45933</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45847</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>44489</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44711</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45104</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45485</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>45581</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>46204</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>46247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44956</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45783</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45071</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44749</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44855</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44778</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44683</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45821</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45082</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44743</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44679</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44530</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44843</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>46027</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45169</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44985</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44698</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45957</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45754</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44695</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>46163</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>46183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>46183</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45741</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44771</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44743</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>44629</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45642</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44880</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45383</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44956</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44474</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45803</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45945</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45070</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>46150</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>46150</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>46198</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45069</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45226</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44863</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>46288</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>46247</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44868</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45118</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44678</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45730</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44778</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45223</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45794</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45457</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44869</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>45532</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45549</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44867</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>46093</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44963</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44489</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45957</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44797</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>46133</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45987</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>44965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45450</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45840</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>46010</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45474</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45826</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>46062</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44955</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45764</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45081</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44760</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45904</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44483</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45147</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45147</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45855</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44705</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>45418</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45708</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45113</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46204</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44649</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45687</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45687</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45960</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45219</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44813</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44704</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45293</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45468</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>44813</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45007</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45205</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44637</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45473</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>44620</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45460</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>44639</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>44917</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>44518</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45572</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44642</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44650</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44833</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44777</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44728</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>44552</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44634</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>44581</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44560</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44771</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44477</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>44524</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44516</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44496</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44690</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>44682</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44626</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>44708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>44642</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44776</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44746</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44845</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44543</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44543</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44495</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>44882</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44545</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>44722</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44742</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>44756</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44806</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44511</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44510</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44867</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44511</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44683</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44539</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>44516</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44712</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>44769</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44543</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>44545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44545</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>44621</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44496</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>44637</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>44735</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44763</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>44735</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44524</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>44575</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>44650</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>44725</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44580</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44777</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>44637</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44655</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44665</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44595</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44744</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>44826</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>44845</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44526</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44642</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>44637</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>44607</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44698</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44609</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44760</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44817</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44477</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44584</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44678</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44682</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44682</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44623</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44665</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44665</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>44533</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44543</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>44704</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>44682</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>44725</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44523</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44815</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44595</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44495</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45621</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45075</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45075</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>44764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45051</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45273</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45749</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45362</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44743</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45203</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>44824</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45625</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45208</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>44879</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>44833</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45218</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45330</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44840</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45433</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45435</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45239</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>44895</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>45450</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45450</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44845</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45755</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45558</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45454</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>45202</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45075</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45075</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45075</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>44866</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45075</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>44809</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>44962</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45257</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45089</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45356</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45448</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>45119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>45463</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>44956</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45272</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>44472</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45468</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45385</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45729</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44470</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>44834</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45713</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45436</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45518</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44516</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45475</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>46029</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45524</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45341</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44708</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45798</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45798</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45798</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45469</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>45469</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>46030</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>46029</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>46029</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46034</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46034</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45888</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>46036</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46036</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45890</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>45813</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45586</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>44540</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45894</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45894</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45859</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45414</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45893</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45894</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45859</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45089</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45893</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45894</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>46042</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45896</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>44904</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45800</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45897</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>44901</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45898</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45898</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45897</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45897</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>46043</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>45075</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45427</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>46047</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40687,7 +40687,7 @@
         <v>45075</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45721</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>46049</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45610</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>46049</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46049</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>46049</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>45831</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44993</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45531</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45908</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45772</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46052</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>44525</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45890</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45803</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45910</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>46056</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45442</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45155</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>46058</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>45831</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46057</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46057</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46057</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>44938</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>46059</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45224</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>46061</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46062</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45918</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46063</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>46063</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45786</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46065</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>46065</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>44902</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46065</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46069</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44813</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>46069</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>46069</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45923</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45586</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45853</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45687</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>46072</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>46077</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>44923</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>46077</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45412</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>46077</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>46077</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>44585</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>45552</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>44945</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>44937</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45145</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45215</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>45930</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45930</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45930</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45155</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45254</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45260</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45790</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45810</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>44714</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>45810</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>46084</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>45936</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>45935</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45933</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45933</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45205</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45937</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45937</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45701</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>46093</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>46094</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>46094</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>44611</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>44986</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>46094</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45810</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45944</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>44775</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>46100</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45223</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>46100</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45947</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>44693</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>45947</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45947</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45947</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>45952</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45952</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>45952</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>45951</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>44867</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45075</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48278,7 +48278,7 @@
         <v>45348</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>45957</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45954</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46113</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>44803</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         <v>45956</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45957</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45693</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45092</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>45092</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>46119</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45075</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>46119</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>46119</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45960</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>46119</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45636</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45020</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45139</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>45614</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49758,7 +49758,7 @@
         <v>44704</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45967</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45022</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>45168</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44790</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45813</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45971</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45411</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44953</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>45376</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45973</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45519</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45107</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46107</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45111</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46132</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>44974</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>44771</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46134</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46133</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45982</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45609</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>44743</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45817</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45638</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45985</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45712</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45898</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45601</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45177</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>44763</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45700</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>46119</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45735</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46135</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>44495</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>45992</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52597,7 +52597,7 @@
         <v>45435</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52670,7 +52670,7 @@
         <v>44749</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>44782</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>45994</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45993</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45994</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45994</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>45993</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>44719</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45903</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45996</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>44980</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45700</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45747</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45490</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>45999</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45707</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45667</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45853</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>44777</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54072,7 +54072,7 @@
         <v>45085</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>46000</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45243</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54296,7 +54296,7 @@
         <v>45953</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45817</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54442,7 +54442,7 @@
         <v>44760</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45042</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>46002</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54661,7 +54661,7 @@
         <v>45219</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>45442</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>46002</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>46000</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>46001</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45068</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>45797</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45953</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45835</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>45063</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>46008</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>46008</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45880</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45847</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
         <v>45391</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55776,7 +55776,7 @@
         <v>45670</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45191</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46009</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>44510</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56078,7 +56078,7 @@
         <v>44815</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45587</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45771</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45824</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>45706</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56453,7 +56453,7 @@
         <v>45730</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45723</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45554</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44670</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>44851</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>45971</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>45054</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45800</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45813</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>45236</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57193,7 +57193,7 @@
         <v>45055</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>45831</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57339,7 +57339,7 @@
         <v>45075</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>44596</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>44549</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57563,7 +57563,7 @@
         <v>45063</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>45065</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57714,7 +57714,7 @@
         <v>46150</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45469</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57860,7 +57860,7 @@
         <v>46150</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>46150</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>46150</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58079,7 +58079,7 @@
         <v>46150</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>44760</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>44816</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>45834</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58371,7 +58371,7 @@
         <v>45834</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45089</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>45834</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>46155</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>45835</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58736,7 +58736,7 @@
         <v>45817</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45740</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>45740</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45344</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59028,7 +59028,7 @@
         <v>45947</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45231</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>46111</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59247,7 +59247,7 @@
         <v>44992</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>45054</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>45054</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>45840</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>45104</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>45839</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45022</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59758,7 +59758,7 @@
         <v>45841</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59831,7 +59831,7 @@
         <v>45886</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>45916</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>44643</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60050,7 +60050,7 @@
         <v>45817</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60123,7 +60123,7 @@
         <v>45581</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60196,7 +60196,7 @@
         <v>45152</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60269,7 +60269,7 @@
         <v>44949</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>44953</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>44963</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>45084</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>44882</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>45852</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60707,7 +60707,7 @@
         <v>45455</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45147</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>46167</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45855</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61004,7 +61004,7 @@
         <v>44556</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61077,7 +61077,7 @@
         <v>45855</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>44470</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61228,7 +61228,7 @@
         <v>45957</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61301,7 +61301,7 @@
         <v>45956</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61374,7 +61374,7 @@
         <v>44621</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61447,7 +61447,7 @@
         <v>44868</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61520,7 +61520,7 @@
         <v>45104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61593,7 +61593,7 @@
         <v>45104</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45376</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61739,7 +61739,7 @@
         <v>45776</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>44510</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45576</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>46174</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62036,7 +62036,7 @@
         <v>45845</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62109,7 +62109,7 @@
         <v>46177</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62182,7 +62182,7 @@
         <v>45446</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
         <v>45525</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62328,7 +62328,7 @@
         <v>45385</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>45536</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>46177</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62547,7 +62547,7 @@
         <v>45170</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62620,7 +62620,7 @@
         <v>44525</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>44546</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>44516</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62844,7 +62844,7 @@
         <v>44516</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62922,7 +62922,7 @@
         <v>46178</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62995,7 +62995,7 @@
         <v>45468</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>46181</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>46181</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63219,7 +63219,7 @@
         <v>44769</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>46178</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>46178</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         <v>46183</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63516,7 +63516,7 @@
         <v>45271</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>45642</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>44637</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45443</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63813,7 +63813,7 @@
         <v>45245</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>46183</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>46183</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>44953</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64105,7 +64105,7 @@
         <v>46189</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
         <v>45533</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>46188</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64324,7 +64324,7 @@
         <v>46188</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64397,7 +64397,7 @@
         <v>45547</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64470,7 +64470,7 @@
         <v>46188</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64543,7 +64543,7 @@
         <v>46191</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64616,7 +64616,7 @@
         <v>44584</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64689,7 +64689,7 @@
         <v>45721</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>46191</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64835,7 +64835,7 @@
         <v>46191</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64908,7 +64908,7 @@
         <v>46077</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64981,7 +64981,7 @@
         <v>46195</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65054,7 +65054,7 @@
         <v>44795</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65127,7 +65127,7 @@
         <v>45075</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45075</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45075</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>45089</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>45776</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>45203</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>46197</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>44596</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>46197</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>46197</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45636</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>45880</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66008,7 +66008,7 @@
         <v>45639</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66081,7 +66081,7 @@
         <v>45644</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66154,7 +66154,7 @@
         <v>45450</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>45957</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66310,7 +66310,7 @@
         <v>44580</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66383,7 +66383,7 @@
         <v>45113</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>44673</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>44648</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66602,7 +66602,7 @@
         <v>44643</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>45386</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>46202</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>46203</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66894,7 +66894,7 @@
         <v>45882</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66967,7 +66967,7 @@
         <v>46203</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67040,7 +67040,7 @@
         <v>46204</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67113,7 +67113,7 @@
         <v>44816</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67186,7 +67186,7 @@
         <v>45456</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>44525</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45617</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67405,7 +67405,7 @@
         <v>46204</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67478,7 +67478,7 @@
         <v>45121</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67551,7 +67551,7 @@
         <v>45232</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67624,7 +67624,7 @@
         <v>45376</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67697,7 +67697,7 @@
         <v>46207</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>46207</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67843,7 +67843,7 @@
         <v>45183</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67916,7 +67916,7 @@
         <v>46206</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67989,7 +67989,7 @@
         <v>44644</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68062,7 +68062,7 @@
         <v>46209</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68135,7 +68135,7 @@
         <v>44635</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68208,7 +68208,7 @@
         <v>44670</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68281,7 +68281,7 @@
         <v>45695</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68359,7 +68359,7 @@
         <v>46254</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68432,7 +68432,7 @@
         <v>45208</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68505,7 +68505,7 @@
         <v>45202</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68578,7 +68578,7 @@
         <v>44624</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68651,7 +68651,7 @@
         <v>45147</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68724,7 +68724,7 @@
         <v>44687</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68802,7 +68802,7 @@
         <v>45775</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68875,7 +68875,7 @@
         <v>46255</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68948,7 +68948,7 @@
         <v>45146</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69026,7 +69026,7 @@
         <v>46258</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69099,7 +69099,7 @@
         <v>46254</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69177,7 +69177,7 @@
         <v>45522</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>46258</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>45685</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>46258</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69469,7 +69469,7 @@
         <v>45757</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69542,7 +69542,7 @@
         <v>46254</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69620,7 +69620,7 @@
         <v>45174</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69698,7 +69698,7 @@
         <v>45686</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69771,7 +69771,7 @@
         <v>44704</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69844,7 +69844,7 @@
         <v>46216</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69917,7 +69917,7 @@
         <v>45208</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69990,7 +69990,7 @@
         <v>45208</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70063,7 +70063,7 @@
         <v>46259</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70136,7 +70136,7 @@
         <v>45237</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70209,7 +70209,7 @@
         <v>45145</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70282,7 +70282,7 @@
         <v>46260</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70360,7 +70360,7 @@
         <v>46259</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70433,7 +70433,7 @@
         <v>46260</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70511,7 +70511,7 @@
         <v>46218</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70584,7 +70584,7 @@
         <v>46260</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70662,7 +70662,7 @@
         <v>45245</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70735,7 +70735,7 @@
         <v>46261</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70808,7 +70808,7 @@
         <v>44708</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70881,7 +70881,7 @@
         <v>44708</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70959,7 +70959,7 @@
         <v>44746</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71032,7 +71032,7 @@
         <v>46261</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71105,7 +71105,7 @@
         <v>46261</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71178,7 +71178,7 @@
         <v>44684</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71251,7 +71251,7 @@
         <v>45127</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71329,7 +71329,7 @@
         <v>45245</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71402,7 +71402,7 @@
         <v>44743</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71480,7 +71480,7 @@
         <v>44732</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71553,7 +71553,7 @@
         <v>45208</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71626,7 +71626,7 @@
         <v>45128</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71699,7 +71699,7 @@
         <v>46220</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71772,7 +71772,7 @@
         <v>44799</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71845,7 +71845,7 @@
         <v>46265</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71918,7 +71918,7 @@
         <v>45293</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71996,7 +71996,7 @@
         <v>45728</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72069,7 +72069,7 @@
         <v>46225</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72142,7 +72142,7 @@
         <v>46268</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72215,7 +72215,7 @@
         <v>46268</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72288,7 +72288,7 @@
         <v>46266</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72361,7 +72361,7 @@
         <v>46266</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72434,7 +72434,7 @@
         <v>46266</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72507,7 +72507,7 @@
         <v>45254</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72580,7 +72580,7 @@
         <v>46266</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72653,7 +72653,7 @@
         <v>46261</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72726,7 +72726,7 @@
         <v>46261</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>44925</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72872,7 +72872,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72950,7 +72950,7 @@
         <v>44806</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73023,7 +73023,7 @@
         <v>44783</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73096,7 +73096,7 @@
         <v>46272</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73169,7 +73169,7 @@
         <v>44785</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73247,7 +73247,7 @@
         <v>45394</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73320,7 +73320,7 @@
         <v>45019</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73393,7 +73393,7 @@
         <v>45631</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73466,7 +73466,7 @@
         <v>44769</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73539,7 +73539,7 @@
         <v>46237</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73612,7 +73612,7 @@
         <v>45401</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
         <v>46238</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73758,7 +73758,7 @@
         <v>45208</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73831,7 +73831,7 @@
         <v>45238</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73904,7 +73904,7 @@
         <v>44698</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73977,7 +73977,7 @@
         <v>45469</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74050,7 +74050,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74123,7 +74123,7 @@
         <v>44621</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74196,7 +74196,7 @@
         <v>45212</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74269,7 +74269,7 @@
         <v>46239</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74342,7 +74342,7 @@
         <v>46239</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74415,7 +74415,7 @@
         <v>45640</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74488,7 +74488,7 @@
         <v>45328</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74561,7 +74561,7 @@
         <v>46241</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74634,7 +74634,7 @@
         <v>45721</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74707,7 +74707,7 @@
         <v>45456</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74780,7 +74780,7 @@
         <v>45531</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74853,7 +74853,7 @@
         <v>44691</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74926,7 +74926,7 @@
         <v>44908</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74999,7 +74999,7 @@
         <v>46283</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75072,7 +75072,7 @@
         <v>45518</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75145,7 +75145,7 @@
         <v>45414</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75218,7 +75218,7 @@
         <v>45033</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75291,7 +75291,7 @@
         <v>44769</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>45183</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75437,7 +75437,7 @@
         <v>46288</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75510,7 +75510,7 @@
         <v>44854</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75583,7 +75583,7 @@
         <v>46288</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75656,7 +75656,7 @@
         <v>44778</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75729,7 +75729,7 @@
         <v>44832</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75802,7 +75802,7 @@
         <v>44682</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75875,7 +75875,7 @@
         <v>45587</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75948,7 +75948,7 @@
         <v>45085</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76026,7 +76026,7 @@
         <v>46289</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76099,7 +76099,7 @@
         <v>44925</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76172,7 +76172,7 @@
         <v>46289</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76245,7 +76245,7 @@
         <v>46289</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76318,7 +76318,7 @@
         <v>46182</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76391,7 +76391,7 @@
         <v>46284</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76464,7 +76464,7 @@
         <v>46284</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76537,7 +76537,7 @@
         <v>44866</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76610,7 +76610,7 @@
         <v>45799</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76683,7 +76683,7 @@
         <v>45561</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76756,7 +76756,7 @@
         <v>46247</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76829,7 +76829,7 @@
         <v>46247</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76902,7 +76902,7 @@
         <v>46247</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76975,7 +76975,7 @@
         <v>46289</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77048,7 +77048,7 @@
         <v>44922</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77121,7 +77121,7 @@
         <v>44767</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77194,7 +77194,7 @@
         <v>44490</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77267,7 +77267,7 @@
         <v>44490</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77340,7 +77340,7 @@
         <v>44995</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77413,7 +77413,7 @@
         <v>44750</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77486,7 +77486,7 @@
         <v>44750</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77559,7 +77559,7 @@
         <v>46247</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77632,7 +77632,7 @@
         <v>46246</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77705,7 +77705,7 @@
         <v>45338</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77778,7 +77778,7 @@
         <v>45082</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77851,7 +77851,7 @@
         <v>45082</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77924,7 +77924,7 @@
         <v>45468</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77997,7 +77997,7 @@
         <v>45261</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78070,7 +78070,7 @@
         <v>45253</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78143,7 +78143,7 @@
         <v>45621</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78221,7 +78221,7 @@
         <v>44938</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78294,7 +78294,7 @@
         <v>44753</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78367,7 +78367,7 @@
         <v>44698</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78445,7 +78445,7 @@
         <v>44777</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78518,7 +78518,7 @@
         <v>45668</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78591,7 +78591,7 @@
         <v>45670</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78664,7 +78664,7 @@
         <v>44599</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78737,7 +78737,7 @@
         <v>44743</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78815,7 +78815,7 @@
         <v>45640</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78888,7 +78888,7 @@
         <v>44858</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78961,7 +78961,7 @@
         <v>45453</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -79034,7 +79034,7 @@
         <v>45310</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79107,7 +79107,7 @@
         <v>45310</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79180,7 +79180,7 @@
         <v>44700</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79253,7 +79253,7 @@
         <v>45254</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79326,7 +79326,7 @@
         <v>45089</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79399,7 +79399,7 @@
         <v>45159</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79472,7 +79472,7 @@
         <v>45322</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79545,7 +79545,7 @@
         <v>45414</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79618,7 +79618,7 @@
         <v>45225</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79691,7 +79691,7 @@
         <v>45139</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79764,7 +79764,7 @@
         <v>45082</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79837,7 +79837,7 @@
         <v>45482</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79910,7 +79910,7 @@
         <v>44956</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79983,7 +79983,7 @@
         <v>45084</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -80061,7 +80061,7 @@
         <v>45257</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80134,7 +80134,7 @@
         <v>44803</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80207,7 +80207,7 @@
         <v>44687</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80280,7 +80280,7 @@
         <v>45056</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80353,7 +80353,7 @@
         <v>45530</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80426,7 +80426,7 @@
         <v>45218</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80499,7 +80499,7 @@
         <v>44817</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80572,7 +80572,7 @@
         <v>45022</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80645,7 +80645,7 @@
         <v>44841</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80723,7 +80723,7 @@
         <v>45518</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80796,7 +80796,7 @@
         <v>45757</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80869,7 +80869,7 @@
         <v>45721</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80942,7 +80942,7 @@
         <v>45708</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>44934</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>44778</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>44581</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>45376</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>45293</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>45245</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45245</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>44956</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>44931</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45460</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45293</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45617</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>44900</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>44714</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>45245</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>45356</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45092</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>44816</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>45075</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45490</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>45357</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>45600</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82631,7 +82631,7 @@
         <v>45644</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82704,7 +82704,7 @@
         <v>45086</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82777,7 +82777,7 @@
         <v>45253</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82850,7 +82850,7 @@
         <v>45737</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82928,7 +82928,7 @@
         <v>45175</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -83001,7 +83001,7 @@
         <v>45259</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83074,7 +83074,7 @@
         <v>45253</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83147,7 +83147,7 @@
         <v>45316</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83220,7 +83220,7 @@
         <v>45190</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83293,7 +83293,7 @@
         <v>45783</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83366,7 +83366,7 @@
         <v>45783</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83439,7 +83439,7 @@
         <v>45385</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83512,7 +83512,7 @@
         <v>45549</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83585,7 +83585,7 @@
         <v>45187</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83658,7 +83658,7 @@
         <v>45735</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83731,7 +83731,7 @@
         <v>45709</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83809,7 +83809,7 @@
         <v>45572</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83882,7 +83882,7 @@
         <v>45537</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83955,7 +83955,7 @@
         <v>45579</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -84028,7 +84028,7 @@
         <v>45352</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84101,7 +84101,7 @@
         <v>44578</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84174,7 +84174,7 @@
         <v>45408</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84247,7 +84247,7 @@
         <v>45635</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84320,7 +84320,7 @@
         <v>44099</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84393,7 +84393,7 @@
         <v>43969</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84466,7 +84466,7 @@
         <v>44959</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84539,7 +84539,7 @@
         <v>43943</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84612,7 +84612,7 @@
         <v>44599</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84685,7 +84685,7 @@
         <v>44638</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84763,7 +84763,7 @@
         <v>44652</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84836,7 +84836,7 @@
         <v>44627</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84909,7 +84909,7 @@
         <v>44558</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84982,7 +84982,7 @@
         <v>44574</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -85055,7 +85055,7 @@
         <v>44690</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85128,7 +85128,7 @@
         <v>44854</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85201,7 +85201,7 @@
         <v>45260</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85274,7 +85274,7 @@
         <v>45366</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85347,7 +85347,7 @@
         <v>45537</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85420,7 +85420,7 @@
         <v>44497</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85493,7 +85493,7 @@
         <v>44497</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85566,7 +85566,7 @@
         <v>44971</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -85639,7 +85639,7 @@
         <v>45569</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -85712,7 +85712,7 @@
         <v>45188</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -85785,7 +85785,7 @@
         <v>44973</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -85858,7 +85858,7 @@
         <v>45183</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -85931,7 +85931,7 @@
         <v>44973</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -86004,7 +86004,7 @@
         <v>45817</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -86077,7 +86077,7 @@
         <v>45807</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -86150,7 +86150,7 @@
         <v>46062</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -86223,7 +86223,7 @@
         <v>46062</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -86296,7 +86296,7 @@
         <v>46188</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -86369,7 +86369,7 @@
         <v>44614</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44482</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45418</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44949</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44571</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>45190</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45994</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>46000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>43969</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44858</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45684</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44949</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45446</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45847</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45540</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45068</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44650</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45960</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45400</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44706</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45112</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45485</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>44956</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45664</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45581</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>46204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>46247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45783</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44972</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44512</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44749</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45082</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45831</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45616</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45821</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44683</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44872</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44855</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44778</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44679</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44880</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44530</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44843</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46027</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45754</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44985</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45169</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44866</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>46183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>46183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45741</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44695</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45609</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44743</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44629</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44594</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44880</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44502</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44474</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44956</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45803</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45559</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44863</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45945</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45118</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45069</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>46150</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>46198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44868</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45226</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45548</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>46247</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45383</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44678</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44497</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44868</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44564</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44858</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44495</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44868</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44658</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44869</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45457</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45177</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44620</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45460</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45007</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45897</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>44963</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45794</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45687</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45532</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45549</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44649</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44617</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>44867</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44483</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45623</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45957</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45730</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>46093</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45280</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45987</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45992</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>46133</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44637</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46062</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45081</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>46010</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>44903</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45855</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44747</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45904</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45708</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45418</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44778</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44797</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44955</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44592</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>46204</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45960</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44705</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44760</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>44813</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45223</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45450</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45474</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45473</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45205</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45608</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45687</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>44704</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45113</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44489</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44639</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>44917</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44518</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>44650</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44833</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44560</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44634</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44771</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>44477</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>44524</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44574</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44516</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>44834</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>44690</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44626</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44496</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>44682</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>44708</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44642</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44776</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44746</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>44543</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>44543</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44845</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44495</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44882</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>44545</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44722</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44742</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44756</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>44806</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44511</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44510</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>44867</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44511</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44683</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>44539</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>44496</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44516</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44712</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44769</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44543</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>44621</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44496</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44637</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44735</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44763</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44735</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44524</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>44575</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>44650</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>44725</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44580</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>44777</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44665</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>44637</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>44655</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44595</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44744</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44826</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44845</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>44526</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>44642</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>44637</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44607</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>44698</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>44609</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>44760</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44817</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>44584</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44477</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44623</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>44682</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44682</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>44665</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>44665</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44543</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44704</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>44682</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44523</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44725</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44595</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44815</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>44495</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44743</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>44670</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45518</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45443</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45022</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45208</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44510</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45089</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44743</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44643</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>44637</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45054</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45019</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45435</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44510</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44938</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44956</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45600</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44841</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45635</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>44578</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45721</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45735</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45709</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>46000</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>46002</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45621</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45537</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45187</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45385</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>45549</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45579</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45352</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45636</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46002</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45376</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>44832</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45455</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45245</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45847</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44783</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>46008</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>46009</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45587</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44895</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>46008</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44995</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45310</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>44904</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45561</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>45219</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44769</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
         <v>45813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>45888</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45700</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45890</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45859</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45859</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45893</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45893</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45894</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>46029</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45894</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45894</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45897</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45897</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45896</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>46029</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45897</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>46029</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45450</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45450</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>46030</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45223</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45642</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45208</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45427</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45208</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45898</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45898</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>46034</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45721</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46034</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>44708</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>44708</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45145</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44900</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>46036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45433</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>46036</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45482</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45831</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45536</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45531</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45772</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45908</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44834</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>44867</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46042</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44953</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45272</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45272</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45475</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45518</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>44708</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45436</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45831</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45910</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45385</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45713</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>45729</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>46043</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44816</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44931</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>44771</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46047</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45798</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45798</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45798</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>44687</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45586</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45803</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>45800</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>44813</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45918</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>46049</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>46049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46049</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>44901</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>46049</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>45224</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45890</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>46052</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>44760</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44581</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45786</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45362</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>45923</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>45640</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45394</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>46056</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>44611</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>46057</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>46057</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>46057</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44732</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45547</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45576</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45853</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>46058</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>46059</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46063</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45810</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>46062</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45930</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45930</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45930</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>46063</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>46061</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45469</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45933</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>46065</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>44945</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>46065</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45933</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46065</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45155</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45936</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>44687</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>46069</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45935</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>44803</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>44803</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45701</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>44778</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46069</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>46069</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45937</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>44767</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46524,7 +46524,7 @@
         <v>45810</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45670</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45937</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45104</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>45127</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45033</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>46072</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45121</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45790</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45944</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>46077</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>45810</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>44809</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>46077</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>46077</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>45947</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45947</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>46077</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         <v>44858</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45951</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45236</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45707</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>44949</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46084</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45063</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45453</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45952</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45952</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>45957</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45957</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45956</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45954</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45813</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>45757</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45960</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45177</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>45817</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45708</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>44584</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>46094</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>46093</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>46094</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45086</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45203</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45531</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>46094</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45971</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45973</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45208</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>44580</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>46100</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>46100</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45203</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45218</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>44714</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>44845</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>44472</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>45084</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45208</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45747</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45530</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45376</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>44937</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>45356</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>44785</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45985</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45982</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46113</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45341</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45554</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51885,7 +51885,7 @@
         <v>45075</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>46119</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52031,7 +52031,7 @@
         <v>45202</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>46119</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45254</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>46119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45824</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52484,7 +52484,7 @@
         <v>46119</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>45730</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>44962</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45993</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>44624</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52854,7 +52854,7 @@
         <v>45992</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52927,7 +52927,7 @@
         <v>45442</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53000,7 +53000,7 @@
         <v>45993</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45994</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>45994</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>45639</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45994</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>46107</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>45145</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45996</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53589,7 +53589,7 @@
         <v>45999</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>46000</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>44840</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>46001</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>44908</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45168</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45831</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45259</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>46133</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54251,7 +54251,7 @@
         <v>46132</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>46134</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45051</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>44673</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45834</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54616,7 +54616,7 @@
         <v>45245</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54689,7 +54689,7 @@
         <v>46135</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54762,7 +54762,7 @@
         <v>45834</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>46119</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54913,7 +54913,7 @@
         <v>44670</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>45835</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55059,7 +55059,7 @@
         <v>45621</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>45834</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55210,7 +55210,7 @@
         <v>45215</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45089</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>45695</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>45376</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45839</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55580,7 +55580,7 @@
         <v>45159</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45898</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45971</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45587</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45685</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45840</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>45853</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>45841</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45082</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56237,7 +56237,7 @@
         <v>45089</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>45155</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56383,7 +56383,7 @@
         <v>45344</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45469</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45670</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45723</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>45953</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45391</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>45152</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>45581</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45435</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>45953</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45092</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>44749</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57264,7 +57264,7 @@
         <v>45903</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>45835</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>45245</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45706</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45056</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45712</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45376</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>44974</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45460</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45855</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45797</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>45609</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45817</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>45855</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45257</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45735</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45700</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45667</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>45022</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45022</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45880</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45835</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>44854</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>44922</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45490</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>44700</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>44635</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>45638</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>44743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45813</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45257</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45525</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45776</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45330</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45757</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59957,7 +59957,7 @@
         <v>44769</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45800</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45446</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>44763</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>44833</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45737</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>45401</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45111</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45749</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60624,7 +60624,7 @@
         <v>44704</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>44778</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45450</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45085</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45625</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>46150</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>46150</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61145,7 +61145,7 @@
         <v>46150</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>46150</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45817</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>44993</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61442,7 +61442,7 @@
         <v>44925</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45721</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>44777</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>45640</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45533</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>44621</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>46155</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45273</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45631</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45490</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>44953</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45175</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45947</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>44992</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45886</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>45469</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45916</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>45817</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>46111</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>44777</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>44704</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>46167</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63048,7 +63048,7 @@
         <v>45456</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63121,7 +63121,7 @@
         <v>45104</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45104</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         <v>44824</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>45644</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>45880</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63491,7 +63491,7 @@
         <v>45957</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63564,7 +63564,7 @@
         <v>45776</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63637,7 +63637,7 @@
         <v>45956</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>45128</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>45322</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63856,7 +63856,7 @@
         <v>46174</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45386</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64002,7 +64002,7 @@
         <v>45845</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         <v>45075</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64153,7 +64153,7 @@
         <v>45882</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>45075</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45075</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64372,7 +64372,7 @@
         <v>45075</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64445,7 +64445,7 @@
         <v>46178</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64518,7 +64518,7 @@
         <v>44525</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64591,7 +64591,7 @@
         <v>45092</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64664,7 +64664,7 @@
         <v>45092</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64737,7 +64737,7 @@
         <v>46178</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>44516</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>44546</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64961,7 +64961,7 @@
         <v>45610</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65034,7 +65034,7 @@
         <v>45411</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65185,7 +65185,7 @@
         <v>46177</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65331,7 +65331,7 @@
         <v>45239</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         <v>46181</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65477,7 +65477,7 @@
         <v>46181</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>45414</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46183</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46183</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65774,7 +65774,7 @@
         <v>46183</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>46188</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>44643</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65998,7 +65998,7 @@
         <v>46188</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66071,7 +66071,7 @@
         <v>46188</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>45456</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45020</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66290,7 +66290,7 @@
         <v>46189</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66363,7 +66363,7 @@
         <v>44882</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         <v>45075</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66509,7 +66509,7 @@
         <v>45075</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66582,7 +66582,7 @@
         <v>45075</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66655,7 +66655,7 @@
         <v>45075</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66728,7 +66728,7 @@
         <v>45771</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66801,7 +66801,7 @@
         <v>44596</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66874,7 +66874,7 @@
         <v>44596</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>45208</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>46077</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>46191</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>46191</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>45552</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         <v>46191</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>46195</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45183</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67536,7 +67536,7 @@
         <v>45293</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67614,7 +67614,7 @@
         <v>45755</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>44952</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67765,7 +67765,7 @@
         <v>44790</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67838,7 +67838,7 @@
         <v>44879</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67911,7 +67911,7 @@
         <v>46197</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67984,7 +67984,7 @@
         <v>45293</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68057,7 +68057,7 @@
         <v>45293</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>44775</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68203,7 +68203,7 @@
         <v>46197</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68276,7 +68276,7 @@
         <v>46197</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68349,7 +68349,7 @@
         <v>44490</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68422,7 +68422,7 @@
         <v>45586</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68495,7 +68495,7 @@
         <v>44648</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68568,7 +68568,7 @@
         <v>45957</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68646,7 +68646,7 @@
         <v>45740</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         <v>45740</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68792,7 +68792,7 @@
         <v>45085</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68865,7 +68865,7 @@
         <v>46202</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68938,7 +68938,7 @@
         <v>44953</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69011,7 +69011,7 @@
         <v>45617</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69084,7 +69084,7 @@
         <v>46203</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69157,7 +69157,7 @@
         <v>45065</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69235,7 +69235,7 @@
         <v>46203</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69308,7 +69308,7 @@
         <v>45068</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69381,7 +69381,7 @@
         <v>46204</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69454,7 +69454,7 @@
         <v>44644</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69527,7 +69527,7 @@
         <v>46204</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69600,7 +69600,7 @@
         <v>46206</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>44746</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69746,7 +69746,7 @@
         <v>45139</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69819,7 +69819,7 @@
         <v>45218</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69892,7 +69892,7 @@
         <v>46207</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69965,7 +69965,7 @@
         <v>46207</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70038,7 +70038,7 @@
         <v>45414</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70111,7 +70111,7 @@
         <v>44599</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70184,7 +70184,7 @@
         <v>45412</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70257,7 +70257,7 @@
         <v>46209</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70330,7 +70330,7 @@
         <v>45205</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70403,7 +70403,7 @@
         <v>45147</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70476,7 +70476,7 @@
         <v>45191</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70554,7 +70554,7 @@
         <v>45084</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70627,7 +70627,7 @@
         <v>45442</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70700,7 +70700,7 @@
         <v>44525</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70778,7 +70778,7 @@
         <v>44540</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70851,7 +70851,7 @@
         <v>46216</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70924,7 +70924,7 @@
         <v>44556</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70997,7 +70997,7 @@
         <v>46258</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71070,7 +71070,7 @@
         <v>46259</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71143,7 +71143,7 @@
         <v>46258</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71216,7 +71216,7 @@
         <v>45468</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71289,7 +71289,7 @@
         <v>46259</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71362,7 +71362,7 @@
         <v>46258</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71435,7 +71435,7 @@
         <v>46260</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71513,7 +71513,7 @@
         <v>45139</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71586,7 +71586,7 @@
         <v>46260</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71664,7 +71664,7 @@
         <v>46261</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71737,7 +71737,7 @@
         <v>46218</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71810,7 +71810,7 @@
         <v>46261</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71883,7 +71883,7 @@
         <v>44525</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71956,7 +71956,7 @@
         <v>45463</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72029,7 +72029,7 @@
         <v>46260</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72107,7 +72107,7 @@
         <v>46261</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72180,7 +72180,7 @@
         <v>45636</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72253,7 +72253,7 @@
         <v>45146</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72331,7 +72331,7 @@
         <v>44698</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72409,7 +72409,7 @@
         <v>45468</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72482,7 +72482,7 @@
         <v>46220</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72555,7 +72555,7 @@
         <v>44691</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72628,7 +72628,7 @@
         <v>46266</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72701,7 +72701,7 @@
         <v>46266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72774,7 +72774,7 @@
         <v>45356</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72847,7 +72847,7 @@
         <v>44816</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72920,7 +72920,7 @@
         <v>46265</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72993,7 +72993,7 @@
         <v>45107</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73066,7 +73066,7 @@
         <v>45075</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73139,7 +73139,7 @@
         <v>45075</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73212,7 +73212,7 @@
         <v>46266</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
         <v>46266</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73358,7 +73358,7 @@
         <v>46268</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73431,7 +73431,7 @@
         <v>46268</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73504,7 +73504,7 @@
         <v>46225</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>46272</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73650,7 +73650,7 @@
         <v>44764</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73723,7 +73723,7 @@
         <v>46261</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73796,7 +73796,7 @@
         <v>46261</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73869,7 +73869,7 @@
         <v>45238</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73942,7 +73942,7 @@
         <v>45261</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74015,7 +74015,7 @@
         <v>45524</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74088,7 +74088,7 @@
         <v>45245</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74161,7 +74161,7 @@
         <v>45454</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74234,7 +74234,7 @@
         <v>46274</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74312,7 +74312,7 @@
         <v>46237</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74385,7 +74385,7 @@
         <v>46238</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74458,7 +74458,7 @@
         <v>45231</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74531,7 +74531,7 @@
         <v>46254</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>44866</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74677,7 +74677,7 @@
         <v>46239</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74750,7 +74750,7 @@
         <v>45082</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74823,7 +74823,7 @@
         <v>45082</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74896,7 +74896,7 @@
         <v>45260</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74969,7 +74969,7 @@
         <v>45260</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75042,7 +75042,7 @@
         <v>45617</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75115,7 +75115,7 @@
         <v>45063</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75188,7 +75188,7 @@
         <v>45721</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75261,7 +75261,7 @@
         <v>45055</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75334,7 +75334,7 @@
         <v>45614</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75407,7 +75407,7 @@
         <v>46239</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75480,7 +75480,7 @@
         <v>46283</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75553,7 +75553,7 @@
         <v>44714</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75626,7 +75626,7 @@
         <v>45687</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75704,7 +75704,7 @@
         <v>45225</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75777,7 +75777,7 @@
         <v>45253</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75850,7 +75850,7 @@
         <v>44851</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75923,7 +75923,7 @@
         <v>45042</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75996,7 +75996,7 @@
         <v>45414</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76069,7 +76069,7 @@
         <v>44585</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76147,7 +76147,7 @@
         <v>45469</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         <v>45385</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76293,7 +76293,7 @@
         <v>46241</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76366,7 +76366,7 @@
         <v>45202</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76439,7 +76439,7 @@
         <v>45075</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76512,7 +76512,7 @@
         <v>44743</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76590,7 +76590,7 @@
         <v>45054</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76663,7 +76663,7 @@
         <v>45054</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76736,7 +76736,7 @@
         <v>44925</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76809,7 +76809,7 @@
         <v>44760</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76882,7 +76882,7 @@
         <v>46288</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76955,7 +76955,7 @@
         <v>46288</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77028,7 +77028,7 @@
         <v>45644</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77101,7 +77101,7 @@
         <v>44621</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77174,7 +77174,7 @@
         <v>46246</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77247,7 +77247,7 @@
         <v>46289</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77320,7 +77320,7 @@
         <v>45183</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77393,7 +77393,7 @@
         <v>45089</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77466,7 +77466,7 @@
         <v>46289</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77539,7 +77539,7 @@
         <v>46289</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77612,7 +77612,7 @@
         <v>46289</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77685,7 +77685,7 @@
         <v>44719</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77758,7 +77758,7 @@
         <v>44698</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77831,7 +77831,7 @@
         <v>45519</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77904,7 +77904,7 @@
         <v>45170</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77977,7 +77977,7 @@
         <v>44549</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78050,7 +78050,7 @@
         <v>45601</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78123,7 +78123,7 @@
         <v>46247</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78196,7 +78196,7 @@
         <v>46247</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78269,7 +78269,7 @@
         <v>44516</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78347,7 +78347,7 @@
         <v>44516</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78425,7 +78425,7 @@
         <v>45448</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78498,7 +78498,7 @@
         <v>44782</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78571,7 +78571,7 @@
         <v>46284</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78644,7 +78644,7 @@
         <v>44753</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78717,7 +78717,7 @@
         <v>44902</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78790,7 +78790,7 @@
         <v>44795</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78863,7 +78863,7 @@
         <v>45518</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78936,7 +78936,7 @@
         <v>46247</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>45799</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79082,7 +79082,7 @@
         <v>46284</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79155,7 +79155,7 @@
         <v>46293</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79228,7 +79228,7 @@
         <v>46182</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79301,7 +79301,7 @@
         <v>46247</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79374,7 +79374,7 @@
         <v>45686</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79447,7 +79447,7 @@
         <v>45522</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>45357</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79593,7 +79593,7 @@
         <v>45147</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79666,7 +79666,7 @@
         <v>44923</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79739,7 +79739,7 @@
         <v>45212</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79812,7 +79812,7 @@
         <v>45119</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79885,7 +79885,7 @@
         <v>45668</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79958,7 +79958,7 @@
         <v>44682</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -80031,7 +80031,7 @@
         <v>44815</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80104,7 +80104,7 @@
         <v>44986</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80177,7 +80177,7 @@
         <v>45089</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80250,7 +80250,7 @@
         <v>46294</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80323,7 +80323,7 @@
         <v>45310</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80396,7 +80396,7 @@
         <v>44866</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80469,7 +80469,7 @@
         <v>44868</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80542,7 +80542,7 @@
         <v>44495</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80615,7 +80615,7 @@
         <v>44963</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80688,7 +80688,7 @@
         <v>44816</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80761,7 +80761,7 @@
         <v>46254</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80834,7 +80834,7 @@
         <v>45693</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80907,7 +80907,7 @@
         <v>46254</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80985,7 +80985,7 @@
         <v>46254</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81063,7 +81063,7 @@
         <v>45728</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81136,7 +81136,7 @@
         <v>45558</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81209,7 +81209,7 @@
         <v>44956</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81282,7 +81282,7 @@
         <v>44956</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81355,7 +81355,7 @@
         <v>46255</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81428,7 +81428,7 @@
         <v>44684</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81501,7 +81501,7 @@
         <v>45253</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81574,7 +81574,7 @@
         <v>44980</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81647,7 +81647,7 @@
         <v>45174</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81725,7 +81725,7 @@
         <v>45232</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81798,7 +81798,7 @@
         <v>45075</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81871,7 +81871,7 @@
         <v>45468</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81944,7 +81944,7 @@
         <v>44938</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -82017,7 +82017,7 @@
         <v>44806</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82090,7 +82090,7 @@
         <v>44934</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82163,7 +82163,7 @@
         <v>44799</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82236,7 +82236,7 @@
         <v>45063</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82309,7 +82309,7 @@
         <v>45075</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82382,7 +82382,7 @@
         <v>45245</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82455,7 +82455,7 @@
         <v>45245</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82528,7 +82528,7 @@
         <v>44750</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82601,7 +82601,7 @@
         <v>44750</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82674,7 +82674,7 @@
         <v>45075</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82747,7 +82747,7 @@
         <v>45338</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82820,7 +82820,7 @@
         <v>45254</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82893,7 +82893,7 @@
         <v>45775</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -82966,7 +82966,7 @@
         <v>44693</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83039,7 +83039,7 @@
         <v>44769</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83112,7 +83112,7 @@
         <v>45113</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83185,7 +83185,7 @@
         <v>45328</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83258,7 +83258,7 @@
         <v>45348</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83336,7 +83336,7 @@
         <v>44490</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83409,7 +83409,7 @@
         <v>45316</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83482,7 +83482,7 @@
         <v>45253</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83555,7 +83555,7 @@
         <v>45190</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83628,7 +83628,7 @@
         <v>45783</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83701,7 +83701,7 @@
         <v>45783</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83774,7 +83774,7 @@
         <v>45408</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83847,7 +83847,7 @@
         <v>43943</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83920,7 +83920,7 @@
         <v>43969</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -83993,7 +83993,7 @@
         <v>44959</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84066,7 +84066,7 @@
         <v>44099</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84139,7 +84139,7 @@
         <v>44854</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84212,7 +84212,7 @@
         <v>44599</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84285,7 +84285,7 @@
         <v>45260</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84358,7 +84358,7 @@
         <v>44638</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84436,7 +84436,7 @@
         <v>45366</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84509,7 +84509,7 @@
         <v>44652</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84582,7 +84582,7 @@
         <v>45537</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84655,7 +84655,7 @@
         <v>44627</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84728,7 +84728,7 @@
         <v>44497</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84801,7 +84801,7 @@
         <v>44558</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84874,7 +84874,7 @@
         <v>44497</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84947,7 +84947,7 @@
         <v>44971</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -85020,7 +85020,7 @@
         <v>44574</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85093,7 +85093,7 @@
         <v>44690</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85166,7 +85166,7 @@
         <v>45569</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85239,7 +85239,7 @@
         <v>45188</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85312,7 +85312,7 @@
         <v>44973</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85385,7 +85385,7 @@
         <v>45183</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85458,7 +85458,7 @@
         <v>44973</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85531,7 +85531,7 @@
         <v>45817</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -85604,7 +85604,7 @@
         <v>45807</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -85677,7 +85677,7 @@
         <v>46062</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>46062</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -85823,7 +85823,7 @@
         <v>46188</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -85896,7 +85896,7 @@
         <v>44614</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44482</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45418</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44949</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44571</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>45190</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45994</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>46000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>43969</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44858</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45684</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44949</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45446</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45847</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45540</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45068</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>44650</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45960</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45400</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44706</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45112</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45485</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>44956</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45664</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45581</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>46204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45104</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>46247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45783</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44972</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44512</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44749</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45082</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45831</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45616</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45821</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>44683</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44872</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44855</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44778</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44679</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44880</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44530</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44843</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46027</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44763</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44771</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45754</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44985</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45169</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44866</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>46163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>46183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>46183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45741</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44695</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45609</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44743</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44629</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44594</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44880</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44502</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44474</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44956</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45803</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45559</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44863</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45945</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45118</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45069</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>46150</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>46198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44868</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45226</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45548</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>46247</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45383</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>44896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44678</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44497</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44868</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44564</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44858</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44495</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44868</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>44658</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44869</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45457</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45177</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44620</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45460</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45007</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45897</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>44963</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45794</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45687</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45532</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45549</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44649</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44617</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>44867</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44483</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45623</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45957</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45730</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>46093</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45280</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45987</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45992</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>46133</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44637</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46062</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45081</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>46010</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>44903</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45855</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44747</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45904</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45708</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45418</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44778</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44797</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44955</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44592</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>46204</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45960</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44705</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44760</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>44813</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45223</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45450</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45474</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45473</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45205</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45608</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45687</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>44704</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45113</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44489</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44639</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>44917</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44518</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>44650</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44833</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44560</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44634</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44771</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>44477</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>44524</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44574</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44516</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>44834</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>44690</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44626</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44496</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>44682</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>44708</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44642</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44776</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44746</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>44543</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>44543</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44845</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44495</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>44882</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>44545</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44722</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44742</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44756</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>44806</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44511</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44510</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>44867</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44511</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44683</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>44539</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>44496</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44516</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44712</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44769</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44543</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>44621</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44496</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44637</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44735</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44763</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44735</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44524</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>44575</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>44650</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>44725</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44580</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>44777</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44665</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>44637</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>44655</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44595</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44744</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44826</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44845</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>44526</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>44642</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>44637</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44607</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>44698</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>44609</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>44760</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44817</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>44584</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44477</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44623</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>44682</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44682</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>44665</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>44665</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44543</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44704</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>44682</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44523</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44725</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44595</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44815</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>44495</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44743</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>44670</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45518</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45443</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45022</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45208</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44510</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45089</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44743</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44643</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>44637</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45054</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45019</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45435</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44510</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44938</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44956</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45600</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44841</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45635</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>44578</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45721</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45735</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45709</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>46000</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>46002</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45621</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45537</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45187</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45385</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>45549</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45579</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45352</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45636</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46002</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45376</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>44832</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45455</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45245</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45847</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44783</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>46008</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>46009</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45587</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44895</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>46008</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44995</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45310</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>44904</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45561</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>45219</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44769</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37080,7 +37080,7 @@
         <v>45813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>45888</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45700</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45890</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45859</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45859</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45893</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45893</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45894</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>46029</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45894</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45894</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45897</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45897</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45896</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>46029</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45897</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>46029</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45450</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45450</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>46030</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45223</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45642</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45208</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45427</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45208</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45898</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45898</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>46034</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45721</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46034</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>44708</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>44708</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45145</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44900</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>46036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45433</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>46036</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45482</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45831</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45536</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45531</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45772</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45908</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44834</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>44867</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46042</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44953</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45272</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45272</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45475</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45518</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>44708</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45436</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45831</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45910</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45385</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45713</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>45729</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>46043</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44816</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44931</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>44771</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46047</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45798</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45798</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45798</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>44687</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45586</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45803</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>45800</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>44813</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45918</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>46049</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>46049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46049</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>44901</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>46049</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>45224</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45890</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>46052</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>44760</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44581</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45786</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45362</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>45923</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>45640</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45394</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>46056</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>44611</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>46057</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>46057</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>46057</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44732</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45547</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45576</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45853</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>46058</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>46059</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46063</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45810</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>46062</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45930</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45930</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45930</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>46063</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>46061</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45049,7 +45049,7 @@
         <v>45469</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45933</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>46065</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>44945</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>46065</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45933</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46065</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45155</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45936</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>44687</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>46069</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45935</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>44803</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>44803</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45701</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>44778</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46069</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>46069</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45937</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>44767</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46524,7 +46524,7 @@
         <v>45810</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45670</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45937</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45104</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>45127</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45033</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>46072</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45121</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45790</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45944</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>46077</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>45810</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>44809</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>46077</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>46077</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>45947</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45947</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>46077</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         <v>44858</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45951</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45236</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>45707</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>44949</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46084</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45063</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45453</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45952</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45952</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>45957</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45957</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45956</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45954</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45813</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>45757</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45960</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45177</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>45817</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45708</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>44584</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>46094</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>46093</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>46094</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45086</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45203</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45531</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>46094</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45971</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45973</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45208</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>44580</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>46100</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>46100</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45203</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45218</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>44714</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>44845</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>44472</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>45084</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45208</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45747</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45530</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45376</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>44937</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>45356</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>44785</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45985</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45982</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46113</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45341</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45554</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51885,7 +51885,7 @@
         <v>45075</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51958,7 +51958,7 @@
         <v>46119</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52031,7 +52031,7 @@
         <v>45202</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>46119</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45254</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>46119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45824</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52484,7 +52484,7 @@
         <v>46119</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>45730</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>44962</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45993</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>44624</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52854,7 +52854,7 @@
         <v>45992</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52927,7 +52927,7 @@
         <v>45442</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53000,7 +53000,7 @@
         <v>45993</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45994</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>45994</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>45639</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>45994</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>46107</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>45145</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45996</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53589,7 +53589,7 @@
         <v>45999</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>46000</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>44840</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>46001</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>44908</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>45168</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45831</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45259</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>46133</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54251,7 +54251,7 @@
         <v>46132</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>46134</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45051</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>44673</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45834</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54616,7 +54616,7 @@
         <v>45245</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54689,7 +54689,7 @@
         <v>46135</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54762,7 +54762,7 @@
         <v>45834</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>46119</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54913,7 +54913,7 @@
         <v>44670</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>45835</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55059,7 +55059,7 @@
         <v>45621</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>45834</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55210,7 +55210,7 @@
         <v>45215</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45089</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>45695</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>45376</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>45839</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55580,7 +55580,7 @@
         <v>45159</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45898</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45971</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45587</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45685</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45840</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>45853</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>45841</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45082</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56237,7 +56237,7 @@
         <v>45089</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>45155</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56383,7 +56383,7 @@
         <v>45344</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45469</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45670</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45723</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>45953</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45391</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>45152</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>45581</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45435</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>45953</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45092</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>44749</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57264,7 +57264,7 @@
         <v>45903</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>45835</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>45245</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45706</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45056</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45712</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45376</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>44974</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>45460</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45855</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45797</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>45609</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45817</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>45855</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45257</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45735</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45700</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45667</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>45022</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45022</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45880</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45835</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>44854</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>44922</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45490</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>44700</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>44635</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>45638</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>44743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45813</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45257</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45525</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45776</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45330</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45757</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59957,7 +59957,7 @@
         <v>44769</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45800</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45446</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>44763</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>44833</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45737</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>45401</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45111</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45749</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60624,7 +60624,7 @@
         <v>44704</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>44778</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45450</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45085</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>45625</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>46150</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>46150</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61145,7 +61145,7 @@
         <v>46150</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>46150</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45817</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>44993</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61442,7 +61442,7 @@
         <v>44925</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45721</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>44777</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>45640</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45533</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>44621</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>46155</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45273</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45631</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45490</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>44953</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45175</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45947</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>44992</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45886</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>45469</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45916</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>45817</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>46111</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>44777</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>44704</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>46167</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63048,7 +63048,7 @@
         <v>45456</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63121,7 +63121,7 @@
         <v>45104</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45104</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         <v>44824</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>45644</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>45880</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63491,7 +63491,7 @@
         <v>45957</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63564,7 +63564,7 @@
         <v>45776</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63637,7 +63637,7 @@
         <v>45956</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>45128</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>45322</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63856,7 +63856,7 @@
         <v>46174</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45386</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64002,7 +64002,7 @@
         <v>45845</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         <v>45075</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64153,7 +64153,7 @@
         <v>45882</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>45075</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45075</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64372,7 +64372,7 @@
         <v>45075</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64445,7 +64445,7 @@
         <v>46178</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64518,7 +64518,7 @@
         <v>44525</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64591,7 +64591,7 @@
         <v>45092</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64664,7 +64664,7 @@
         <v>45092</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64737,7 +64737,7 @@
         <v>46178</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>44516</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>44546</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64961,7 +64961,7 @@
         <v>45610</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65034,7 +65034,7 @@
         <v>45411</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65185,7 +65185,7 @@
         <v>46177</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65331,7 +65331,7 @@
         <v>45239</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         <v>46181</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65477,7 +65477,7 @@
         <v>46181</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>45414</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46183</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46183</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65774,7 +65774,7 @@
         <v>46183</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>46188</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>44643</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65998,7 +65998,7 @@
         <v>46188</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66071,7 +66071,7 @@
         <v>46188</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>45456</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45020</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66290,7 +66290,7 @@
         <v>46189</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66363,7 +66363,7 @@
         <v>44882</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         <v>45075</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66509,7 +66509,7 @@
         <v>45075</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66582,7 +66582,7 @@
         <v>45075</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66655,7 +66655,7 @@
         <v>45075</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66728,7 +66728,7 @@
         <v>45771</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66801,7 +66801,7 @@
         <v>44596</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66874,7 +66874,7 @@
         <v>44596</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>45208</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>46077</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>46191</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>46191</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>45552</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         <v>46191</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>46195</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45183</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67536,7 +67536,7 @@
         <v>45293</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67614,7 +67614,7 @@
         <v>45755</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>44952</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67765,7 +67765,7 @@
         <v>44790</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67838,7 +67838,7 @@
         <v>44879</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67911,7 +67911,7 @@
         <v>46197</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67984,7 +67984,7 @@
         <v>45293</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68057,7 +68057,7 @@
         <v>45293</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>44775</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68203,7 +68203,7 @@
         <v>46197</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68276,7 +68276,7 @@
         <v>46197</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68349,7 +68349,7 @@
         <v>44490</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68422,7 +68422,7 @@
         <v>45586</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68495,7 +68495,7 @@
         <v>44648</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68568,7 +68568,7 @@
         <v>45957</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68646,7 +68646,7 @@
         <v>45740</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         <v>45740</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68792,7 +68792,7 @@
         <v>45085</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68865,7 +68865,7 @@
         <v>46202</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68938,7 +68938,7 @@
         <v>44953</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69011,7 +69011,7 @@
         <v>45617</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69084,7 +69084,7 @@
         <v>46203</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69157,7 +69157,7 @@
         <v>45065</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69235,7 +69235,7 @@
         <v>46203</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69308,7 +69308,7 @@
         <v>45068</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69381,7 +69381,7 @@
         <v>46204</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69454,7 +69454,7 @@
         <v>44644</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69527,7 +69527,7 @@
         <v>46204</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69600,7 +69600,7 @@
         <v>46206</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>44746</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69746,7 +69746,7 @@
         <v>45139</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69819,7 +69819,7 @@
         <v>45218</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69892,7 +69892,7 @@
         <v>46207</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69965,7 +69965,7 @@
         <v>46207</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70038,7 +70038,7 @@
         <v>45414</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70111,7 +70111,7 @@
         <v>44599</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70184,7 +70184,7 @@
         <v>45412</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70257,7 +70257,7 @@
         <v>46209</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70330,7 +70330,7 @@
         <v>45205</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70403,7 +70403,7 @@
         <v>45147</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70476,7 +70476,7 @@
         <v>45191</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70554,7 +70554,7 @@
         <v>45084</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70627,7 +70627,7 @@
         <v>45442</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70700,7 +70700,7 @@
         <v>44525</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70778,7 +70778,7 @@
         <v>44540</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70851,7 +70851,7 @@
         <v>46216</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70924,7 +70924,7 @@
         <v>44556</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70997,7 +70997,7 @@
         <v>46258</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71070,7 +71070,7 @@
         <v>46259</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71143,7 +71143,7 @@
         <v>46258</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71216,7 +71216,7 @@
         <v>45468</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71289,7 +71289,7 @@
         <v>46259</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71362,7 +71362,7 @@
         <v>46258</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71435,7 +71435,7 @@
         <v>46260</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71513,7 +71513,7 @@
         <v>45139</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71586,7 +71586,7 @@
         <v>46260</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71664,7 +71664,7 @@
         <v>46261</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71737,7 +71737,7 @@
         <v>46218</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71810,7 +71810,7 @@
         <v>46261</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71883,7 +71883,7 @@
         <v>44525</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71956,7 +71956,7 @@
         <v>45463</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72029,7 +72029,7 @@
         <v>46260</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72107,7 +72107,7 @@
         <v>46261</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72180,7 +72180,7 @@
         <v>45636</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72253,7 +72253,7 @@
         <v>45146</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72331,7 +72331,7 @@
         <v>44698</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72409,7 +72409,7 @@
         <v>45468</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72482,7 +72482,7 @@
         <v>46220</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72555,7 +72555,7 @@
         <v>44691</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72628,7 +72628,7 @@
         <v>46266</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72701,7 +72701,7 @@
         <v>46266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72774,7 +72774,7 @@
         <v>45356</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72847,7 +72847,7 @@
         <v>44816</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72920,7 +72920,7 @@
         <v>46265</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72993,7 +72993,7 @@
         <v>45107</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73066,7 +73066,7 @@
         <v>45075</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73139,7 +73139,7 @@
         <v>45075</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73212,7 +73212,7 @@
         <v>46266</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
         <v>46266</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73358,7 +73358,7 @@
         <v>46268</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73431,7 +73431,7 @@
         <v>46268</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73504,7 +73504,7 @@
         <v>46225</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>46272</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73650,7 +73650,7 @@
         <v>44764</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73723,7 +73723,7 @@
         <v>46261</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73796,7 +73796,7 @@
         <v>46261</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73869,7 +73869,7 @@
         <v>45238</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73942,7 +73942,7 @@
         <v>45261</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74015,7 +74015,7 @@
         <v>45524</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74088,7 +74088,7 @@
         <v>45245</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74161,7 +74161,7 @@
         <v>45454</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74234,7 +74234,7 @@
         <v>46274</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74312,7 +74312,7 @@
         <v>46237</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74385,7 +74385,7 @@
         <v>46238</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74458,7 +74458,7 @@
         <v>45231</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74531,7 +74531,7 @@
         <v>46254</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74604,7 +74604,7 @@
         <v>44866</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74677,7 +74677,7 @@
         <v>46239</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74750,7 +74750,7 @@
         <v>45082</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74823,7 +74823,7 @@
         <v>45082</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74896,7 +74896,7 @@
         <v>45260</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74969,7 +74969,7 @@
         <v>45260</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75042,7 +75042,7 @@
         <v>45617</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75115,7 +75115,7 @@
         <v>45063</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75188,7 +75188,7 @@
         <v>45721</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75261,7 +75261,7 @@
         <v>45055</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75334,7 +75334,7 @@
         <v>45614</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75407,7 +75407,7 @@
         <v>46239</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75480,7 +75480,7 @@
         <v>46283</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75553,7 +75553,7 @@
         <v>44714</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75626,7 +75626,7 @@
         <v>45687</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75704,7 +75704,7 @@
         <v>45225</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75777,7 +75777,7 @@
         <v>45253</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75850,7 +75850,7 @@
         <v>44851</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75923,7 +75923,7 @@
         <v>45042</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75996,7 +75996,7 @@
         <v>45414</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76069,7 +76069,7 @@
         <v>44585</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76147,7 +76147,7 @@
         <v>45469</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         <v>45385</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76293,7 +76293,7 @@
         <v>46241</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76366,7 +76366,7 @@
         <v>45202</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76439,7 +76439,7 @@
         <v>45075</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76512,7 +76512,7 @@
         <v>44743</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76590,7 +76590,7 @@
         <v>45054</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76663,7 +76663,7 @@
         <v>45054</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76736,7 +76736,7 @@
         <v>44925</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76809,7 +76809,7 @@
         <v>44760</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76882,7 +76882,7 @@
         <v>46288</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76955,7 +76955,7 @@
         <v>46288</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77028,7 +77028,7 @@
         <v>45644</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77101,7 +77101,7 @@
         <v>44621</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77174,7 +77174,7 @@
         <v>46246</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77247,7 +77247,7 @@
         <v>46289</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77320,7 +77320,7 @@
         <v>45183</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77393,7 +77393,7 @@
         <v>45089</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77466,7 +77466,7 @@
         <v>46289</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77539,7 +77539,7 @@
         <v>46289</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77612,7 +77612,7 @@
         <v>46289</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77685,7 +77685,7 @@
         <v>44719</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77758,7 +77758,7 @@
         <v>44698</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77831,7 +77831,7 @@
         <v>45519</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77904,7 +77904,7 @@
         <v>45170</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77977,7 +77977,7 @@
         <v>44549</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78050,7 +78050,7 @@
         <v>45601</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78123,7 +78123,7 @@
         <v>46247</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78196,7 +78196,7 @@
         <v>46247</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78269,7 +78269,7 @@
         <v>44516</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78347,7 +78347,7 @@
         <v>44516</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78425,7 +78425,7 @@
         <v>45448</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78498,7 +78498,7 @@
         <v>44782</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78571,7 +78571,7 @@
         <v>46284</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78644,7 +78644,7 @@
         <v>44753</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78717,7 +78717,7 @@
         <v>44902</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78790,7 +78790,7 @@
         <v>44795</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78863,7 +78863,7 @@
         <v>45518</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78936,7 +78936,7 @@
         <v>46247</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>45799</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79082,7 +79082,7 @@
         <v>46284</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79155,7 +79155,7 @@
         <v>46293</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79228,7 +79228,7 @@
         <v>46182</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79301,7 +79301,7 @@
         <v>46247</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79374,7 +79374,7 @@
         <v>45686</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79447,7 +79447,7 @@
         <v>45522</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>45357</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79593,7 +79593,7 @@
         <v>45147</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79666,7 +79666,7 @@
         <v>44923</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79739,7 +79739,7 @@
         <v>45212</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79812,7 +79812,7 @@
         <v>45119</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79885,7 +79885,7 @@
         <v>45668</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79958,7 +79958,7 @@
         <v>44682</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -80031,7 +80031,7 @@
         <v>44815</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80104,7 +80104,7 @@
         <v>44986</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80177,7 +80177,7 @@
         <v>45089</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80250,7 +80250,7 @@
         <v>46294</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80323,7 +80323,7 @@
         <v>45310</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80396,7 +80396,7 @@
         <v>44866</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80469,7 +80469,7 @@
         <v>44868</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80542,7 +80542,7 @@
         <v>44495</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80615,7 +80615,7 @@
         <v>44963</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80688,7 +80688,7 @@
         <v>44816</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80761,7 +80761,7 @@
         <v>46254</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80834,7 +80834,7 @@
         <v>45693</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80907,7 +80907,7 @@
         <v>46254</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80985,7 +80985,7 @@
         <v>46254</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81063,7 +81063,7 @@
         <v>45728</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81136,7 +81136,7 @@
         <v>45558</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81209,7 +81209,7 @@
         <v>44956</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81282,7 +81282,7 @@
         <v>44956</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81355,7 +81355,7 @@
         <v>46255</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81428,7 +81428,7 @@
         <v>44684</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81501,7 +81501,7 @@
         <v>45253</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81574,7 +81574,7 @@
         <v>44980</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81647,7 +81647,7 @@
         <v>45174</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81725,7 +81725,7 @@
         <v>45232</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81798,7 +81798,7 @@
         <v>45075</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81871,7 +81871,7 @@
         <v>45468</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81944,7 +81944,7 @@
         <v>44938</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -82017,7 +82017,7 @@
         <v>44806</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82090,7 +82090,7 @@
         <v>44934</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82163,7 +82163,7 @@
         <v>44799</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82236,7 +82236,7 @@
         <v>45063</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82309,7 +82309,7 @@
         <v>45075</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82382,7 +82382,7 @@
         <v>45245</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82455,7 +82455,7 @@
         <v>45245</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82528,7 +82528,7 @@
         <v>44750</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82601,7 +82601,7 @@
         <v>44750</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82674,7 +82674,7 @@
         <v>45075</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82747,7 +82747,7 @@
         <v>45338</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82820,7 +82820,7 @@
         <v>45254</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82893,7 +82893,7 @@
         <v>45775</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -82966,7 +82966,7 @@
         <v>44693</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83039,7 +83039,7 @@
         <v>44769</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83112,7 +83112,7 @@
         <v>45113</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83185,7 +83185,7 @@
         <v>45328</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83258,7 +83258,7 @@
         <v>45348</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83336,7 +83336,7 @@
         <v>44490</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83409,7 +83409,7 @@
         <v>45316</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83482,7 +83482,7 @@
         <v>45253</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83555,7 +83555,7 @@
         <v>45190</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83628,7 +83628,7 @@
         <v>45783</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83701,7 +83701,7 @@
         <v>45783</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83774,7 +83774,7 @@
         <v>45408</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83847,7 +83847,7 @@
         <v>43943</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83920,7 +83920,7 @@
         <v>43969</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -83993,7 +83993,7 @@
         <v>44959</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84066,7 +84066,7 @@
         <v>44099</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84139,7 +84139,7 @@
         <v>44854</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84212,7 +84212,7 @@
         <v>44599</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84285,7 +84285,7 @@
         <v>45260</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84358,7 +84358,7 @@
         <v>44638</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84436,7 +84436,7 @@
         <v>45366</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84509,7 +84509,7 @@
         <v>44652</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84582,7 +84582,7 @@
         <v>45537</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84655,7 +84655,7 @@
         <v>44627</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84728,7 +84728,7 @@
         <v>44497</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84801,7 +84801,7 @@
         <v>44558</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84874,7 +84874,7 @@
         <v>44497</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84947,7 +84947,7 @@
         <v>44971</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -85020,7 +85020,7 @@
         <v>44574</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85093,7 +85093,7 @@
         <v>44690</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85166,7 +85166,7 @@
         <v>45569</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85239,7 +85239,7 @@
         <v>45188</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85312,7 +85312,7 @@
         <v>44973</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85385,7 +85385,7 @@
         <v>45183</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85458,7 +85458,7 @@
         <v>44973</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85531,7 +85531,7 @@
         <v>45817</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -85604,7 +85604,7 @@
         <v>45807</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -85677,7 +85677,7 @@
         <v>46062</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>46062</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -85823,7 +85823,7 @@
         <v>46188</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -85896,7 +85896,7 @@
         <v>44614</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44482</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44550</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45418</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44949</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45800</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44571</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>46107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45994</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>43969</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>44858</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45104</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45684</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44949</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44650</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45068</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45540</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46107</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45960</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44706</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45112</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44956</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45485</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45783</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45664</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45581</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>46204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>46247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44972</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44749</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45082</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44872</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44855</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44778</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45821</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44683</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44679</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44843</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44763</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44695</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45609</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45169</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44985</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44698</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44866</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44771</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>46027</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>46183</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>46183</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>46301</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>44629</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44880</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44502</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44594</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45383</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45548</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44956</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45118</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45803</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45070</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45945</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45226</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45293</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44863</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46150</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>46150</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>46247</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>46295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44678</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>44896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>44868</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45081</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44760</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45730</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44778</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44483</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45223</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45205</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45457</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44705</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44869</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44637</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45418</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45473</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>44592</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45260</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44620</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45177</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45794</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45113</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44867</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45532</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45549</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>44649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44963</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45112</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45687</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45608</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44489</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45623</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45687</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44797</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45826</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45957</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45855</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44704</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45450</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45708</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44955</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45987</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45992</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45764</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>44747</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>46133</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45840</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44813</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>46010</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45007</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46062</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45904</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>46093</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>46204</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45960</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46301</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44639</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44917</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44518</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44650</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44833</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44777</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>44634</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>44581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>44560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>44771</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44524</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44574</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44834</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44626</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44496</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44682</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44690</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44708</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44642</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44776</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44746</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44543</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>44543</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44845</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>44495</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44882</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44545</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44722</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>44742</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44756</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44806</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44511</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44510</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44867</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44511</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44637</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44735</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>44683</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44580</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44763</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>44539</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44665</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44642</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44516</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44777</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>44496</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44637</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>44655</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>44735</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44637</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>44595</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44607</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44524</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>44712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44769</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44744</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44698</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44575</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44826</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44543</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>44543</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>44760</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>44545</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44609</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44572</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44817</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44845</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>44650</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44621</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44526</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44496</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44725</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44584</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44678</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44682</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44682</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45063</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45065</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44623</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44665</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>44665</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44533</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44704</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44543</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44682</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>44523</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44595</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44725</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45414</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44815</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45469</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45225</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44495</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45139</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45330</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45082</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45218</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45621</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44760</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44816</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45356</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45089</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45482</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>44956</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>44840</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45433</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45435</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45084</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44743</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45257</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44803</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45740</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45740</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45344</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45273</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45075</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45075</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>44764</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45051</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45749</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45362</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44895</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44687</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45231</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>44992</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45054</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45054</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45450</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45450</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45755</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45203</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45239</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45022</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44845</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>44824</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45558</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45454</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44809</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45202</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44643</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45075</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45075</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45075</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45075</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45625</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>44962</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45089</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44949</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>44953</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45208</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44866</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44879</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44963</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45530</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45448</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>44833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45218</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>44817</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45084</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44882</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45022</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45455</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45147</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>44525</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44841</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45518</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>44556</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45757</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45063</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>44956</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>45721</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45119</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45463</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45708</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45468</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44934</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44778</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44581</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44516</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45376</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45293</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45245</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45245</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>44834</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44956</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44931</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45460</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45293</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44621</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>44868</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45524</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45888</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45617</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45341</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45104</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>44900</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45813</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45376</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>44952</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44510</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45245</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45356</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45469</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45469</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45092</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45576</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>44816</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45894</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45894</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45859</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45893</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45859</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45893</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45894</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45896</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45898</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45898</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45897</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45897</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45075</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45427</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45490</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45357</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45721</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45600</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45644</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45086</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45253</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45737</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45586</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45175</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>44540</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45414</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45089</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45385</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44904</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45536</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44901</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45908</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45772</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45170</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45259</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44525</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>44546</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>44516</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>44516</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45075</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45468</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45253</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45316</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45075</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45910</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45190</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45610</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44769</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45831</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44993</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45271</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45642</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45783</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45531</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>44637</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44525</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>45783</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45443</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45385</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45245</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45549</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45442</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45155</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45187</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45735</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45709</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45918</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>44938</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45572</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44953</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45533</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45547</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45786</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45537</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45579</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44584</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45352</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45721</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>44578</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44902</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45408</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45923</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45853</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45635</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45687</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44795</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45075</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45075</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45075</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45089</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45203</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>44923</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>45412</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>44585</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45552</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>45272</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44596</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>44945</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45385</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45729</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45636</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>44937</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45713</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45145</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45436</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45518</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45215</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45475</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45639</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45155</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45254</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>45260</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45260</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>44714</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45644</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>44708</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45930</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45450</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45798</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44580</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45930</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45930</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45113</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>44673</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51320,7 +51320,7 @@
         <v>45798</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45798</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51466,7 +51466,7 @@
         <v>45936</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>44648</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>45205</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44643</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>45935</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45701</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45800</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45933</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>44816</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45456</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45617</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>44611</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45803</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45933</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45121</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45224</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>44986</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>44813</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45937</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45586</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>44775</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52999,7 +52999,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53072,7 +53072,7 @@
         <v>45937</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>45232</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>45376</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45790</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45183</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>45810</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>44644</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>44693</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45810</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>44635</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>44670</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>45810</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45695</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>44867</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45208</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45944</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>45202</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>45075</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45813</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45348</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>44624</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45376</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>44803</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>44687</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45817</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>45775</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>45693</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45747</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45092</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45092</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45146</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55438,7 +55438,7 @@
         <v>45075</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>45522</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45685</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>45824</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45757</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55808,7 +55808,7 @@
         <v>45174</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45686</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55959,7 +55959,7 @@
         <v>45636</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>44704</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>45020</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45139</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45614</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>45208</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>45208</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>44704</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45237</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56616,7 +56616,7 @@
         <v>45145</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45952</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>45022</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>45831</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56908,7 +56908,7 @@
         <v>45168</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>44790</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45951</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45957</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45954</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45956</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45957</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>45960</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45411</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>44953</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45245</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>45834</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45519</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45107</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45834</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45111</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>44708</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>44708</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>44746</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58320,7 +58320,7 @@
         <v>45834</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>45835</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>44684</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>45127</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>44743</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>44974</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>44732</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>45840</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>44771</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45208</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59133,7 +59133,7 @@
         <v>45839</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59206,7 +59206,7 @@
         <v>45609</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59279,7 +59279,7 @@
         <v>44743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45601</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>45581</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59503,7 +59503,7 @@
         <v>45177</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59576,7 +59576,7 @@
         <v>45128</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45152</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59722,7 +59722,7 @@
         <v>44763</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45971</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>44495</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59946,7 +59946,7 @@
         <v>44799</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>44749</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>44782</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45293</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45973</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60316,7 +60316,7 @@
         <v>45852</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>44719</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45855</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60540,7 +60540,7 @@
         <v>45855</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>44980</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>45700</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45707</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>44777</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45085</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45254</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45243</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>45776</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>44760</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45042</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61353,7 +61353,7 @@
         <v>45219</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61426,7 +61426,7 @@
         <v>45442</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45446</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45525</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45068</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
         <v>44925</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>45063</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>45191</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>44806</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>44510</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62093,7 +62093,7 @@
         <v>44783</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>45776</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>44815</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62312,7 +62312,7 @@
         <v>44785</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45394</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>45771</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>45880</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62614,7 +62614,7 @@
         <v>45019</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62687,7 +62687,7 @@
         <v>45730</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62760,7 +62760,7 @@
         <v>45386</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62833,7 +62833,7 @@
         <v>45554</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62906,7 +62906,7 @@
         <v>45882</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>45631</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63052,7 +63052,7 @@
         <v>44670</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>44769</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>46094</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63276,7 +63276,7 @@
         <v>45982</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63354,7 +63354,7 @@
         <v>44851</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63427,7 +63427,7 @@
         <v>45401</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>46100</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>45054</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63646,7 +63646,7 @@
         <v>46100</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63719,7 +63719,7 @@
         <v>45208</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63792,7 +63792,7 @@
         <v>45238</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>44698</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         <v>45469</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>44621</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64084,7 +64084,7 @@
         <v>45212</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>45985</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64235,7 +64235,7 @@
         <v>45640</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>45236</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64381,7 +64381,7 @@
         <v>45055</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64454,7 +64454,7 @@
         <v>45328</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64527,7 +64527,7 @@
         <v>45075</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64600,7 +64600,7 @@
         <v>45721</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64673,7 +64673,7 @@
         <v>45992</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64746,7 +64746,7 @@
         <v>46113</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>45456</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64892,7 +64892,7 @@
         <v>44596</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -64970,7 +64970,7 @@
         <v>45994</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>44549</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65116,7 +65116,7 @@
         <v>45531</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>45993</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>46119</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65335,7 +65335,7 @@
         <v>46119</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65413,7 +65413,7 @@
         <v>46119</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>44691</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>46119</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>45994</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         <v>44908</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>45994</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>45993</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>45518</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>45996</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>45999</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>46000</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66226,7 +66226,7 @@
         <v>45033</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66299,7 +66299,7 @@
         <v>46107</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66372,7 +66372,7 @@
         <v>46002</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>44769</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         <v>45183</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>46132</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>46002</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>46000</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66810,7 +66810,7 @@
         <v>44854</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>46001</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         <v>44778</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67029,7 +67029,7 @@
         <v>44832</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>46134</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67175,7 +67175,7 @@
         <v>46133</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>44682</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>45638</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67399,7 +67399,7 @@
         <v>46008</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67477,7 +67477,7 @@
         <v>45587</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67550,7 +67550,7 @@
         <v>45085</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67628,7 +67628,7 @@
         <v>45712</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67706,7 +67706,7 @@
         <v>45898</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67779,7 +67779,7 @@
         <v>45700</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67857,7 +67857,7 @@
         <v>46008</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67930,7 +67930,7 @@
         <v>46119</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68008,7 +68008,7 @@
         <v>45735</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68081,7 +68081,7 @@
         <v>44925</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68154,7 +68154,7 @@
         <v>45847</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68232,7 +68232,7 @@
         <v>46135</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>44866</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>45561</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68451,7 +68451,7 @@
         <v>45835</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68529,7 +68529,7 @@
         <v>46009</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68602,7 +68602,7 @@
         <v>45435</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68675,7 +68675,7 @@
         <v>44922</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68748,7 +68748,7 @@
         <v>44767</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         <v>44490</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68894,7 +68894,7 @@
         <v>44490</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68967,7 +68967,7 @@
         <v>44995</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69040,7 +69040,7 @@
         <v>44750</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69113,7 +69113,7 @@
         <v>44750</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69186,7 +69186,7 @@
         <v>45903</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69264,7 +69264,7 @@
         <v>45338</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69337,7 +69337,7 @@
         <v>45082</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69410,7 +69410,7 @@
         <v>45082</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>45490</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>45667</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>45853</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>46029</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69780,7 +69780,7 @@
         <v>45953</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69853,7 +69853,7 @@
         <v>45817</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69926,7 +69926,7 @@
         <v>45468</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -69999,7 +69999,7 @@
         <v>45261</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70072,7 +70072,7 @@
         <v>46030</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70145,7 +70145,7 @@
         <v>46029</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70218,7 +70218,7 @@
         <v>46029</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70291,7 +70291,7 @@
         <v>45253</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70364,7 +70364,7 @@
         <v>45621</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70442,7 +70442,7 @@
         <v>45797</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70515,7 +70515,7 @@
         <v>45953</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70588,7 +70588,7 @@
         <v>45835</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70666,7 +70666,7 @@
         <v>46034</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70739,7 +70739,7 @@
         <v>44938</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70812,7 +70812,7 @@
         <v>46034</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70890,7 +70890,7 @@
         <v>44753</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70963,7 +70963,7 @@
         <v>45880</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71041,7 +71041,7 @@
         <v>46036</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71114,7 +71114,7 @@
         <v>46036</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71187,7 +71187,7 @@
         <v>44698</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71265,7 +71265,7 @@
         <v>45391</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71338,7 +71338,7 @@
         <v>45670</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71411,7 +71411,7 @@
         <v>44777</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71484,7 +71484,7 @@
         <v>46042</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71557,7 +71557,7 @@
         <v>45668</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71630,7 +71630,7 @@
         <v>45670</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71703,7 +71703,7 @@
         <v>44599</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71776,7 +71776,7 @@
         <v>45587</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>44743</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71927,7 +71927,7 @@
         <v>45640</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72000,7 +72000,7 @@
         <v>45706</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72078,7 +72078,7 @@
         <v>45723</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72156,7 +72156,7 @@
         <v>44858</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46043</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72302,7 +72302,7 @@
         <v>45453</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72375,7 +72375,7 @@
         <v>45971</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72448,7 +72448,7 @@
         <v>45310</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72521,7 +72521,7 @@
         <v>45310</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72594,7 +72594,7 @@
         <v>46047</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72667,7 +72667,7 @@
         <v>44700</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72740,7 +72740,7 @@
         <v>45254</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>46049</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>46049</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72959,7 +72959,7 @@
         <v>46049</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73032,7 +73032,7 @@
         <v>46049</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73105,7 +73105,7 @@
         <v>45089</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73178,7 +73178,7 @@
         <v>45159</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73251,7 +73251,7 @@
         <v>45322</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73324,7 +73324,7 @@
         <v>45800</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73397,7 +73397,7 @@
         <v>46052</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73475,7 +73475,7 @@
         <v>45890</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73548,7 +73548,7 @@
         <v>46056</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73626,7 +73626,7 @@
         <v>46058</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46057</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46057</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73860,7 +73860,7 @@
         <v>46057</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73938,7 +73938,7 @@
         <v>45813</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74016,7 +74016,7 @@
         <v>46061</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>46062</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74167,7 +74167,7 @@
         <v>46063</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74240,7 +74240,7 @@
         <v>46063</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74313,7 +74313,7 @@
         <v>46065</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74386,7 +74386,7 @@
         <v>46065</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46065</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74532,7 +74532,7 @@
         <v>46069</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74610,7 +74610,7 @@
         <v>46150</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74683,7 +74683,7 @@
         <v>46069</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>46069</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>46150</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>46150</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74985,7 +74985,7 @@
         <v>46072</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75058,7 +75058,7 @@
         <v>46077</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75136,7 +75136,7 @@
         <v>46077</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75214,7 +75214,7 @@
         <v>46077</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75292,7 +75292,7 @@
         <v>46077</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>46155</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>46084</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75516,7 +75516,7 @@
         <v>45817</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75589,7 +75589,7 @@
         <v>45947</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75662,7 +75662,7 @@
         <v>46111</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75735,7 +75735,7 @@
         <v>46093</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75808,7 +75808,7 @@
         <v>46094</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75886,7 +75886,7 @@
         <v>46094</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75964,7 +75964,7 @@
         <v>45886</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>45916</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76110,7 +76110,7 @@
         <v>45817</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76183,7 +76183,7 @@
         <v>46167</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76256,7 +76256,7 @@
         <v>45957</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76329,7 +76329,7 @@
         <v>45956</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76402,7 +76402,7 @@
         <v>46174</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76475,7 +76475,7 @@
         <v>45845</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76548,7 +76548,7 @@
         <v>46177</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76621,7 +76621,7 @@
         <v>46177</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76694,7 +76694,7 @@
         <v>46178</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76767,7 +76767,7 @@
         <v>46181</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76845,7 +76845,7 @@
         <v>46181</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76918,7 +76918,7 @@
         <v>46178</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -76991,7 +76991,7 @@
         <v>46178</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77064,7 +77064,7 @@
         <v>46183</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77142,7 +77142,7 @@
         <v>46183</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77215,7 +77215,7 @@
         <v>46183</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77288,7 +77288,7 @@
         <v>46189</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77361,7 +77361,7 @@
         <v>46188</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77434,7 +77434,7 @@
         <v>46188</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77507,7 +77507,7 @@
         <v>46188</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77580,7 +77580,7 @@
         <v>46191</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77653,7 +77653,7 @@
         <v>46191</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77726,7 +77726,7 @@
         <v>46191</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77799,7 +77799,7 @@
         <v>46077</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77872,7 +77872,7 @@
         <v>46195</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77945,7 +77945,7 @@
         <v>46197</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78018,7 +78018,7 @@
         <v>46197</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78091,7 +78091,7 @@
         <v>46197</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78164,7 +78164,7 @@
         <v>45957</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78242,7 +78242,7 @@
         <v>46202</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78315,7 +78315,7 @@
         <v>46203</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78388,7 +78388,7 @@
         <v>46203</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78461,7 +78461,7 @@
         <v>46204</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78534,7 +78534,7 @@
         <v>46204</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78607,7 +78607,7 @@
         <v>46207</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78680,7 +78680,7 @@
         <v>46206</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78753,7 +78753,7 @@
         <v>46209</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78826,7 +78826,7 @@
         <v>46216</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78899,7 +78899,7 @@
         <v>46218</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -78972,7 +78972,7 @@
         <v>46220</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79045,7 +79045,7 @@
         <v>46265</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79118,7 +79118,7 @@
         <v>46225</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79191,7 +79191,7 @@
         <v>46268</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79264,7 +79264,7 @@
         <v>46268</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79337,7 +79337,7 @@
         <v>46266</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79410,7 +79410,7 @@
         <v>46266</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79483,7 +79483,7 @@
         <v>46266</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79556,7 +79556,7 @@
         <v>46266</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79629,7 +79629,7 @@
         <v>46274</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79707,7 +79707,7 @@
         <v>46272</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79780,7 +79780,7 @@
         <v>46237</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79853,7 +79853,7 @@
         <v>46238</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79926,7 +79926,7 @@
         <v>46239</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -79999,7 +79999,7 @@
         <v>46239</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80072,7 +80072,7 @@
         <v>46241</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80145,7 +80145,7 @@
         <v>46283</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80218,7 +80218,7 @@
         <v>45414</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80291,7 +80291,7 @@
         <v>46288</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80364,7 +80364,7 @@
         <v>46288</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80437,7 +80437,7 @@
         <v>46289</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80510,7 +80510,7 @@
         <v>46289</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80583,7 +80583,7 @@
         <v>46289</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80656,7 +80656,7 @@
         <v>46182</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80729,7 +80729,7 @@
         <v>46284</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80802,7 +80802,7 @@
         <v>46284</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80875,7 +80875,7 @@
         <v>46247</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80948,7 +80948,7 @@
         <v>46247</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81021,7 +81021,7 @@
         <v>46247</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81094,7 +81094,7 @@
         <v>46289</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81167,7 +81167,7 @@
         <v>46247</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81240,7 +81240,7 @@
         <v>46246</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81313,7 +81313,7 @@
         <v>46293</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81386,7 +81386,7 @@
         <v>46294</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81459,7 +81459,7 @@
         <v>45728</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81532,7 +81532,7 @@
         <v>46254</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81610,7 +81610,7 @@
         <v>46254</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81688,7 +81688,7 @@
         <v>46254</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81761,7 +81761,7 @@
         <v>46300</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81834,7 +81834,7 @@
         <v>46255</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81907,7 +81907,7 @@
         <v>46259</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -81980,7 +81980,7 @@
         <v>46258</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82053,7 +82053,7 @@
         <v>46258</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82126,7 +82126,7 @@
         <v>46259</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82199,7 +82199,7 @@
         <v>46258</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82272,7 +82272,7 @@
         <v>46261</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82345,7 +82345,7 @@
         <v>45952</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82418,7 +82418,7 @@
         <v>46254</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82491,7 +82491,7 @@
         <v>46261</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82564,7 +82564,7 @@
         <v>45799</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82637,7 +82637,7 @@
         <v>45890</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82710,7 +82710,7 @@
         <v>46261</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82783,7 +82783,7 @@
         <v>46261</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82856,7 +82856,7 @@
         <v>46261</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -82929,7 +82929,7 @@
         <v>46260</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83007,7 +83007,7 @@
         <v>46304</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83080,7 +83080,7 @@
         <v>46207</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83153,7 +83153,7 @@
         <v>44099</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83226,7 +83226,7 @@
         <v>43969</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83299,7 +83299,7 @@
         <v>44959</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83372,7 +83372,7 @@
         <v>43943</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83445,7 +83445,7 @@
         <v>44599</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83518,7 +83518,7 @@
         <v>44638</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>44652</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>44627</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83742,7 +83742,7 @@
         <v>44558</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83815,7 +83815,7 @@
         <v>44574</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83888,7 +83888,7 @@
         <v>44690</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -83961,7 +83961,7 @@
         <v>44854</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84034,7 +84034,7 @@
         <v>45260</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84107,7 +84107,7 @@
         <v>45366</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84180,7 +84180,7 @@
         <v>45537</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84253,7 +84253,7 @@
         <v>44497</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84326,7 +84326,7 @@
         <v>44497</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84399,7 +84399,7 @@
         <v>44971</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84472,7 +84472,7 @@
         <v>45569</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84545,7 +84545,7 @@
         <v>45188</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84618,7 +84618,7 @@
         <v>44973</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84691,7 +84691,7 @@
         <v>45183</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84764,7 +84764,7 @@
         <v>44973</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84837,7 +84837,7 @@
         <v>45817</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84910,7 +84910,7 @@
         <v>45807</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -84983,7 +84983,7 @@
         <v>46062</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85056,7 +85056,7 @@
         <v>46062</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85129,7 +85129,7 @@
         <v>46188</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85202,7 +85202,7 @@
         <v>44614</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>46181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44482</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44550</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45418</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44949</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45800</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>44571</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>46107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45994</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>43969</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>44858</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45104</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45684</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44949</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44650</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45068</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>45540</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46107</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>45960</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44706</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45112</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44956</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45485</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45783</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45664</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45581</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>46204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>46247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44972</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44749</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45082</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44872</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44855</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44778</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45821</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44683</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44743</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44679</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44843</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44763</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44695</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45609</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44743</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45169</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44985</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44698</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44866</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44771</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>46027</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>46183</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>46183</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>46301</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>44629</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45642</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44880</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44502</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44594</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45383</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45548</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44956</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45118</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45803</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45070</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45945</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45226</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45293</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44863</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46150</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>46150</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46288</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>46247</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>46295</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44678</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>44896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>44868</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45081</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44760</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45730</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44778</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44483</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45223</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45205</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45457</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44705</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44869</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44637</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45418</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45473</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>44592</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45260</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44620</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45177</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45794</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45113</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44867</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45532</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45549</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>44649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44963</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45112</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45687</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45608</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44489</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45623</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45687</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44797</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45826</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45957</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45855</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44704</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45450</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45708</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44955</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45987</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45992</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45764</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>44747</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>46133</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45840</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44813</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>46010</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45007</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46062</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45904</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>46093</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>46204</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45960</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46301</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44639</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44917</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44518</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44650</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44833</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44777</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>44634</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>44581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>44560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>44771</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44524</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44574</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44834</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44626</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44496</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44682</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44690</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44708</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44642</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44776</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44746</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44543</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>44543</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44845</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>44495</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44882</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44545</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44722</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>44742</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44756</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44806</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44511</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44510</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44867</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44511</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44637</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44735</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>44683</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44580</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44763</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>44539</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44665</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44642</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44516</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44777</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>44496</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>44637</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>44655</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>44735</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44637</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>44595</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44607</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44524</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>44712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44769</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44744</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44698</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44575</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44826</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44543</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>44543</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>44760</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>44545</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44609</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44572</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44817</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44845</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>44650</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44621</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44526</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44496</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44725</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44584</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44678</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44682</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44682</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45063</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45065</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44623</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44665</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>44665</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44533</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44704</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44543</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44682</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>44523</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44595</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44725</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45414</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44815</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45469</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45225</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44495</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45139</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45330</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45082</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>45218</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45621</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44760</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44816</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45356</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45089</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45482</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>44956</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>44840</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45433</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45435</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45084</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44743</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45257</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44803</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45740</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45740</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45344</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45273</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45075</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45075</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>44764</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45051</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45749</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45362</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>44895</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44687</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45231</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>44992</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45054</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45054</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>45450</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45450</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45755</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45203</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45239</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45022</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44845</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>44824</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45558</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45454</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>44809</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45202</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44643</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45075</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45075</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45075</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45075</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45625</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>44962</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45089</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44949</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>44953</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45208</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44866</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44879</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44963</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45530</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45448</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>44833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45218</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>44817</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45084</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44882</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45022</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45455</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45147</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>44525</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44841</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45518</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>44556</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45757</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45063</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>44956</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>45721</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45119</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45463</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45708</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45468</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44934</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44778</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44581</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44516</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45376</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45293</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45245</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45245</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>44834</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44956</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44931</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45460</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>45293</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44621</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>44868</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45524</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45888</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45617</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45341</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45104</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>44900</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45813</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45376</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>44952</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44510</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45245</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45356</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45469</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45469</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45092</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45576</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>44816</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45894</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45894</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45859</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45893</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45859</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45893</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45894</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45896</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45898</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45898</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45897</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45897</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45075</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45427</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45490</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45357</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45721</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45600</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45644</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45086</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45253</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45737</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45586</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45175</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>44540</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45414</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45089</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45385</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45831</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44904</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45536</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44901</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45908</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45772</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45170</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45259</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44525</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>44546</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>44516</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>44516</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45075</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45468</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45253</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45316</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45075</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45910</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45190</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45610</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44769</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45831</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44993</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45271</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45642</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45783</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45531</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>44637</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44525</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>45783</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45443</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45385</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45245</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45549</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45442</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45155</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45187</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45735</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45709</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45918</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>44938</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45572</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44953</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45533</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45547</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45786</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45537</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45579</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44584</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45352</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45721</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>44578</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44902</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45408</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45923</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45853</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45635</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45687</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44795</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45075</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45075</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45075</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45089</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45203</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>44923</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>45412</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>44585</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45552</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>45272</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44596</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>44945</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45385</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45729</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45636</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>44937</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45713</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45145</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45436</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45518</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45215</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45475</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45639</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45155</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45254</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>45260</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>45260</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>44714</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45644</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>44708</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45930</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45450</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45798</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44580</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45930</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45930</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45113</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>44673</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51320,7 +51320,7 @@
         <v>45798</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45798</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51466,7 +51466,7 @@
         <v>45936</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>44648</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>45205</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44643</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>45935</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45701</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45800</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45933</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>44816</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45456</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45617</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>44611</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45803</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45933</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45121</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45224</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>44986</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>44813</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45937</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45586</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>44775</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52999,7 +52999,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53072,7 +53072,7 @@
         <v>45937</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>45232</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>45376</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45790</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45183</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>45810</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>44644</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>44693</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45810</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>44635</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>44670</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>45810</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45695</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>44867</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45208</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45944</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>45202</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>45075</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45813</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45348</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>44624</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45376</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>44803</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>44687</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45817</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>45775</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>45693</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45747</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45092</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45092</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45146</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55438,7 +55438,7 @@
         <v>45075</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>45522</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45685</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>45824</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55735,7 +55735,7 @@
         <v>45757</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55808,7 +55808,7 @@
         <v>45174</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55886,7 +55886,7 @@
         <v>45686</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55959,7 +55959,7 @@
         <v>45636</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>44704</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>45020</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45139</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45614</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>45208</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>45208</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>44704</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45237</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56616,7 +56616,7 @@
         <v>45145</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45952</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>45022</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>45831</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56908,7 +56908,7 @@
         <v>45168</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>44790</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45951</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45957</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45954</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45956</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45957</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>45960</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45411</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>44953</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45245</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>45834</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45519</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45107</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45834</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45111</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>44708</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>44708</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>44746</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58320,7 +58320,7 @@
         <v>45834</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>45835</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>44684</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>45127</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>44743</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>44974</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>44732</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>45840</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>44771</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45208</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59133,7 +59133,7 @@
         <v>45839</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59206,7 +59206,7 @@
         <v>45609</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59279,7 +59279,7 @@
         <v>44743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45601</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>45581</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59503,7 +59503,7 @@
         <v>45177</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59576,7 +59576,7 @@
         <v>45128</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45152</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59722,7 +59722,7 @@
         <v>44763</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45971</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>44495</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59946,7 +59946,7 @@
         <v>44799</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>44749</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>44782</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45293</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45973</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60316,7 +60316,7 @@
         <v>45852</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>44719</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45855</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60540,7 +60540,7 @@
         <v>45855</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>44980</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>45700</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45707</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>44777</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45085</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45254</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45243</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>45776</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>44760</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45042</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61353,7 +61353,7 @@
         <v>45219</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61426,7 +61426,7 @@
         <v>45442</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45446</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45525</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45068</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
         <v>44925</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>45063</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>45191</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>44806</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>44510</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62093,7 +62093,7 @@
         <v>44783</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>45776</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>44815</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62312,7 +62312,7 @@
         <v>44785</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45394</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>45771</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>45880</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62614,7 +62614,7 @@
         <v>45019</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62687,7 +62687,7 @@
         <v>45730</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62760,7 +62760,7 @@
         <v>45386</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62833,7 +62833,7 @@
         <v>45554</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62906,7 +62906,7 @@
         <v>45882</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>45631</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63052,7 +63052,7 @@
         <v>44670</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>44769</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>46094</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63276,7 +63276,7 @@
         <v>45982</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63354,7 +63354,7 @@
         <v>44851</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63427,7 +63427,7 @@
         <v>45401</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>46100</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>45054</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63646,7 +63646,7 @@
         <v>46100</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63719,7 +63719,7 @@
         <v>45208</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63792,7 +63792,7 @@
         <v>45238</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>44698</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         <v>45469</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>44621</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64084,7 +64084,7 @@
         <v>45212</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>45985</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64235,7 +64235,7 @@
         <v>45640</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>45236</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64381,7 +64381,7 @@
         <v>45055</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64454,7 +64454,7 @@
         <v>45328</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64527,7 +64527,7 @@
         <v>45075</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64600,7 +64600,7 @@
         <v>45721</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64673,7 +64673,7 @@
         <v>45992</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64746,7 +64746,7 @@
         <v>46113</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>45456</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64892,7 +64892,7 @@
         <v>44596</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -64970,7 +64970,7 @@
         <v>45994</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>44549</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65116,7 +65116,7 @@
         <v>45531</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>45993</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>46119</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65335,7 +65335,7 @@
         <v>46119</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65413,7 +65413,7 @@
         <v>46119</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>44691</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>46119</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>45994</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         <v>44908</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>45994</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>45993</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>45518</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>45996</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>45999</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>46000</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66226,7 +66226,7 @@
         <v>45033</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66299,7 +66299,7 @@
         <v>46107</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66372,7 +66372,7 @@
         <v>46002</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>44769</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         <v>45183</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>46132</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>46002</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66737,7 +66737,7 @@
         <v>46000</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66810,7 +66810,7 @@
         <v>44854</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>46001</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         <v>44778</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67029,7 +67029,7 @@
         <v>44832</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>46134</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67175,7 +67175,7 @@
         <v>46133</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67248,7 +67248,7 @@
         <v>44682</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>45638</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67399,7 +67399,7 @@
         <v>46008</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67477,7 +67477,7 @@
         <v>45587</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67550,7 +67550,7 @@
         <v>45085</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67628,7 +67628,7 @@
         <v>45712</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67706,7 +67706,7 @@
         <v>45898</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67779,7 +67779,7 @@
         <v>45700</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67857,7 +67857,7 @@
         <v>46008</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67930,7 +67930,7 @@
         <v>46119</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68008,7 +68008,7 @@
         <v>45735</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68081,7 +68081,7 @@
         <v>44925</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68154,7 +68154,7 @@
         <v>45847</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68232,7 +68232,7 @@
         <v>46135</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>44866</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>45561</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68451,7 +68451,7 @@
         <v>45835</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68529,7 +68529,7 @@
         <v>46009</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68602,7 +68602,7 @@
         <v>45435</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68675,7 +68675,7 @@
         <v>44922</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68748,7 +68748,7 @@
         <v>44767</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         <v>44490</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68894,7 +68894,7 @@
         <v>44490</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68967,7 +68967,7 @@
         <v>44995</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69040,7 +69040,7 @@
         <v>44750</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69113,7 +69113,7 @@
         <v>44750</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69186,7 +69186,7 @@
         <v>45903</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69264,7 +69264,7 @@
         <v>45338</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69337,7 +69337,7 @@
         <v>45082</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69410,7 +69410,7 @@
         <v>45082</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>45490</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>45667</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69634,7 +69634,7 @@
         <v>45853</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>46029</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69780,7 +69780,7 @@
         <v>45953</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69853,7 +69853,7 @@
         <v>45817</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69926,7 +69926,7 @@
         <v>45468</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -69999,7 +69999,7 @@
         <v>45261</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70072,7 +70072,7 @@
         <v>46030</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70145,7 +70145,7 @@
         <v>46029</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70218,7 +70218,7 @@
         <v>46029</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70291,7 +70291,7 @@
         <v>45253</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70364,7 +70364,7 @@
         <v>45621</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70442,7 +70442,7 @@
         <v>45797</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70515,7 +70515,7 @@
         <v>45953</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70588,7 +70588,7 @@
         <v>45835</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70666,7 +70666,7 @@
         <v>46034</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70739,7 +70739,7 @@
         <v>44938</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70812,7 +70812,7 @@
         <v>46034</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70890,7 +70890,7 @@
         <v>44753</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70963,7 +70963,7 @@
         <v>45880</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71041,7 +71041,7 @@
         <v>46036</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71114,7 +71114,7 @@
         <v>46036</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71187,7 +71187,7 @@
         <v>44698</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71265,7 +71265,7 @@
         <v>45391</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71338,7 +71338,7 @@
         <v>45670</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71411,7 +71411,7 @@
         <v>44777</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71484,7 +71484,7 @@
         <v>46042</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71557,7 +71557,7 @@
         <v>45668</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71630,7 +71630,7 @@
         <v>45670</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71703,7 +71703,7 @@
         <v>44599</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71776,7 +71776,7 @@
         <v>45587</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>44743</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71927,7 +71927,7 @@
         <v>45640</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72000,7 +72000,7 @@
         <v>45706</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72078,7 +72078,7 @@
         <v>45723</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72156,7 +72156,7 @@
         <v>44858</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72229,7 +72229,7 @@
         <v>46043</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72302,7 +72302,7 @@
         <v>45453</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72375,7 +72375,7 @@
         <v>45971</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72448,7 +72448,7 @@
         <v>45310</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72521,7 +72521,7 @@
         <v>45310</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72594,7 +72594,7 @@
         <v>46047</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72667,7 +72667,7 @@
         <v>44700</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72740,7 +72740,7 @@
         <v>45254</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>46049</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>46049</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72959,7 +72959,7 @@
         <v>46049</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73032,7 +73032,7 @@
         <v>46049</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73105,7 +73105,7 @@
         <v>45089</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73178,7 +73178,7 @@
         <v>45159</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73251,7 +73251,7 @@
         <v>45322</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73324,7 +73324,7 @@
         <v>45800</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73397,7 +73397,7 @@
         <v>46052</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73475,7 +73475,7 @@
         <v>45890</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73548,7 +73548,7 @@
         <v>46056</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73626,7 +73626,7 @@
         <v>46058</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46057</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46057</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73860,7 +73860,7 @@
         <v>46057</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73938,7 +73938,7 @@
         <v>45813</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74016,7 +74016,7 @@
         <v>46061</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>46062</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74167,7 +74167,7 @@
         <v>46063</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74240,7 +74240,7 @@
         <v>46063</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74313,7 +74313,7 @@
         <v>46065</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74386,7 +74386,7 @@
         <v>46065</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46065</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74532,7 +74532,7 @@
         <v>46069</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74610,7 +74610,7 @@
         <v>46150</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74683,7 +74683,7 @@
         <v>46069</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>46069</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>46150</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>46150</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74985,7 +74985,7 @@
         <v>46072</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75058,7 +75058,7 @@
         <v>46077</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75136,7 +75136,7 @@
         <v>46077</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75214,7 +75214,7 @@
         <v>46077</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75292,7 +75292,7 @@
         <v>46077</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75370,7 +75370,7 @@
         <v>46155</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>46084</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75516,7 +75516,7 @@
         <v>45817</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75589,7 +75589,7 @@
         <v>45947</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75662,7 +75662,7 @@
         <v>46111</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75735,7 +75735,7 @@
         <v>46093</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75808,7 +75808,7 @@
         <v>46094</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75886,7 +75886,7 @@
         <v>46094</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75964,7 +75964,7 @@
         <v>45886</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>45916</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76110,7 +76110,7 @@
         <v>45817</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76183,7 +76183,7 @@
         <v>46167</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76256,7 +76256,7 @@
         <v>45957</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76329,7 +76329,7 @@
         <v>45956</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76402,7 +76402,7 @@
         <v>46174</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76475,7 +76475,7 @@
         <v>45845</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76548,7 +76548,7 @@
         <v>46177</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76621,7 +76621,7 @@
         <v>46177</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76694,7 +76694,7 @@
         <v>46178</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76767,7 +76767,7 @@
         <v>46181</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76845,7 +76845,7 @@
         <v>46181</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76918,7 +76918,7 @@
         <v>46178</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -76991,7 +76991,7 @@
         <v>46178</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77064,7 +77064,7 @@
         <v>46183</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77142,7 +77142,7 @@
         <v>46183</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77215,7 +77215,7 @@
         <v>46183</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77288,7 +77288,7 @@
         <v>46189</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77361,7 +77361,7 @@
         <v>46188</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77434,7 +77434,7 @@
         <v>46188</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77507,7 +77507,7 @@
         <v>46188</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77580,7 +77580,7 @@
         <v>46191</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77653,7 +77653,7 @@
         <v>46191</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77726,7 +77726,7 @@
         <v>46191</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77799,7 +77799,7 @@
         <v>46077</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77872,7 +77872,7 @@
         <v>46195</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77945,7 +77945,7 @@
         <v>46197</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -78018,7 +78018,7 @@
         <v>46197</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78091,7 +78091,7 @@
         <v>46197</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78164,7 +78164,7 @@
         <v>45957</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78242,7 +78242,7 @@
         <v>46202</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78315,7 +78315,7 @@
         <v>46203</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78388,7 +78388,7 @@
         <v>46203</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78461,7 +78461,7 @@
         <v>46204</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78534,7 +78534,7 @@
         <v>46204</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78607,7 +78607,7 @@
         <v>46207</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78680,7 +78680,7 @@
         <v>46206</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78753,7 +78753,7 @@
         <v>46209</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78826,7 +78826,7 @@
         <v>46216</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78899,7 +78899,7 @@
         <v>46218</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -78972,7 +78972,7 @@
         <v>46220</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -79045,7 +79045,7 @@
         <v>46265</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79118,7 +79118,7 @@
         <v>46225</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79191,7 +79191,7 @@
         <v>46268</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79264,7 +79264,7 @@
         <v>46268</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79337,7 +79337,7 @@
         <v>46266</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79410,7 +79410,7 @@
         <v>46266</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79483,7 +79483,7 @@
         <v>46266</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79556,7 +79556,7 @@
         <v>46266</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79629,7 +79629,7 @@
         <v>46274</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79707,7 +79707,7 @@
         <v>46272</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79780,7 +79780,7 @@
         <v>46237</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79853,7 +79853,7 @@
         <v>46238</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79926,7 +79926,7 @@
         <v>46239</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -79999,7 +79999,7 @@
         <v>46239</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80072,7 +80072,7 @@
         <v>46241</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80145,7 +80145,7 @@
         <v>46283</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80218,7 +80218,7 @@
         <v>45414</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80291,7 +80291,7 @@
         <v>46288</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80364,7 +80364,7 @@
         <v>46288</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80437,7 +80437,7 @@
         <v>46289</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80510,7 +80510,7 @@
         <v>46289</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80583,7 +80583,7 @@
         <v>46289</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80656,7 +80656,7 @@
         <v>46182</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80729,7 +80729,7 @@
         <v>46284</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80802,7 +80802,7 @@
         <v>46284</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80875,7 +80875,7 @@
         <v>46247</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80948,7 +80948,7 @@
         <v>46247</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -81021,7 +81021,7 @@
         <v>46247</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81094,7 +81094,7 @@
         <v>46289</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81167,7 +81167,7 @@
         <v>46247</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81240,7 +81240,7 @@
         <v>46246</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81313,7 +81313,7 @@
         <v>46293</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81386,7 +81386,7 @@
         <v>46294</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81459,7 +81459,7 @@
         <v>45728</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81532,7 +81532,7 @@
         <v>46254</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81610,7 +81610,7 @@
         <v>46254</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81688,7 +81688,7 @@
         <v>46254</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81761,7 +81761,7 @@
         <v>46300</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81834,7 +81834,7 @@
         <v>46255</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81907,7 +81907,7 @@
         <v>46259</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -81980,7 +81980,7 @@
         <v>46258</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82053,7 +82053,7 @@
         <v>46258</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82126,7 +82126,7 @@
         <v>46259</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82199,7 +82199,7 @@
         <v>46258</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82272,7 +82272,7 @@
         <v>46261</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82345,7 +82345,7 @@
         <v>45952</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82418,7 +82418,7 @@
         <v>46254</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82491,7 +82491,7 @@
         <v>46261</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82564,7 +82564,7 @@
         <v>45799</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82637,7 +82637,7 @@
         <v>45890</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82710,7 +82710,7 @@
         <v>46261</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82783,7 +82783,7 @@
         <v>46261</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82856,7 +82856,7 @@
         <v>46261</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -82929,7 +82929,7 @@
         <v>46260</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -83007,7 +83007,7 @@
         <v>46304</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83080,7 +83080,7 @@
         <v>46207</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83153,7 +83153,7 @@
         <v>44099</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83226,7 +83226,7 @@
         <v>43969</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83299,7 +83299,7 @@
         <v>44959</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83372,7 +83372,7 @@
         <v>43943</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83445,7 +83445,7 @@
         <v>44599</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83518,7 +83518,7 @@
         <v>44638</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>44652</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>44627</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83742,7 +83742,7 @@
         <v>44558</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83815,7 +83815,7 @@
         <v>44574</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83888,7 +83888,7 @@
         <v>44690</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -83961,7 +83961,7 @@
         <v>44854</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -84034,7 +84034,7 @@
         <v>45260</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84107,7 +84107,7 @@
         <v>45366</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84180,7 +84180,7 @@
         <v>45537</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84253,7 +84253,7 @@
         <v>44497</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84326,7 +84326,7 @@
         <v>44497</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84399,7 +84399,7 @@
         <v>44971</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84472,7 +84472,7 @@
         <v>45569</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84545,7 +84545,7 @@
         <v>45188</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84618,7 +84618,7 @@
         <v>44973</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84691,7 +84691,7 @@
         <v>45183</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84764,7 +84764,7 @@
         <v>44973</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84837,7 +84837,7 @@
         <v>45817</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84910,7 +84910,7 @@
         <v>45807</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -84983,7 +84983,7 @@
         <v>46062</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85056,7 +85056,7 @@
         <v>46062</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85129,7 +85129,7 @@
         <v>46188</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85202,7 +85202,7 @@
         <v>44614</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>46181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45418</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44949</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45800</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44571</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45436</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45190</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43969</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45104</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44949</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45446</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44650</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45960</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45400</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45847</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44706</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>45847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44711</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45485</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44956</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45664</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45783</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45581</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45810</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45071</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44512</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44749</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45082</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45831</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44683</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44743</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44855</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44778</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45616</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45821</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44679</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44880</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44530</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44843</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44763</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44771</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45754</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44985</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>46163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>46027</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45741</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>46183</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>46183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44695</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44743</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>46301</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>44629</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44594</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44880</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44502</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44816</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>44956</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44863</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45118</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45069</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45943</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>44868</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>46198</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>46288</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45383</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>46247</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>46295</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45803</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45559</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45146</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>46311</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44896</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44678</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44869</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45457</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45177</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45007</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44963</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44649</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44867</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45730</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>46010</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45897</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44637</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45081</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45957</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45904</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>44747</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45987</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45764</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45992</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45840</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45418</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>44778</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44797</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>44955</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44592</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>44813</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>46093</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46133</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46062</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>46204</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44705</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45260</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44760</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45223</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45474</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45473</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45205</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45112</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45687</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44704</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45113</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44489</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46301</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45794</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45532</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45549</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44965</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45826</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45855</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45708</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>44639</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44917</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>44518</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45994</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>44540</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44650</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>44833</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44728</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44777</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44634</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>44581</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44560</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44771</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44524</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44574</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>44496</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44626</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>44690</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>44682</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44708</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>44642</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44776</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>44746</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>44845</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>44543</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44543</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44495</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>44749</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>44882</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44545</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44722</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>44742</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>44756</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44806</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44511</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44510</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44867</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44511</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44683</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>44539</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>44496</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44516</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44712</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44543</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>44543</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44545</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44545</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44621</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44496</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44637</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44735</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44763</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44735</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44524</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44572</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44650</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44725</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>44580</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44777</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44665</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>44637</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>44655</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44744</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44826</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44845</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44526</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44642</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>44637</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44607</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>44698</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44609</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44817</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44760</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44623</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>44584</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44678</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>44682</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44682</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44665</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44665</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44704</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>44543</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44682</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44523</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>44815</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44725</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44495</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45022</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>44670</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45237</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45518</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45089</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>44743</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44643</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45443</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44510</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45208</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>44637</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>45054</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>45019</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45435</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44510</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44956</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44841</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45600</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45636</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45621</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45245</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>44832</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45376</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>44783</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45455</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45587</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44895</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44995</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45219</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45310</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44769</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45700</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>44904</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>44817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45561</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45450</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45450</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45223</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45642</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45208</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45208</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>44708</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44708</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45145</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45482</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45536</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44900</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45531</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45433</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>44953</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44816</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44834</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>44867</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44771</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44687</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>44901</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45362</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>44760</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>44581</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45640</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>44732</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45394</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44611</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45547</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45576</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45701</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>44778</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>44945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44767</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>44803</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44803</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45155</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45670</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>44687</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45033</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44809</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45121</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45104</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45127</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>44858</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45063</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45453</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45236</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45707</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>44949</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45243</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45177</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45757</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45708</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>44584</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45203</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45531</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45086</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45271</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45208</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44714</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>45203</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44580</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44845</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45084</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45530</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45208</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44937</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45218</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45356</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>44785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45469</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>45882</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>45670</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>45723</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45953</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45391</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45435</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45953</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45341</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45554</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45075</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45903</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45202</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45254</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45835</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45254</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45706</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45712</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45730</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>44962</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44624</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45442</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45797</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45817</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45639</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45888</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44525</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45145</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45735</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45700</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45859</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45859</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>44516</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44840</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45893</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45893</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45894</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45667</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45894</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>44908</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45894</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45897</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45168</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45897</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45896</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45897</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45880</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>45835</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45427</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45490</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45051</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45638</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45813</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>44673</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45898</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45245</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45898</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45721</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45800</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>44670</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45621</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45215</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45089</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45695</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45831</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45376</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45772</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45908</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45159</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45685</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45831</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45910</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45082</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45089</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45155</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45344</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45469</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45918</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45092</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45786</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44749</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45923</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45245</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45056</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45376</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45853</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>44974</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45460</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>46150</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45930</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45930</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45930</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45933</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>46150</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45933</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45936</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45935</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45609</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>46150</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45937</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45257</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45937</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45022</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>45022</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>44854</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45817</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>44922</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>44700</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45944</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>44635</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>44743</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45951</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45952</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45257</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>45957</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45330</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45957</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46155</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45956</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>45954</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45757</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>44769</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45960</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>44763</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>44833</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45737</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45401</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45947</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45971</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45973</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45886</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45111</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45749</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>44704</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>44778</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>45916</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45817</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45450</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45085</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45625</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>46167</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45985</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44993</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45982</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>44925</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45721</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>44777</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45640</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>45533</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>44621</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45273</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45631</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45490</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44953</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45175</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45993</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45992</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45993</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45957</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45994</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44992</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45469</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45994</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45994</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45996</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>44777</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45999</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>44704</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>46000</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45456</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>45956</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>45104</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45104</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44824</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>46001</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45644</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>46000</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>46002</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>46002</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>45128</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45847</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>46008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>46009</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>45322</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46008</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45075</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54894,7 +54894,7 @@
         <v>45075</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45075</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45075</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45092</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>44546</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>45610</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45411</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45239</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>46029</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45845</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>46029</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46029</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>46030</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45414</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>44643</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>46034</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>46034</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46036</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46178</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>46036</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46178</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>45456</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>46177</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45020</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>46042</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>46177</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>46178</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>44882</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45075</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45075</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45075</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45075</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45771</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>44596</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>44596</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57537,7 +57537,7 @@
         <v>46043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>45208</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>46047</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45552</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>46049</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>46049</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>46049</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>46049</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58121,7 +58121,7 @@
         <v>45890</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>46181</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>46052</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45183</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>45293</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>46056</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>45755</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58647,7 +58647,7 @@
         <v>46057</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58725,7 +58725,7 @@
         <v>46057</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>44952</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58881,7 +58881,7 @@
         <v>46181</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>46057</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>44790</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>44879</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>46183</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59256,7 +59256,7 @@
         <v>46183</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59329,7 +59329,7 @@
         <v>46183</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>46058</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59485,7 +59485,7 @@
         <v>45293</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59558,7 +59558,7 @@
         <v>45293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>44775</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>46063</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>46062</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59855,7 +59855,7 @@
         <v>46063</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59928,7 +59928,7 @@
         <v>46061</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60001,7 +60001,7 @@
         <v>46065</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60074,7 +60074,7 @@
         <v>46065</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60147,7 +60147,7 @@
         <v>44490</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60220,7 +60220,7 @@
         <v>46065</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60293,7 +60293,7 @@
         <v>45586</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60366,7 +60366,7 @@
         <v>46069</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60444,7 +60444,7 @@
         <v>46188</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>44648</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>46069</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>46069</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45740</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>45740</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60892,7 +60892,7 @@
         <v>45085</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60965,7 +60965,7 @@
         <v>44953</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61038,7 +61038,7 @@
         <v>46072</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61111,7 +61111,7 @@
         <v>45617</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>46077</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>46077</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>46077</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>46188</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61491,7 +61491,7 @@
         <v>46188</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>46077</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61642,7 +61642,7 @@
         <v>45065</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>45068</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>44644</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61866,7 +61866,7 @@
         <v>44746</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45139</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>46084</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45218</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>46189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45414</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>44599</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62377,7 +62377,7 @@
         <v>45412</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62450,7 +62450,7 @@
         <v>45205</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62523,7 +62523,7 @@
         <v>45147</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62596,7 +62596,7 @@
         <v>45191</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>46077</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62747,7 +62747,7 @@
         <v>45084</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62820,7 +62820,7 @@
         <v>46094</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62898,7 +62898,7 @@
         <v>46191</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>46191</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>46093</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>46094</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45442</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46094</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46191</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>44525</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>44540</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>44556</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45468</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>46100</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>46100</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>45139</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>46195</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64008,7 +64008,7 @@
         <v>44525</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64081,7 +64081,7 @@
         <v>45463</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64154,7 +64154,7 @@
         <v>45636</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>45146</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64305,7 +64305,7 @@
         <v>44698</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64383,7 +64383,7 @@
         <v>45468</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64456,7 +64456,7 @@
         <v>46197</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64529,7 +64529,7 @@
         <v>46197</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64602,7 +64602,7 @@
         <v>46113</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>44691</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64748,7 +64748,7 @@
         <v>46197</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>46119</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64894,7 +64894,7 @@
         <v>45356</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64967,7 +64967,7 @@
         <v>46119</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>44816</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>46119</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>46119</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65269,7 +65269,7 @@
         <v>45107</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65342,7 +65342,7 @@
         <v>45075</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         <v>45075</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65488,7 +65488,7 @@
         <v>45957</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65566,7 +65566,7 @@
         <v>46107</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65639,7 +65639,7 @@
         <v>44764</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65712,7 +65712,7 @@
         <v>46202</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65785,7 +65785,7 @@
         <v>45238</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65858,7 +65858,7 @@
         <v>45261</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65931,7 +65931,7 @@
         <v>45524</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66004,7 +66004,7 @@
         <v>46133</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66077,7 +66077,7 @@
         <v>46132</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66150,7 +66150,7 @@
         <v>46134</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>45245</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45454</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66369,7 +66369,7 @@
         <v>46135</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66442,7 +66442,7 @@
         <v>46203</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66515,7 +66515,7 @@
         <v>46119</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66593,7 +66593,7 @@
         <v>46203</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66666,7 +66666,7 @@
         <v>46204</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>45898</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>46204</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66885,7 +66885,7 @@
         <v>45971</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66958,7 +66958,7 @@
         <v>46206</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         <v>45587</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45231</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>44866</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>45082</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67323,7 +67323,7 @@
         <v>45082</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67396,7 +67396,7 @@
         <v>45260</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45260</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67542,7 +67542,7 @@
         <v>45853</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67615,7 +67615,7 @@
         <v>45617</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67688,7 +67688,7 @@
         <v>45063</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>45721</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>46207</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>45055</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         <v>45614</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68053,7 +68053,7 @@
         <v>44714</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68126,7 +68126,7 @@
         <v>45687</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>46209</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         <v>45225</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45253</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68423,7 +68423,7 @@
         <v>44851</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45042</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>44585</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>45469</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68720,7 +68720,7 @@
         <v>45385</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68793,7 +68793,7 @@
         <v>45202</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68866,7 +68866,7 @@
         <v>45075</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68939,7 +68939,7 @@
         <v>46216</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>44743</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69090,7 +69090,7 @@
         <v>45054</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69163,7 +69163,7 @@
         <v>45054</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69236,7 +69236,7 @@
         <v>46218</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69309,7 +69309,7 @@
         <v>44925</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69382,7 +69382,7 @@
         <v>44760</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69455,7 +69455,7 @@
         <v>46220</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69528,7 +69528,7 @@
         <v>45644</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69601,7 +69601,7 @@
         <v>44621</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69674,7 +69674,7 @@
         <v>45183</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69747,7 +69747,7 @@
         <v>45089</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69820,7 +69820,7 @@
         <v>44719</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69893,7 +69893,7 @@
         <v>44698</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69966,7 +69966,7 @@
         <v>46225</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70039,7 +70039,7 @@
         <v>46272</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70112,7 +70112,7 @@
         <v>45519</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70185,7 +70185,7 @@
         <v>45170</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70258,7 +70258,7 @@
         <v>44549</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70331,7 +70331,7 @@
         <v>45601</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70404,7 +70404,7 @@
         <v>44516</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70482,7 +70482,7 @@
         <v>44516</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70560,7 +70560,7 @@
         <v>45448</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70633,7 +70633,7 @@
         <v>44782</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>44753</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>44902</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>44795</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70925,7 +70925,7 @@
         <v>45518</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>46274</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>45686</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71149,7 +71149,7 @@
         <v>45522</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>45357</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>45147</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>44923</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71441,7 +71441,7 @@
         <v>45212</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71514,7 +71514,7 @@
         <v>45119</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>45668</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>44682</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>44815</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71806,7 +71806,7 @@
         <v>44986</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>45089</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>46237</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>45310</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72098,7 +72098,7 @@
         <v>44866</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72171,7 +72171,7 @@
         <v>44868</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72244,7 +72244,7 @@
         <v>46238</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72317,7 +72317,7 @@
         <v>44495</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72390,7 +72390,7 @@
         <v>44963</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72463,7 +72463,7 @@
         <v>46239</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72536,7 +72536,7 @@
         <v>44816</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>45693</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72682,7 +72682,7 @@
         <v>46239</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72755,7 +72755,7 @@
         <v>46283</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72828,7 +72828,7 @@
         <v>45558</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72901,7 +72901,7 @@
         <v>44956</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72974,7 +72974,7 @@
         <v>44956</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73047,7 +73047,7 @@
         <v>45414</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73120,7 +73120,7 @@
         <v>46241</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>44684</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45253</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>44980</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>45174</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73490,7 +73490,7 @@
         <v>45232</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73563,7 +73563,7 @@
         <v>45075</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>45468</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73709,7 +73709,7 @@
         <v>46288</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46288</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73855,7 +73855,7 @@
         <v>46246</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73928,7 +73928,7 @@
         <v>46289</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74001,7 +74001,7 @@
         <v>46289</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74074,7 +74074,7 @@
         <v>44938</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>46289</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74220,7 +74220,7 @@
         <v>46289</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74293,7 +74293,7 @@
         <v>46247</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74366,7 +74366,7 @@
         <v>46247</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74439,7 +74439,7 @@
         <v>44806</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>44934</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74585,7 +74585,7 @@
         <v>46284</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>44799</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74731,7 +74731,7 @@
         <v>45063</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74804,7 +74804,7 @@
         <v>45075</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>46247</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>46284</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>45245</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>45245</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>46293</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>46182</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75315,7 +75315,7 @@
         <v>46247</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75388,7 +75388,7 @@
         <v>44750</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75461,7 +75461,7 @@
         <v>44750</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75534,7 +75534,7 @@
         <v>45075</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75607,7 +75607,7 @@
         <v>45338</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>45254</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75753,7 +75753,7 @@
         <v>45775</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75826,7 +75826,7 @@
         <v>44693</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75899,7 +75899,7 @@
         <v>44769</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -75972,7 +75972,7 @@
         <v>45113</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76045,7 +76045,7 @@
         <v>45328</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76118,7 +76118,7 @@
         <v>46254</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76191,7 +76191,7 @@
         <v>46254</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76269,7 +76269,7 @@
         <v>46254</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76347,7 +76347,7 @@
         <v>45728</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76420,7 +76420,7 @@
         <v>46255</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76493,7 +76493,7 @@
         <v>45348</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76571,7 +76571,7 @@
         <v>44490</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76644,7 +76644,7 @@
         <v>46300</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76717,7 +76717,7 @@
         <v>45316</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76790,7 +76790,7 @@
         <v>45253</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76863,7 +76863,7 @@
         <v>45190</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -76936,7 +76936,7 @@
         <v>46258</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77009,7 +77009,7 @@
         <v>45783</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77082,7 +77082,7 @@
         <v>46258</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77155,7 +77155,7 @@
         <v>45783</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77228,7 +77228,7 @@
         <v>46258</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77301,7 +77301,7 @@
         <v>45408</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77374,7 +77374,7 @@
         <v>45635</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77447,7 +77447,7 @@
         <v>44578</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77520,7 +77520,7 @@
         <v>45735</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77593,7 +77593,7 @@
         <v>45952</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77666,7 +77666,7 @@
         <v>45709</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77744,7 +77744,7 @@
         <v>45537</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77817,7 +77817,7 @@
         <v>45187</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77890,7 +77890,7 @@
         <v>45385</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -77963,7 +77963,7 @@
         <v>45572</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78036,7 +78036,7 @@
         <v>45890</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78109,7 +78109,7 @@
         <v>45549</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78182,7 +78182,7 @@
         <v>45579</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78255,7 +78255,7 @@
         <v>45352</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78328,7 +78328,7 @@
         <v>46260</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78406,7 +78406,7 @@
         <v>46259</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78479,7 +78479,7 @@
         <v>46259</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78552,7 +78552,7 @@
         <v>46261</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78625,7 +78625,7 @@
         <v>46254</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78698,7 +78698,7 @@
         <v>46261</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78771,7 +78771,7 @@
         <v>45272</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78844,7 +78844,7 @@
         <v>45272</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -78917,7 +78917,7 @@
         <v>45475</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -78990,7 +78990,7 @@
         <v>46207</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79063,7 +79063,7 @@
         <v>45518</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79136,7 +79136,7 @@
         <v>46261</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79209,7 +79209,7 @@
         <v>44708</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79282,7 +79282,7 @@
         <v>45436</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79355,7 +79355,7 @@
         <v>46304</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79428,7 +79428,7 @@
         <v>46261</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79501,7 +79501,7 @@
         <v>45385</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79574,7 +79574,7 @@
         <v>45713</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79652,7 +79652,7 @@
         <v>45729</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79725,7 +79725,7 @@
         <v>46261</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79798,7 +79798,7 @@
         <v>45798</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79871,7 +79871,7 @@
         <v>45798</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -79944,7 +79944,7 @@
         <v>45799</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80017,7 +80017,7 @@
         <v>45798</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80090,7 +80090,7 @@
         <v>45586</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80163,7 +80163,7 @@
         <v>46266</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80236,7 +80236,7 @@
         <v>46304</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80309,7 +80309,7 @@
         <v>45803</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80382,7 +80382,7 @@
         <v>45800</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80455,7 +80455,7 @@
         <v>44813</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80528,7 +80528,7 @@
         <v>45224</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80601,7 +80601,7 @@
         <v>46266</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80674,7 +80674,7 @@
         <v>46265</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80747,7 +80747,7 @@
         <v>46309</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80825,7 +80825,7 @@
         <v>45810</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80898,7 +80898,7 @@
         <v>46266</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -80971,7 +80971,7 @@
         <v>46266</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81044,7 +81044,7 @@
         <v>45810</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81117,7 +81117,7 @@
         <v>45790</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81190,7 +81190,7 @@
         <v>45810</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81263,7 +81263,7 @@
         <v>45813</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81336,7 +81336,7 @@
         <v>46311</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81409,7 +81409,7 @@
         <v>45817</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81487,7 +81487,7 @@
         <v>46268</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81560,7 +81560,7 @@
         <v>46268</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81633,7 +81633,7 @@
         <v>45747</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81706,7 +81706,7 @@
         <v>45376</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81784,7 +81784,7 @@
         <v>46311</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81857,7 +81857,7 @@
         <v>46311</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -81930,7 +81930,7 @@
         <v>45824</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82008,7 +82008,7 @@
         <v>46294</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82081,7 +82081,7 @@
         <v>45831</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82154,7 +82154,7 @@
         <v>45834</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82227,7 +82227,7 @@
         <v>45834</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82300,7 +82300,7 @@
         <v>45835</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82373,7 +82373,7 @@
         <v>45834</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82446,7 +82446,7 @@
         <v>45839</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82519,7 +82519,7 @@
         <v>45840</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82592,7 +82592,7 @@
         <v>45152</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82665,7 +82665,7 @@
         <v>45581</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82738,7 +82738,7 @@
         <v>45852</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82811,7 +82811,7 @@
         <v>45855</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -82889,7 +82889,7 @@
         <v>45855</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -82967,7 +82967,7 @@
         <v>45525</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83040,7 +83040,7 @@
         <v>45776</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83113,7 +83113,7 @@
         <v>45446</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83186,7 +83186,7 @@
         <v>45880</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83264,7 +83264,7 @@
         <v>45776</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83337,7 +83337,7 @@
         <v>45386</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83410,7 +83410,7 @@
         <v>43943</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83483,7 +83483,7 @@
         <v>43969</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83556,7 +83556,7 @@
         <v>44959</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83629,7 +83629,7 @@
         <v>44099</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83702,7 +83702,7 @@
         <v>44854</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83775,7 +83775,7 @@
         <v>44599</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83848,7 +83848,7 @@
         <v>45260</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -83921,7 +83921,7 @@
         <v>44638</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -83999,7 +83999,7 @@
         <v>45366</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84072,7 +84072,7 @@
         <v>44652</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84145,7 +84145,7 @@
         <v>45537</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84218,7 +84218,7 @@
         <v>44627</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84291,7 +84291,7 @@
         <v>44497</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84364,7 +84364,7 @@
         <v>44558</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84437,7 +84437,7 @@
         <v>44497</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84510,7 +84510,7 @@
         <v>44971</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84583,7 +84583,7 @@
         <v>44574</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84656,7 +84656,7 @@
         <v>44690</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84729,7 +84729,7 @@
         <v>45569</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84802,7 +84802,7 @@
         <v>45188</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84875,7 +84875,7 @@
         <v>44973</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -84948,7 +84948,7 @@
         <v>45183</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85021,7 +85021,7 @@
         <v>44973</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85094,7 +85094,7 @@
         <v>45817</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85167,7 +85167,7 @@
         <v>45807</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85240,7 +85240,7 @@
         <v>46062</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85313,7 +85313,7 @@
         <v>46062</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85386,7 +85386,7 @@
         <v>46188</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85459,7 +85459,7 @@
         <v>44614</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>44946</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>45757</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45715</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>46181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45418</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44949</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44550</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45800</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44880</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44571</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45436</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45190</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43969</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45104</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44949</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45446</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44650</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>45960</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45400</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45847</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44706</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>45847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>44489</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44711</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45485</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44956</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45664</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45783</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45581</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45810</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45071</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44512</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44749</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45082</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45831</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44683</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44743</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44855</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44778</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45616</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45821</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44679</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44880</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44530</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44843</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44763</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44771</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45754</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44985</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>46163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>46027</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45741</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>46183</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>46183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44695</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44743</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>46301</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>44629</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44594</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44880</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44502</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44816</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>44956</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44863</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45118</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45069</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45943</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>44868</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>46198</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45548</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>46288</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45383</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>46247</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>46295</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45803</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45559</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45146</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>46311</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44896</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44678</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44868</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44868</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44869</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45457</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45177</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45007</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44963</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44649</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44867</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45730</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>46010</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45897</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44637</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45081</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45957</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45904</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>44747</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45987</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45764</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45992</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45840</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45418</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>44778</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44797</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>44955</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44592</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>44813</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>46093</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46133</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46062</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>46204</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44705</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45260</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44760</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44813</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45223</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45474</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>45473</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45205</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45112</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45687</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44704</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45113</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44489</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46301</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45794</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45532</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45549</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44965</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45826</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45855</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45708</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>44639</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44917</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>44518</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45994</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>44540</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44650</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>44833</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44728</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44777</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44634</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>44581</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44560</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44771</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44524</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44574</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>44496</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44626</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>44690</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>44682</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44708</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>44642</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44776</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>44746</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>44845</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>44543</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44543</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44495</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>44749</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>44882</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44545</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44722</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>44742</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>44756</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44806</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44511</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44510</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44867</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44511</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44683</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>44539</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>44496</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44516</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44712</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44543</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>44543</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44545</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44545</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44621</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44496</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44637</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44735</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44763</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44735</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44524</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44572</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44650</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44725</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>44580</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44777</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44665</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>44637</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>44655</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44744</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44826</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44845</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44526</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44642</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>44637</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44607</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>44698</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44609</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44817</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44760</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44623</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>44584</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44678</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>44682</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44682</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44665</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44665</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44704</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>44543</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44682</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44523</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>44815</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44725</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44495</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44743</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45022</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>44670</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45237</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45518</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45089</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>44743</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44643</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45443</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44510</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45208</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>44637</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>45054</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>45019</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45435</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44510</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44956</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44841</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45600</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45636</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45621</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45245</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>44832</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45376</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>44783</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45455</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45587</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44895</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44995</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45219</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45310</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44769</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45700</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>44904</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>44817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45561</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45450</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45450</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45223</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45642</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45208</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45208</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>44708</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44708</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45145</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45482</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45536</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44900</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45531</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45433</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>44953</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44816</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44834</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>44867</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44771</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44687</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>44901</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45362</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>44760</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>44581</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45640</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>44732</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45394</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44611</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45547</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45576</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45701</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>44778</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>44945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44767</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>44803</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44803</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45155</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45670</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>44687</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45033</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44809</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45121</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45104</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45127</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>44858</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45063</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45453</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45236</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45707</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>44949</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45243</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45177</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45757</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45708</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>44584</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45203</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45531</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45086</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45271</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45208</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44714</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>45203</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44580</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44845</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45084</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45530</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45208</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44937</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45218</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45356</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>44785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45469</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>45882</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>45670</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>45723</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45953</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45391</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45435</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45953</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45341</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45554</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45075</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45903</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45202</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45254</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45835</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45254</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45706</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45712</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45730</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>44962</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44624</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45442</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45797</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45817</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45639</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45888</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44525</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45145</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45735</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45700</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45859</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45859</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>44516</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>44840</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45893</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45893</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45894</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45667</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45894</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>44908</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45894</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45897</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45168</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45897</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45896</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45897</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45880</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>45835</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45427</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45490</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45051</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45638</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45813</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>44673</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45898</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45245</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45898</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45721</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45800</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>44670</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45621</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45215</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45089</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45695</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45831</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45376</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45772</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45908</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45159</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45685</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45831</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45910</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45082</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45089</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45155</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45344</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45469</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45918</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45092</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45786</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44749</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45923</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45245</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45056</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45376</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45853</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>44974</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45460</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>46150</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45930</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45930</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45930</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45933</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>46150</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45933</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45936</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45935</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45609</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>46150</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45937</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45257</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45937</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45022</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>45022</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>44854</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45817</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>44922</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>44700</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>45944</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>44635</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>44743</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45951</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45952</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45257</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>45957</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45330</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45957</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46155</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45956</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>45954</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45757</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>44769</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45960</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>44763</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>44833</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45737</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45401</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45947</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45971</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45973</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45886</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45111</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45749</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>44704</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>44778</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>45916</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45817</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45450</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45085</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45625</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>46167</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45985</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>44993</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45982</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>44925</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45721</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>44777</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45640</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>45533</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>44621</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45273</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45631</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45490</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44953</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45175</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45993</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45992</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45993</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45957</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45994</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44992</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45469</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45994</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45994</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45996</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>44777</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45999</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>44704</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>46000</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45456</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>45956</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>45104</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45104</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44824</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>46001</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45644</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>46000</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>46002</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>46002</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>45128</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45847</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>46008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>46009</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>45322</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46008</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45075</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54894,7 +54894,7 @@
         <v>45075</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45075</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45075</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45092</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>44546</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>45610</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45411</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45239</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>46029</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45845</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>46029</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46029</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>46030</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45414</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>44643</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>46034</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>46034</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46036</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>46178</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>46036</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46178</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>45456</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>46177</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45020</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>46042</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>46177</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>46178</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>44882</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45075</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45075</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45075</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45075</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45771</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>44596</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>44596</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57537,7 +57537,7 @@
         <v>46043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>45208</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>46047</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45552</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>46049</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>46049</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>46049</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>46049</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58121,7 +58121,7 @@
         <v>45890</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>46181</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>46052</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45183</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>45293</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>46056</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>45755</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58647,7 +58647,7 @@
         <v>46057</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58725,7 +58725,7 @@
         <v>46057</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>44952</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58881,7 +58881,7 @@
         <v>46181</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>46057</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>44790</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>44879</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>46183</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59256,7 +59256,7 @@
         <v>46183</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59329,7 +59329,7 @@
         <v>46183</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>46058</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59485,7 +59485,7 @@
         <v>45293</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59558,7 +59558,7 @@
         <v>45293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>44775</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>46063</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>46062</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59855,7 +59855,7 @@
         <v>46063</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59928,7 +59928,7 @@
         <v>46061</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60001,7 +60001,7 @@
         <v>46065</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60074,7 +60074,7 @@
         <v>46065</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60147,7 +60147,7 @@
         <v>44490</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60220,7 +60220,7 @@
         <v>46065</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60293,7 +60293,7 @@
         <v>45586</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60366,7 +60366,7 @@
         <v>46069</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60444,7 +60444,7 @@
         <v>46188</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60517,7 +60517,7 @@
         <v>44648</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>46069</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>46069</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45740</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>45740</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60892,7 +60892,7 @@
         <v>45085</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60965,7 +60965,7 @@
         <v>44953</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61038,7 +61038,7 @@
         <v>46072</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61111,7 +61111,7 @@
         <v>45617</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>46077</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>46077</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>46077</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>46188</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61491,7 +61491,7 @@
         <v>46188</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>46077</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61642,7 +61642,7 @@
         <v>45065</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>45068</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>44644</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61866,7 +61866,7 @@
         <v>44746</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45139</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>46084</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45218</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>46189</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45414</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>44599</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62377,7 +62377,7 @@
         <v>45412</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62450,7 +62450,7 @@
         <v>45205</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62523,7 +62523,7 @@
         <v>45147</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62596,7 +62596,7 @@
         <v>45191</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>46077</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62747,7 +62747,7 @@
         <v>45084</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62820,7 +62820,7 @@
         <v>46094</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62898,7 +62898,7 @@
         <v>46191</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>46191</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>46093</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>46094</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45442</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46094</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46191</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>44525</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>44540</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>44556</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45468</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>46100</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>46100</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>45139</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>46195</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64008,7 +64008,7 @@
         <v>44525</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64081,7 +64081,7 @@
         <v>45463</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64154,7 +64154,7 @@
         <v>45636</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>45146</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64305,7 +64305,7 @@
         <v>44698</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64383,7 +64383,7 @@
         <v>45468</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64456,7 +64456,7 @@
         <v>46197</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64529,7 +64529,7 @@
         <v>46197</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64602,7 +64602,7 @@
         <v>46113</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>44691</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64748,7 +64748,7 @@
         <v>46197</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>46119</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64894,7 +64894,7 @@
         <v>45356</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64967,7 +64967,7 @@
         <v>46119</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>44816</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>46119</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>46119</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65269,7 +65269,7 @@
         <v>45107</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65342,7 +65342,7 @@
         <v>45075</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         <v>45075</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65488,7 +65488,7 @@
         <v>45957</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65566,7 +65566,7 @@
         <v>46107</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65639,7 +65639,7 @@
         <v>44764</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65712,7 +65712,7 @@
         <v>46202</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65785,7 +65785,7 @@
         <v>45238</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65858,7 +65858,7 @@
         <v>45261</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65931,7 +65931,7 @@
         <v>45524</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66004,7 +66004,7 @@
         <v>46133</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66077,7 +66077,7 @@
         <v>46132</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66150,7 +66150,7 @@
         <v>46134</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>45245</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45454</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66369,7 +66369,7 @@
         <v>46135</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66442,7 +66442,7 @@
         <v>46203</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66515,7 +66515,7 @@
         <v>46119</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66593,7 +66593,7 @@
         <v>46203</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66666,7 +66666,7 @@
         <v>46204</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>45898</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>46204</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66885,7 +66885,7 @@
         <v>45971</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66958,7 +66958,7 @@
         <v>46206</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         <v>45587</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45231</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>44866</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>45082</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67323,7 +67323,7 @@
         <v>45082</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67396,7 +67396,7 @@
         <v>45260</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45260</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67542,7 +67542,7 @@
         <v>45853</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67615,7 +67615,7 @@
         <v>45617</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67688,7 +67688,7 @@
         <v>45063</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>45721</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>46207</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>45055</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         <v>45614</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68053,7 +68053,7 @@
         <v>44714</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68126,7 +68126,7 @@
         <v>45687</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>46209</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         <v>45225</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45253</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68423,7 +68423,7 @@
         <v>44851</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45042</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>44585</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>45469</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68720,7 +68720,7 @@
         <v>45385</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68793,7 +68793,7 @@
         <v>45202</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68866,7 +68866,7 @@
         <v>45075</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68939,7 +68939,7 @@
         <v>46216</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>44743</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69090,7 +69090,7 @@
         <v>45054</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69163,7 +69163,7 @@
         <v>45054</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69236,7 +69236,7 @@
         <v>46218</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69309,7 +69309,7 @@
         <v>44925</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69382,7 +69382,7 @@
         <v>44760</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69455,7 +69455,7 @@
         <v>46220</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69528,7 +69528,7 @@
         <v>45644</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69601,7 +69601,7 @@
         <v>44621</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69674,7 +69674,7 @@
         <v>45183</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69747,7 +69747,7 @@
         <v>45089</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69820,7 +69820,7 @@
         <v>44719</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69893,7 +69893,7 @@
         <v>44698</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69966,7 +69966,7 @@
         <v>46225</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70039,7 +70039,7 @@
         <v>46272</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70112,7 +70112,7 @@
         <v>45519</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70185,7 +70185,7 @@
         <v>45170</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70258,7 +70258,7 @@
         <v>44549</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70331,7 +70331,7 @@
         <v>45601</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70404,7 +70404,7 @@
         <v>44516</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70482,7 +70482,7 @@
         <v>44516</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70560,7 +70560,7 @@
         <v>45448</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70633,7 +70633,7 @@
         <v>44782</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>44753</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>44902</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>44795</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70925,7 +70925,7 @@
         <v>45518</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>46274</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>45686</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71149,7 +71149,7 @@
         <v>45522</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71222,7 +71222,7 @@
         <v>45357</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71295,7 +71295,7 @@
         <v>45147</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>44923</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71441,7 +71441,7 @@
         <v>45212</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71514,7 +71514,7 @@
         <v>45119</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>45668</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>44682</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>44815</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71806,7 +71806,7 @@
         <v>44986</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>45089</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>46237</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>45310</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72098,7 +72098,7 @@
         <v>44866</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72171,7 +72171,7 @@
         <v>44868</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72244,7 +72244,7 @@
         <v>46238</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72317,7 +72317,7 @@
         <v>44495</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72390,7 +72390,7 @@
         <v>44963</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72463,7 +72463,7 @@
         <v>46239</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72536,7 +72536,7 @@
         <v>44816</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72609,7 +72609,7 @@
         <v>45693</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72682,7 +72682,7 @@
         <v>46239</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72755,7 +72755,7 @@
         <v>46283</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72828,7 +72828,7 @@
         <v>45558</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72901,7 +72901,7 @@
         <v>44956</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72974,7 +72974,7 @@
         <v>44956</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73047,7 +73047,7 @@
         <v>45414</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73120,7 +73120,7 @@
         <v>46241</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>44684</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45253</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>44980</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>45174</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73490,7 +73490,7 @@
         <v>45232</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73563,7 +73563,7 @@
         <v>45075</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>45468</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73709,7 +73709,7 @@
         <v>46288</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46288</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73855,7 +73855,7 @@
         <v>46246</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73928,7 +73928,7 @@
         <v>46289</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74001,7 +74001,7 @@
         <v>46289</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74074,7 +74074,7 @@
         <v>44938</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>46289</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74220,7 +74220,7 @@
         <v>46289</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74293,7 +74293,7 @@
         <v>46247</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74366,7 +74366,7 @@
         <v>46247</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74439,7 +74439,7 @@
         <v>44806</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74512,7 +74512,7 @@
         <v>44934</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74585,7 +74585,7 @@
         <v>46284</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74658,7 +74658,7 @@
         <v>44799</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74731,7 +74731,7 @@
         <v>45063</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74804,7 +74804,7 @@
         <v>45075</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
         <v>46247</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74950,7 +74950,7 @@
         <v>46284</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75023,7 +75023,7 @@
         <v>45245</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75096,7 +75096,7 @@
         <v>45245</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75169,7 +75169,7 @@
         <v>46293</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75242,7 +75242,7 @@
         <v>46182</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75315,7 +75315,7 @@
         <v>46247</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75388,7 +75388,7 @@
         <v>44750</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75461,7 +75461,7 @@
         <v>44750</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75534,7 +75534,7 @@
         <v>45075</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75607,7 +75607,7 @@
         <v>45338</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>45254</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75753,7 +75753,7 @@
         <v>45775</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75826,7 +75826,7 @@
         <v>44693</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75899,7 +75899,7 @@
         <v>44769</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -75972,7 +75972,7 @@
         <v>45113</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76045,7 +76045,7 @@
         <v>45328</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76118,7 +76118,7 @@
         <v>46254</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76191,7 +76191,7 @@
         <v>46254</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76269,7 +76269,7 @@
         <v>46254</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76347,7 +76347,7 @@
         <v>45728</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76420,7 +76420,7 @@
         <v>46255</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76493,7 +76493,7 @@
         <v>45348</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76571,7 +76571,7 @@
         <v>44490</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76644,7 +76644,7 @@
         <v>46300</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76717,7 +76717,7 @@
         <v>45316</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76790,7 +76790,7 @@
         <v>45253</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76863,7 +76863,7 @@
         <v>45190</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -76936,7 +76936,7 @@
         <v>46258</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77009,7 +77009,7 @@
         <v>45783</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77082,7 +77082,7 @@
         <v>46258</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77155,7 +77155,7 @@
         <v>45783</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77228,7 +77228,7 @@
         <v>46258</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77301,7 +77301,7 @@
         <v>45408</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77374,7 +77374,7 @@
         <v>45635</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77447,7 +77447,7 @@
         <v>44578</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77520,7 +77520,7 @@
         <v>45735</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77593,7 +77593,7 @@
         <v>45952</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77666,7 +77666,7 @@
         <v>45709</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77744,7 +77744,7 @@
         <v>45537</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77817,7 +77817,7 @@
         <v>45187</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77890,7 +77890,7 @@
         <v>45385</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -77963,7 +77963,7 @@
         <v>45572</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -78036,7 +78036,7 @@
         <v>45890</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78109,7 +78109,7 @@
         <v>45549</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78182,7 +78182,7 @@
         <v>45579</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78255,7 +78255,7 @@
         <v>45352</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78328,7 +78328,7 @@
         <v>46260</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78406,7 +78406,7 @@
         <v>46259</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78479,7 +78479,7 @@
         <v>46259</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78552,7 +78552,7 @@
         <v>46261</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78625,7 +78625,7 @@
         <v>46254</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78698,7 +78698,7 @@
         <v>46261</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78771,7 +78771,7 @@
         <v>45272</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78844,7 +78844,7 @@
         <v>45272</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -78917,7 +78917,7 @@
         <v>45475</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -78990,7 +78990,7 @@
         <v>46207</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79063,7 +79063,7 @@
         <v>45518</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79136,7 +79136,7 @@
         <v>46261</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79209,7 +79209,7 @@
         <v>44708</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79282,7 +79282,7 @@
         <v>45436</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79355,7 +79355,7 @@
         <v>46304</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79428,7 +79428,7 @@
         <v>46261</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79501,7 +79501,7 @@
         <v>45385</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79574,7 +79574,7 @@
         <v>45713</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79652,7 +79652,7 @@
         <v>45729</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79725,7 +79725,7 @@
         <v>46261</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79798,7 +79798,7 @@
         <v>45798</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79871,7 +79871,7 @@
         <v>45798</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -79944,7 +79944,7 @@
         <v>45799</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -80017,7 +80017,7 @@
         <v>45798</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80090,7 +80090,7 @@
         <v>45586</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80163,7 +80163,7 @@
         <v>46266</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80236,7 +80236,7 @@
         <v>46304</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80309,7 +80309,7 @@
         <v>45803</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80382,7 +80382,7 @@
         <v>45800</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80455,7 +80455,7 @@
         <v>44813</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80528,7 +80528,7 @@
         <v>45224</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80601,7 +80601,7 @@
         <v>46266</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80674,7 +80674,7 @@
         <v>46265</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80747,7 +80747,7 @@
         <v>46309</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80825,7 +80825,7 @@
         <v>45810</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80898,7 +80898,7 @@
         <v>46266</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -80971,7 +80971,7 @@
         <v>46266</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81044,7 +81044,7 @@
         <v>45810</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81117,7 +81117,7 @@
         <v>45790</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81190,7 +81190,7 @@
         <v>45810</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81263,7 +81263,7 @@
         <v>45813</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81336,7 +81336,7 @@
         <v>46311</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81409,7 +81409,7 @@
         <v>45817</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81487,7 +81487,7 @@
         <v>46268</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -81560,7 +81560,7 @@
         <v>46268</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -81633,7 +81633,7 @@
         <v>45747</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -81706,7 +81706,7 @@
         <v>45376</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -81784,7 +81784,7 @@
         <v>46311</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -81857,7 +81857,7 @@
         <v>46311</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -81930,7 +81930,7 @@
         <v>45824</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -82008,7 +82008,7 @@
         <v>46294</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -82081,7 +82081,7 @@
         <v>45831</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -82154,7 +82154,7 @@
         <v>45834</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -82227,7 +82227,7 @@
         <v>45834</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -82300,7 +82300,7 @@
         <v>45835</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -82373,7 +82373,7 @@
         <v>45834</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -82446,7 +82446,7 @@
         <v>45839</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -82519,7 +82519,7 @@
         <v>45840</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -82592,7 +82592,7 @@
         <v>45152</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -82665,7 +82665,7 @@
         <v>45581</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -82738,7 +82738,7 @@
         <v>45852</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -82811,7 +82811,7 @@
         <v>45855</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -82889,7 +82889,7 @@
         <v>45855</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -82967,7 +82967,7 @@
         <v>45525</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -83040,7 +83040,7 @@
         <v>45776</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -83113,7 +83113,7 @@
         <v>45446</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -83186,7 +83186,7 @@
         <v>45880</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -83264,7 +83264,7 @@
         <v>45776</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -83337,7 +83337,7 @@
         <v>45386</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -83410,7 +83410,7 @@
         <v>43943</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -83483,7 +83483,7 @@
         <v>43969</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -83556,7 +83556,7 @@
         <v>44959</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -83629,7 +83629,7 @@
         <v>44099</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -83702,7 +83702,7 @@
         <v>44854</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -83775,7 +83775,7 @@
         <v>44599</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -83848,7 +83848,7 @@
         <v>45260</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -83921,7 +83921,7 @@
         <v>44638</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -83999,7 +83999,7 @@
         <v>45366</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -84072,7 +84072,7 @@
         <v>44652</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -84145,7 +84145,7 @@
         <v>45537</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -84218,7 +84218,7 @@
         <v>44627</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -84291,7 +84291,7 @@
         <v>44497</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -84364,7 +84364,7 @@
         <v>44558</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -84437,7 +84437,7 @@
         <v>44497</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -84510,7 +84510,7 @@
         <v>44971</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -84583,7 +84583,7 @@
         <v>44574</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -84656,7 +84656,7 @@
         <v>44690</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -84729,7 +84729,7 @@
         <v>45569</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -84802,7 +84802,7 @@
         <v>45188</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -84875,7 +84875,7 @@
         <v>44973</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -84948,7 +84948,7 @@
         <v>45183</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -85021,7 +85021,7 @@
         <v>44973</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -85094,7 +85094,7 @@
         <v>45817</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -85167,7 +85167,7 @@
         <v>45807</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -85240,7 +85240,7 @@
         <v>46062</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -85313,7 +85313,7 @@
         <v>46062</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -85386,7 +85386,7 @@
         <v>46188</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -85459,7 +85459,7 @@
         <v>44614</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -601,7 +601,7 @@
         <v>44834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>45135</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>46112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45757</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44946</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45831</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>46121</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45715</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45800</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45973</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45267</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45784</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44880</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44909</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44497</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45784</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45367</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>46181</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>46103</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45847</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44874</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>46029</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>46107</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45418</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45800</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>44550</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44949</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44571</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>45994</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43969</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45104</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44727</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44650</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46107</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7373,10 +7373,10 @@
         <v>7</v>
       </c>
       <c r="T54" t="n">
+        <v>13</v>
+      </c>
+      <c r="U54" t="n">
         <v>7</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45847</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45540</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45446</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45068</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44949</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45400</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44706</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45847</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44711</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45162</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44956</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>46204</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>45783</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>46247</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45581</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>45485</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44972</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45071</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44512</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44749</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45898</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44743</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44855</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45616</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45821</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>44778</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>45082</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44545</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44839</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44679</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44530</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44843</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44763</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44771</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>46183</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>46183</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44743</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46027</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45169</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>46301</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44985</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45754</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44698</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44695</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44866</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45741</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44629</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45642</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44594</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44880</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44502</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44816</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45219</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44868</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45943</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45383</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45945</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>46198</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45118</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44956</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46288</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45146</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45559</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45803</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>46247</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>46295</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>46311</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>46150</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45070</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45548</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45069</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45226</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45293</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>44863</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>44678</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>44896</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44497</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44972</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45994</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44573</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44868</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44564</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44858</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44495</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44680</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>44868</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>44658</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45730</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>44778</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45280</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45897</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44813</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45007</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45183</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45223</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45957</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45960</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45205</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>46204</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>44637</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45987</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45960</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45457</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45473</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45840</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44620</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45794</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45532</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45549</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44869</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45826</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21220,10 +21220,10 @@
         <v>1</v>
       </c>
       <c r="T181" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="U181" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>46093</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>13</v>
       </c>
       <c r="U182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V182" s="2" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46301</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45708</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44592</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46133</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>46010</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>44617</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>46062</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44867</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>44963</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45623</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>1</v>
       </c>
       <c r="T194" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="U194" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="V194" s="2" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45904</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44797</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45450</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45474</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44955</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45081</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44760</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45147</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45147</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44705</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45418</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45260</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45177</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>44649</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45687</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24512,10 +24512,10 @@
         <v>1</v>
       </c>
       <c r="T212" t="n">
+        <v>4</v>
+      </c>
+      <c r="U212" t="n">
         <v>2</v>
-      </c>
-      <c r="U212" t="n">
-        <v>0</v>
       </c>
       <c r="V212" s="2" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45608</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45687</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24727,10 +24727,10 @@
         <v>1</v>
       </c>
       <c r="T214" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="U214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V214" s="2" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45219</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>44813</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44704</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44747</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44639</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>44917</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44518</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45572</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45994</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>44642</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44540</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44650</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44833</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44810</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44777</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>44634</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44581</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44560</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44771</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>44524</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>44516</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44834</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44496</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44626</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>44690</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44682</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44708</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>44642</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44776</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44746</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>44845</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>44543</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>44543</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>44495</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>44749</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44545</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>44722</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44742</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44756</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44806</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>44511</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44510</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>44867</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44511</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44683</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44539</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>44516</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44496</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44712</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44769</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44543</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44543</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>44545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>44545</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44621</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44496</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>44637</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44735</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>44763</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>44735</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>44524</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44575</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44572</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44650</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>44725</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>44580</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>44777</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44665</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44637</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44655</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>44595</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44744</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44826</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44526</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>44845</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>44642</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44637</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44607</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>44698</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>44609</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44817</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44760</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>44584</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>44678</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44682</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>44682</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>44623</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>44665</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44665</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>44533</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44704</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44543</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>44682</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44523</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>44595</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44725</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>44815</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45888</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44495</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45621</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>44682</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>45587</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44743</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45813</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45085</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45075</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45075</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>44764</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45051</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45749</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45362</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45894</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45894</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45859</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45893</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45859</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45893</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45894</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45896</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45203</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44925</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44824</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45897</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>44866</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>45898</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>45898</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45561</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45897</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45897</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45625</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45208</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44879</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45427</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44922</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44833</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>44767</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>44995</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45721</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>44750</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>44750</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45338</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45082</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45831</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45908</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45772</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>46111</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45910</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45468</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45886</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45916</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45261</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45831</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45253</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45817</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45621</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44938</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45918</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>44753</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>44698</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45786</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>44777</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45668</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45670</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45923</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44599</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>46167</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45853</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>44743</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45640</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45957</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45956</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45330</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>44858</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45930</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45930</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45930</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45453</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45936</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45310</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45310</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45935</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45933</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>44700</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45218</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45254</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45933</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45937</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45356</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45937</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45089</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45159</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45322</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45414</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>46174</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45845</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44840</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45433</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45435</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44895</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>46177</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>45944</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45225</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45139</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45450</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45450</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45755</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45239</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44845</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45082</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45558</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45454</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44809</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45202</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45075</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45075</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45075</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45075</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>44962</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45089</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45482</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>44866</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>46178</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>46181</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>44956</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>46181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45084</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45257</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44803</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46178</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45952</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>46178</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>46183</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45951</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>44687</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45957</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45954</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45956</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46183</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>46183</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45960</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45448</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>46188</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45257</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>46188</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>46191</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46191</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>46191</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45056</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46077</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>45530</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45218</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44817</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46195</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45022</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45971</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>44841</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45518</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45757</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>46197</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46197</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45721</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>46197</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45708</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45973</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>44934</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44778</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>44581</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45376</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45293</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45245</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45957</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>44956</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44931</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45460</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45293</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>46202</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>46203</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>46203</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45617</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>46204</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45982</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>44900</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45063</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44714</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>44956</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>46204</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45245</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45356</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45092</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45985</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>44816</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45075</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45490</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>46207</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>46206</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45357</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46209</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45600</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>45644</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45086</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45992</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45253</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45737</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45175</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45119</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45994</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45463</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45993</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45468</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45994</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45993</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>46216</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45996</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>46218</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45259</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45999</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45253</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46220</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45316</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45190</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>46002</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46002</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46225</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>46000</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>46001</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45783</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>46008</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45783</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45385</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>46008</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45847</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45549</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>46237</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45187</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45735</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>44834</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45709</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>46009</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>46238</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>45572</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45537</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45579</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>46239</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46239</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45352</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>44578</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45408</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>46029</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45635</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>46030</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>46241</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46029</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46029</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46034</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46034</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46036</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>46036</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45272</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45272</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45385</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45729</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>46283</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45713</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>45436</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45518</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45475</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45414</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         <v>46042</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>44708</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45798</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>45798</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>45798</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>46288</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>46043</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>46288</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>46047</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45800</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>46049</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>46049</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46049</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46049</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45803</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45224</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>46052</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>44813</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>46289</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>45524</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45890</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45586</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54688,7 +54688,7 @@
         <v>46289</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>46289</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54834,7 +54834,7 @@
         <v>46182</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>46284</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>46284</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>46056</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>46247</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         <v>46247</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55277,7 +55277,7 @@
         <v>46247</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -55350,7 +55350,7 @@
         <v>46289</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>46058</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -55501,7 +55501,7 @@
         <v>46057</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>45790</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>45810</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>46057</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55803,7 +55803,7 @@
         <v>46247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>46246</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>46057</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45810</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>46293</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>45810</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56246,7 +56246,7 @@
         <v>46061</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>46062</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>45341</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>46063</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45813</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56616,7 +56616,7 @@
         <v>46063</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>46065</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>45376</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>46065</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>46065</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>46069</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45817</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>46069</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45747</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>46069</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>46072</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>46077</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>46077</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57600,7 +57600,7 @@
         <v>46077</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>46077</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45824</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57834,7 +57834,7 @@
         <v>45831</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57907,7 +57907,7 @@
         <v>45728</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57980,7 +57980,7 @@
         <v>46084</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58053,7 +58053,7 @@
         <v>45834</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45834</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45834</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58272,7 +58272,7 @@
         <v>45835</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>46254</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
         <v>46254</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -58501,7 +58501,7 @@
         <v>45840</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>46093</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58647,7 +58647,7 @@
         <v>46094</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58725,7 +58725,7 @@
         <v>45839</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58798,7 +58798,7 @@
         <v>46094</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>44952</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58954,7 +58954,7 @@
         <v>46254</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>46094</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59105,7 +59105,7 @@
         <v>46300</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45469</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59251,7 +59251,7 @@
         <v>45469</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59324,7 +59324,7 @@
         <v>45581</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>46100</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45152</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>46100</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>46255</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59689,7 +59689,7 @@
         <v>46259</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>46258</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>46258</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45852</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45855</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60059,7 +60059,7 @@
         <v>45855</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>46259</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>46113</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60283,7 +60283,7 @@
         <v>46258</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>45776</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45952</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>46119</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>46119</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60653,7 +60653,7 @@
         <v>46119</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60731,7 +60731,7 @@
         <v>45446</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>45525</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>46119</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>46261</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>45586</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45799</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45890</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>44540</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>45414</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>46261</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>46261</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>46260</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>46304</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45089</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>46107</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45776</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>46132</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>46304</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45880</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>44904</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>45386</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62274,7 +62274,7 @@
         <v>45882</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -62347,7 +62347,7 @@
         <v>44901</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>46265</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>46134</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62566,7 +62566,7 @@
         <v>45075</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62639,7 +62639,7 @@
         <v>46133</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62712,7 +62712,7 @@
         <v>45075</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62785,7 +62785,7 @@
         <v>44525</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62858,7 +62858,7 @@
         <v>45610</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62931,7 +62931,7 @@
         <v>44993</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>45638</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63087,7 +63087,7 @@
         <v>45531</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63160,7 +63160,7 @@
         <v>44525</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63238,7 +63238,7 @@
         <v>45712</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63316,7 +63316,7 @@
         <v>45898</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -63389,7 +63389,7 @@
         <v>46207</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -63462,7 +63462,7 @@
         <v>45700</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63540,7 +63540,7 @@
         <v>46119</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63618,7 +63618,7 @@
         <v>45735</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63691,7 +63691,7 @@
         <v>46135</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63764,7 +63764,7 @@
         <v>46266</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63837,7 +63837,7 @@
         <v>45835</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63915,7 +63915,7 @@
         <v>45442</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -63988,7 +63988,7 @@
         <v>45435</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>45155</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>46309</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64212,7 +64212,7 @@
         <v>46266</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64285,7 +64285,7 @@
         <v>46266</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -64358,7 +64358,7 @@
         <v>46266</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>44938</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64504,7 +64504,7 @@
         <v>45903</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64582,7 +64582,7 @@
         <v>45490</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         <v>46268</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -64733,7 +64733,7 @@
         <v>46268</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>45667</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>45853</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -64952,7 +64952,7 @@
         <v>45953</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65025,7 +65025,7 @@
         <v>45817</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         <v>46311</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65171,7 +65171,7 @@
         <v>46254</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65244,7 +65244,7 @@
         <v>44902</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -65317,7 +65317,7 @@
         <v>45797</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -65390,7 +65390,7 @@
         <v>45953</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -65463,7 +65463,7 @@
         <v>45835</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>45687</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -65619,7 +65619,7 @@
         <v>46314</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
         <v>45880</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -65770,7 +65770,7 @@
         <v>44923</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>45391</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>45670</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>46261</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66062,7 +66062,7 @@
         <v>45412</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>44585</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>45587</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45706</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -66364,7 +66364,7 @@
         <v>45552</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>46261</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>45723</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>44945</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -66661,7 +66661,7 @@
         <v>44937</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -66734,7 +66734,7 @@
         <v>45145</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -66807,7 +66807,7 @@
         <v>45971</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66880,7 +66880,7 @@
         <v>45215</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66953,7 +66953,7 @@
         <v>46272</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>45155</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>45254</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67172,7 +67172,7 @@
         <v>45260</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67245,7 +67245,7 @@
         <v>45260</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -67318,7 +67318,7 @@
         <v>44714</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>46274</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>46311</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -67542,7 +67542,7 @@
         <v>45800</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -67615,7 +67615,7 @@
         <v>46311</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -67688,7 +67688,7 @@
         <v>45205</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>45813</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67839,7 +67839,7 @@
         <v>45701</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67912,7 +67912,7 @@
         <v>46294</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -67985,7 +67985,7 @@
         <v>44611</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68058,7 +68058,7 @@
         <v>44986</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68131,7 +68131,7 @@
         <v>46150</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>44775</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         <v>45223</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>46150</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -68423,7 +68423,7 @@
         <v>46150</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>44693</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>44867</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -68642,7 +68642,7 @@
         <v>46155</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -68715,7 +68715,7 @@
         <v>45075</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68788,7 +68788,7 @@
         <v>45348</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68866,7 +68866,7 @@
         <v>45817</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68939,7 +68939,7 @@
         <v>44803</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>45947</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69085,7 +69085,7 @@
         <v>45693</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69158,7 +69158,7 @@
         <v>45092</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>45092</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -69304,7 +69304,7 @@
         <v>45075</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>45636</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -69450,7 +69450,7 @@
         <v>45020</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -69523,7 +69523,7 @@
         <v>45139</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -69596,7 +69596,7 @@
         <v>45614</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -69669,7 +69669,7 @@
         <v>44704</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -69742,7 +69742,7 @@
         <v>45022</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>45168</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69893,7 +69893,7 @@
         <v>44790</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -69966,7 +69966,7 @@
         <v>45411</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>44953</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70117,7 +70117,7 @@
         <v>45519</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70190,7 +70190,7 @@
         <v>45107</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70263,7 +70263,7 @@
         <v>45111</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -70336,7 +70336,7 @@
         <v>44974</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -70409,7 +70409,7 @@
         <v>44771</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -70482,7 +70482,7 @@
         <v>45609</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -70555,7 +70555,7 @@
         <v>44743</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -70633,7 +70633,7 @@
         <v>45601</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>45177</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>44763</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70852,7 +70852,7 @@
         <v>44495</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70925,7 +70925,7 @@
         <v>44749</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -70998,7 +70998,7 @@
         <v>44782</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71071,7 +71071,7 @@
         <v>44719</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71144,7 +71144,7 @@
         <v>44980</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71217,7 +71217,7 @@
         <v>45700</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -71290,7 +71290,7 @@
         <v>45707</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -71363,7 +71363,7 @@
         <v>44777</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -71436,7 +71436,7 @@
         <v>45085</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -71509,7 +71509,7 @@
         <v>45243</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>44760</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>45042</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>45219</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71806,7 +71806,7 @@
         <v>45442</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>45068</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>45063</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>45191</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72103,7 +72103,7 @@
         <v>44510</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72181,7 +72181,7 @@
         <v>44815</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>45771</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -72327,7 +72327,7 @@
         <v>45730</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -72400,7 +72400,7 @@
         <v>45554</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -72473,7 +72473,7 @@
         <v>44670</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -72546,7 +72546,7 @@
         <v>44851</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -72619,7 +72619,7 @@
         <v>45054</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -72692,7 +72692,7 @@
         <v>45236</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72765,7 +72765,7 @@
         <v>45055</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72838,7 +72838,7 @@
         <v>45075</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72911,7 +72911,7 @@
         <v>44596</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -72989,7 +72989,7 @@
         <v>44549</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73062,7 +73062,7 @@
         <v>45063</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73135,7 +73135,7 @@
         <v>45065</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -73213,7 +73213,7 @@
         <v>45469</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -73286,7 +73286,7 @@
         <v>44760</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -73359,7 +73359,7 @@
         <v>44816</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -73432,7 +73432,7 @@
         <v>45089</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -73505,7 +73505,7 @@
         <v>45740</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>45740</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -73651,7 +73651,7 @@
         <v>45344</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73724,7 +73724,7 @@
         <v>45231</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73797,7 +73797,7 @@
         <v>44992</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73870,7 +73870,7 @@
         <v>45054</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -73943,7 +73943,7 @@
         <v>45054</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74016,7 +74016,7 @@
         <v>45104</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>45022</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74162,7 +74162,7 @@
         <v>44643</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -74235,7 +74235,7 @@
         <v>44949</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -74308,7 +74308,7 @@
         <v>44953</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>44963</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -74454,7 +74454,7 @@
         <v>45084</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -74527,7 +74527,7 @@
         <v>44882</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -74600,7 +74600,7 @@
         <v>45455</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -74673,7 +74673,7 @@
         <v>45147</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74746,7 +74746,7 @@
         <v>44556</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74819,7 +74819,7 @@
         <v>44621</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74892,7 +74892,7 @@
         <v>44868</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -74965,7 +74965,7 @@
         <v>45104</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75038,7 +75038,7 @@
         <v>45104</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75111,7 +75111,7 @@
         <v>45376</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -75184,7 +75184,7 @@
         <v>44510</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -75262,7 +75262,7 @@
         <v>45576</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -75335,7 +75335,7 @@
         <v>45385</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -75408,7 +75408,7 @@
         <v>45536</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -75481,7 +75481,7 @@
         <v>45170</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -75554,7 +75554,7 @@
         <v>44525</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -75627,7 +75627,7 @@
         <v>44546</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75700,7 +75700,7 @@
         <v>44516</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75778,7 +75778,7 @@
         <v>44516</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75856,7 +75856,7 @@
         <v>45468</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -75929,7 +75929,7 @@
         <v>44769</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76002,7 +76002,7 @@
         <v>45271</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76075,7 +76075,7 @@
         <v>45642</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -76148,7 +76148,7 @@
         <v>44637</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -76226,7 +76226,7 @@
         <v>45443</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -76299,7 +76299,7 @@
         <v>45245</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -76372,7 +76372,7 @@
         <v>44953</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -76445,7 +76445,7 @@
         <v>45533</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -76518,7 +76518,7 @@
         <v>45547</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -76591,7 +76591,7 @@
         <v>44584</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -76664,7 +76664,7 @@
         <v>45721</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -76737,7 +76737,7 @@
         <v>44795</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -76810,7 +76810,7 @@
         <v>45075</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -76883,7 +76883,7 @@
         <v>45075</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -76956,7 +76956,7 @@
         <v>45075</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77029,7 +77029,7 @@
         <v>45089</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -77102,7 +77102,7 @@
         <v>45203</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -77175,7 +77175,7 @@
         <v>44596</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -77248,7 +77248,7 @@
         <v>45636</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -77321,7 +77321,7 @@
         <v>45639</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -77394,7 +77394,7 @@
         <v>45644</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -77467,7 +77467,7 @@
         <v>45450</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -77545,7 +77545,7 @@
         <v>44580</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -77618,7 +77618,7 @@
         <v>45113</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -77691,7 +77691,7 @@
         <v>44673</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -77764,7 +77764,7 @@
         <v>44648</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -77837,7 +77837,7 @@
         <v>44643</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -77910,7 +77910,7 @@
         <v>44816</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -77983,7 +77983,7 @@
         <v>45456</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -78056,7 +78056,7 @@
         <v>45617</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -78129,7 +78129,7 @@
         <v>45121</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -78202,7 +78202,7 @@
         <v>45232</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -78275,7 +78275,7 @@
         <v>45376</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -78348,7 +78348,7 @@
         <v>45183</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -78421,7 +78421,7 @@
         <v>44644</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -78494,7 +78494,7 @@
         <v>44635</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -78567,7 +78567,7 @@
         <v>44670</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -78640,7 +78640,7 @@
         <v>45695</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -78718,7 +78718,7 @@
         <v>45208</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -78791,7 +78791,7 @@
         <v>45202</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -78864,7 +78864,7 @@
         <v>44624</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -78937,7 +78937,7 @@
         <v>45147</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -79010,7 +79010,7 @@
         <v>44687</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -79088,7 +79088,7 @@
         <v>45775</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -79161,7 +79161,7 @@
         <v>45146</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -79239,7 +79239,7 @@
         <v>45522</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -79312,7 +79312,7 @@
         <v>45685</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -79385,7 +79385,7 @@
         <v>45757</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -79458,7 +79458,7 @@
         <v>45174</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -79536,7 +79536,7 @@
         <v>45686</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -79609,7 +79609,7 @@
         <v>44704</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -79682,7 +79682,7 @@
         <v>45208</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -79755,7 +79755,7 @@
         <v>45208</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -79828,7 +79828,7 @@
         <v>45237</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -79901,7 +79901,7 @@
         <v>45145</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -79974,7 +79974,7 @@
         <v>45245</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -80047,7 +80047,7 @@
         <v>44708</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -80120,7 +80120,7 @@
         <v>44708</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -80198,7 +80198,7 @@
         <v>44746</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -80271,7 +80271,7 @@
         <v>44684</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -80344,7 +80344,7 @@
         <v>45127</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -80422,7 +80422,7 @@
         <v>45245</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -80495,7 +80495,7 @@
         <v>44743</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -80573,7 +80573,7 @@
         <v>44732</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -80646,7 +80646,7 @@
         <v>45208</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -80719,7 +80719,7 @@
         <v>45128</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -80792,7 +80792,7 @@
         <v>44799</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -80865,7 +80865,7 @@
         <v>45293</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -80943,7 +80943,7 @@
         <v>45254</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -81016,7 +81016,7 @@
         <v>44925</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -81089,7 +81089,7 @@
         <v>44806</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -81162,7 +81162,7 @@
         <v>44783</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -81235,7 +81235,7 @@
         <v>44785</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -81313,7 +81313,7 @@
         <v>45394</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -81386,7 +81386,7 @@
         <v>45019</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -81459,7 +81459,7 @@
         <v>45631</v>
     